--- a/excel_ai/legacy/workbooks/Tracking issues.xlsx
+++ b/excel_ai/legacy/workbooks/Tracking issues.xlsx
@@ -15,7 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPAT_dev" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BUGSandISSUES'!$A$3:$R$308</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BUGSandISSUES'!$A$3:$S$312</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
 </workbook>
@@ -1016,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R308"/>
+  <dimension ref="A1:S312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1037,12 +1037,13 @@
     <col width="18" customWidth="1" min="16" max="16"/>
     <col width="26" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="48" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="45" t="inlineStr">
         <is>
-          <t>Bugs and issues of legacy CPAT and whether CPAT-AI-Mitigation-MVP v7.0 replicates them (our codes: L legacy bugs, D distribution bugs, I issues, DI distribution issues, M prototype bugs, LD LegacyDiff rows)</t>
+          <t>Bugs and issues of legacy CPAT and whether CPAT-AI-Mitigation-Prototype v7.0 replicates them (our codes: L legacy bugs, D distribution bugs, I issues, DI distribution issues, M prototype bugs, LD LegacyDiff rows)</t>
         </is>
       </c>
       <c r="B1" s="46" t="n"/>
@@ -1059,7 +1060,7 @@
     <row r="2">
       <c r="A2" s="52" t="inlineStr">
         <is>
-          <t>Updated from the register (issues_register_v7_0.py) by update_tracker_v7_0.py. Details, fix procedure and cell-level plans: documentation/CPAT-AI-Mitigation-MVP_BugsAndIssues_v7.0.docx. Columns L-R added. Codes are keyed to legacy file 456; the 459 file is not reconciled yet.</t>
+          <t>Updated from the register (issues_register.py) by update_tracker.py. Details, fix procedure and cell-level plans: excel_ai/CPAT-AI_BugsAndIssues_latest.docx. Columns L-R added. Codes are keyed to legacy file 456; the 459 file is not reconciled yet. Column S: the fixes checked in legacy 465 (excel_ai/bugsfixed/).</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1132,7 @@
       </c>
       <c r="N3" s="47" t="inlineStr">
         <is>
-          <t>Settled in (MVP version)</t>
+          <t>Settled in (prototype version)</t>
         </is>
       </c>
       <c r="O3" s="47" t="inlineStr">
@@ -1152,6 +1153,11 @@
       <c r="R3" s="47" t="inlineStr">
         <is>
           <t>Updated</t>
+        </is>
+      </c>
+      <c r="S3" s="47" t="inlineStr">
+        <is>
+          <t>Status in legacy 465</t>
         </is>
       </c>
     </row>
@@ -1238,6 +1244,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S4" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="38.25" customHeight="1">
       <c r="A5" s="48" t="inlineStr">
@@ -1326,6 +1337,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S5" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="51" customHeight="1">
       <c r="A6" s="48" t="inlineStr">
@@ -1414,6 +1430,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S6" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="38.25" customHeight="1">
       <c r="A7" s="48" t="inlineStr">
@@ -1498,6 +1519,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S7" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="51" customHeight="1">
       <c r="A8" s="48" t="inlineStr">
@@ -1582,6 +1608,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S8" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="51" customHeight="1">
       <c r="A9" s="48" t="inlineStr">
@@ -1666,6 +1697,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S9" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="38.25" customHeight="1">
       <c r="A10" s="48" t="inlineStr">
@@ -1754,6 +1790,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S10" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="25.5" customHeight="1">
       <c r="A11" s="48" t="inlineStr">
@@ -1842,6 +1883,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S11" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="38.25" customHeight="1">
       <c r="A12" s="48" t="inlineStr">
@@ -1926,6 +1972,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S12" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="38.25" customHeight="1">
       <c r="A13" s="48" t="inlineStr">
@@ -2010,6 +2061,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S13" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="38.25" customHeight="1">
       <c r="A14" s="48" t="inlineStr">
@@ -2049,7 +2105,7 @@
       </c>
       <c r="H14" s="48" t="inlineStr">
         <is>
-          <t>None while G4291 stays empty; wrong dispatch if anything is typed there. MVP: Harmless while the cell is empty; not built in the MVP.</t>
+          <t>None while G4291 stays empty; wrong dispatch if anything is typed there. prototype: Harmless while the cell is empty; not built in the prototype.</t>
         </is>
       </c>
       <c r="I14" s="48" t="inlineStr">
@@ -2094,6 +2150,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S14" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed: exactly the planned fix (the $G4291 term is gone)</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="25.5" customHeight="1">
       <c r="A15" s="48" t="inlineStr">
@@ -2133,7 +2194,7 @@
       </c>
       <c r="H15" s="48" t="inlineStr">
         <is>
-          <t>Reported total investment is 0. MVP: Reporting only; the MVP sums.</t>
+          <t>Reported total investment is 0. prototype: Reporting only; the prototype sums.</t>
         </is>
       </c>
       <c r="I15" s="48" t="inlineStr">
@@ -2178,6 +2239,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S15" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="63.75" customHeight="1">
       <c r="A16" s="48" t="inlineStr">
@@ -2217,7 +2283,7 @@
       </c>
       <c r="H16" s="48" t="inlineStr">
         <is>
-          <t>Retail price falls to the 0.01 floor with the oil price; fuel use rises tenfold by 2030 (Egypt). MVP: Changed in the MVP (v0.10, user decision): pass-through and margin from the IMF dataset like the other oil products (LegacyDiff).</t>
+          <t>Retail price falls to the 0.01 floor with the oil price; fuel use rises tenfold by 2030 (Egypt). prototype: Changed in the prototype (v0.10, user decision): pass-through and margin from the IMF dataset like the other oil products (LegacyDiff).</t>
         </is>
       </c>
       <c r="I16" s="48" t="inlineStr">
@@ -2268,6 +2334,11 @@
       <c r="R16" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S16" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2380,7 @@
       </c>
       <c r="H17" s="48" t="inlineStr">
         <is>
-          <t>Taxes jump in the first projected year when pass-through is between 0 and 1 (none for Egypt: 0 or 1). MVP: Fixed in v4.10 (user rule: bugs are never replicated): the floating part is (1 - pass-through) x (last tax + fall in supply cost), applied once (txf; PriceProjection_Method_v7_0.md A10); no effect for Egypt (pass-through 0 or 1).</t>
+          <t>Taxes jump in the first projected year when pass-through is between 0 and 1 (none for Egypt: 0 or 1). prototype: Fixed in v4.10 (user rule: bugs are never replicated): the floating part is (1 - pass-through) x (last tax + fall in supply cost), applied once (txf; Methods, chapter Prices A10); no effect for Egypt (pass-through 0 or 1).</t>
         </is>
       </c>
       <c r="I17" s="48" t="inlineStr">
@@ -2358,6 +2429,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S17" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="51" customHeight="1">
       <c r="A18" s="48" t="inlineStr">
@@ -2397,7 +2473,7 @@
       </c>
       <c r="H18" s="48" t="inlineStr">
         <is>
-          <t>The ETS price effectiveness ignores the volatility inputs. MVP: Replaced in the MVP by the volatility adjustment (v1.02); suggested to the legacy team (TODO).</t>
+          <t>The ETS price effectiveness ignores the volatility inputs. prototype: Replaced in the prototype by the volatility adjustment (v1.02); suggested to the legacy team (TODO).</t>
         </is>
       </c>
       <c r="I18" s="48" t="inlineStr">
@@ -2446,6 +2522,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S18" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="63.75" customHeight="1">
       <c r="A19" s="48" t="inlineStr">
@@ -2485,7 +2566,7 @@
       </c>
       <c r="H19" s="48" t="inlineStr">
         <is>
-          <t>The fast ETS price estimate is off for large cuts, so the goal seek starts far from the answer. MVP: MVP uses the log form LN(cap / baseline) / (semi-elasticity x effectiveness x volatility adjustment) (v1.02).</t>
+          <t>The fast ETS price estimate is off for large cuts, so the goal seek starts far from the answer. prototype: prototype uses the log form LN(cap / baseline) / (semi-elasticity x effectiveness x volatility adjustment) (v1.02).</t>
         </is>
       </c>
       <c r="I19" s="48" t="inlineStr">
@@ -2534,6 +2615,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S19" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: log form in L1868 only; M1868:P1868 are still the constant 0 (plan: fill L1868:AE1868); Q onward is the L57 formula</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="63.75" customHeight="1">
       <c r="A20" s="48" t="inlineStr">
@@ -2573,7 +2659,7 @@
       </c>
       <c r="H20" s="48" t="inlineStr">
         <is>
-          <t>Non-energy methane is flat and a methane fee on agriculture and waste has no effect. MVP: Fixed in v2.8: the sources grow with income and population and the fee abates them along their curves (GHG_Method_v7_0.md).</t>
+          <t>Non-energy methane is flat and a methane fee on agriculture and waste has no effect. prototype: Fixed in v2.8: the sources grow with income and population and the fee abates them along their curves (Methods, chapter Emissions).</t>
         </is>
       </c>
       <c r="I20" s="48" t="inlineStr">
@@ -2624,6 +2710,11 @@
       <c r="R20" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S20" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2756,7 @@
       </c>
       <c r="H21" s="48" t="inlineStr">
         <is>
-          <t>Methane overstated and CO2 understated when the fee abates oil and gas methane. MVP: Fixed in v2.8: reported as CO2 in energy (row ghg.flr).</t>
+          <t>Methane overstated and CO2 understated when the fee abates oil and gas methane. prototype: Fixed in v2.8: reported as CO2 in energy (row ghg.flr).</t>
         </is>
       </c>
       <c r="I21" s="48" t="inlineStr">
@@ -2714,6 +2805,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S21" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="51" customHeight="1">
       <c r="A22" s="48" t="inlineStr">
@@ -2753,7 +2849,7 @@
       </c>
       <c r="H22" s="48" t="inlineStr">
         <is>
-          <t>Egypt reaches 185 million in 2041 instead of 147 million; agriculture, waste and other GHGs too high after 2030. MVP: Fixed in v2.8: population from UNPop (UN WPP).</t>
+          <t>Egypt reaches 185 million in 2041 instead of 147 million; agriculture, waste and other GHGs too high after 2030. prototype: Fixed in v2.8: population from UNPop (UN WPP).</t>
         </is>
       </c>
       <c r="I22" s="48" t="inlineStr">
@@ -2804,6 +2900,11 @@
       <c r="R22" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S22" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2946,7 @@
       </c>
       <c r="H23" s="48" t="inlineStr">
         <is>
-          <t>Waste methane is abated as if it were livestock. MVP: Fixed in v2.8: every source uses its own curve.</t>
+          <t>Waste methane is abated as if it were livestock. prototype: Fixed in v2.8: every source uses its own curve.</t>
         </is>
       </c>
       <c r="I23" s="48" t="inlineStr">
@@ -2894,6 +2995,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S23" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24" s="48" t="inlineStr">
@@ -2933,7 +3039,7 @@
       </c>
       <c r="H24" s="48" t="inlineStr">
         <is>
-          <t>Pollutant totals miss navigation. MVP: Fixed in v2.9: navigation included (section 15).</t>
+          <t>Pollutant totals miss navigation. prototype: Fixed in v2.9: navigation included (section 15).</t>
         </is>
       </c>
       <c r="I24" s="48" t="inlineStr">
@@ -2982,6 +3088,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S24" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="76.5" customHeight="1">
       <c r="A25" s="48" t="inlineStr">
@@ -3021,7 +3132,7 @@
       </c>
       <c r="H25" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt (they emit zero there); totals too low wherever they emit. MVP: Fixed in v3.0: totals = all subsectors + power.</t>
+          <t>None for Egypt (they emit zero there); totals too low wherever they emit. prototype: Fixed in v3.0: totals = all subsectors + power.</t>
         </is>
       </c>
       <c r="I25" s="48" t="inlineStr">
@@ -3070,6 +3181,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S25" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="76.5" customHeight="1">
       <c r="A26" s="48" t="inlineStr">
@@ -3109,7 +3225,7 @@
       </c>
       <c r="H26" s="48" t="inlineStr">
         <is>
-          <t>A steady effect of 0.5% compounds to about +10% of GDP after 20 years, in every run with endogenous GDP effects (the NoPropData file strips these rows). MVP: Fixed in v3.1: the GDP level is raised by the effect (growth from the ratio of level factors).</t>
+          <t>A steady effect of 0.5% compounds to about +10% of GDP after 20 years, in every run with endogenous GDP effects (the NoPropData file strips these rows). prototype: Fixed in v3.1: the GDP level is raised by the effect (growth from the ratio of level factors).</t>
         </is>
       </c>
       <c r="I26" s="48" t="inlineStr">
@@ -3158,6 +3274,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S26" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="63.75" customHeight="1">
       <c r="A27" s="48" t="inlineStr">
@@ -3197,7 +3318,7 @@
       </c>
       <c r="H27" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I27" s="48" t="inlineStr">
@@ -3246,6 +3367,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S27" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="63.75" customHeight="1">
       <c r="A28" s="48" t="inlineStr">
@@ -3285,7 +3411,7 @@
       </c>
       <c r="H28" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I28" s="48" t="inlineStr">
@@ -3334,6 +3460,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S28" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="76.5" customHeight="1">
       <c r="A29" s="48" t="inlineStr">
@@ -3373,7 +3504,7 @@
       </c>
       <c r="H29" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -33.9%, diesel -37.9%, road electricity -52.4%, passenger EV sales share -2.6 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -33.9%, diesel -37.9%, road electricity -52.4%, passenger EV sales share -2.6 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I29" s="48" t="inlineStr">
@@ -3422,6 +3553,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S29" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="76.5" customHeight="1">
       <c r="A30" s="48" t="inlineStr">
@@ -3461,7 +3597,7 @@
       </c>
       <c r="H30" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.0%, road electricity -0.6%, passenger EV sales share -0.1 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.0%, road electricity -0.6%, passenger EV sales share -0.1 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I30" s="48" t="inlineStr">
@@ -3510,6 +3646,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S30" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="63.75" customHeight="1">
       <c r="A31" s="48" t="inlineStr">
@@ -3549,7 +3690,7 @@
       </c>
       <c r="H31" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I31" s="48" t="inlineStr">
@@ -3598,6 +3739,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S31" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="76.5" customHeight="1">
       <c r="A32" s="48" t="inlineStr">
@@ -3637,7 +3783,7 @@
       </c>
       <c r="H32" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel -0.3%, road electricity -16.8%, passenger EV sales share +0.0 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel -0.3%, road electricity -16.8%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I32" s="48" t="inlineStr">
@@ -3686,6 +3832,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S32" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="76.5" customHeight="1">
       <c r="A33" s="48" t="inlineStr">
@@ -3725,7 +3876,7 @@
       </c>
       <c r="H33" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.0%, road electricity -0.3%, passenger EV sales share +0.0 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.0%, road electricity -0.3%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I33" s="48" t="inlineStr">
@@ -3774,6 +3925,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S33" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="63.75" customHeight="1">
       <c r="A34" s="48" t="inlineStr">
@@ -3813,7 +3969,7 @@
       </c>
       <c r="H34" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I34" s="48" t="inlineStr">
@@ -3862,6 +4018,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S34" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="76.5" customHeight="1">
       <c r="A35" s="48" t="inlineStr">
@@ -3901,7 +4062,7 @@
       </c>
       <c r="H35" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel -0.2%, road electricity +4.0%, passenger EV sales share +0.0 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel -0.2%, road electricity +4.0%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I35" s="48" t="inlineStr">
@@ -3950,6 +4111,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S35" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="76.5" customHeight="1">
       <c r="A36" s="48" t="inlineStr">
@@ -3989,7 +4155,7 @@
       </c>
       <c r="H36" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.2%, road electricity -1.0%, passenger EV sales share -0.0 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +0.0%, diesel +0.2%, road electricity -1.0%, passenger EV sales share -0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I36" s="48" t="inlineStr">
@@ -4038,6 +4204,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S36" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="76.5" customHeight="1">
       <c r="A37" s="48" t="inlineStr">
@@ -4077,7 +4248,7 @@
       </c>
       <c r="H37" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.1%, road electricity +0.2%, passenger EV sales share +0.0 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.0%, diesel +0.1%, road electricity +0.2%, passenger EV sales share +0.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I37" s="48" t="inlineStr">
@@ -4126,6 +4297,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S37" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="63.75" customHeight="1">
       <c r="A38" s="48" t="inlineStr">
@@ -4165,7 +4341,7 @@
       </c>
       <c r="H38" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I38" s="48" t="inlineStr">
@@ -4214,6 +4390,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S38" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="76.5" customHeight="1">
       <c r="A39" s="48" t="inlineStr">
@@ -4253,7 +4434,7 @@
       </c>
       <c r="H39" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline -0.1%, diesel -0.0%, road electricity +1.2%, passenger EV sales share +0.5 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline -0.1%, diesel -0.0%, road electricity +1.2%, passenger EV sales share +0.5 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I39" s="48" t="inlineStr">
@@ -4302,6 +4483,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S39" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="76.5" customHeight="1">
       <c r="A40" s="48" t="inlineStr">
@@ -4341,7 +4527,7 @@
       </c>
       <c r="H40" s="48" t="inlineStr">
         <is>
-          <t>Egypt engineer baseline 2035: gasoline +5.1%, diesel +3.1%, road electricity -50.7%, passenger EV sales share -10.0 points. MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>Egypt engineer baseline 2035: gasoline +5.1%, diesel +3.1%, road electricity -50.7%, passenger EV sales share -10.0 points. prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I40" s="48" t="inlineStr">
@@ -4390,6 +4576,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S40" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="63.75" customHeight="1">
       <c r="A41" s="48" t="inlineStr">
@@ -4429,7 +4620,7 @@
       </c>
       <c r="H41" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I41" s="48" t="inlineStr">
@@ -4478,6 +4669,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S41" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="63.75" customHeight="1">
       <c r="A42" s="48" t="inlineStr">
@@ -4517,7 +4713,7 @@
       </c>
       <c r="H42" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I42" s="48" t="inlineStr">
@@ -4566,6 +4762,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S42" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="63.75" customHeight="1">
       <c r="A43" s="48" t="inlineStr">
@@ -4605,7 +4806,7 @@
       </c>
       <c r="H43" s="48" t="inlineStr">
         <is>
-          <t>None in the Egypt engineer run (the policy or fuel is zero there). MVP: Fixed in the MVP engineer road model (v3.5; Transport_vs_Legacy_v7_0.md); latent in the legacy Egypt run (elasticity road model).</t>
+          <t>None in the Egypt engineer run (the policy or fuel is zero there). prototype: Fixed in the prototype engineer road model (v3.5; Methods, chapter Transport); latent in the legacy Egypt run (elasticity road model).</t>
         </is>
       </c>
       <c r="I43" s="48" t="inlineStr">
@@ -4654,6 +4855,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S43" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="51" customHeight="1">
       <c r="A44" s="48" t="inlineStr">
@@ -4693,7 +4899,7 @@
       </c>
       <c r="H44" s="48" t="inlineStr">
         <is>
-          <t>Jet fuel x0.87 (2023) to x1.07 (2040) against the standard form. MVP: Fixed in v3.11: jet fuel in the MVP with the standard form (shock once) and the transport oil income elasticity.</t>
+          <t>Jet fuel x0.87 (2023) to x1.07 (2040) against the standard form. prototype: Fixed in v3.11: jet fuel in the prototype with the standard form (shock once) and the transport oil income elasticity.</t>
         </is>
       </c>
       <c r="I44" s="48" t="inlineStr">
@@ -4744,6 +4950,11 @@
       <c r="R44" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S44" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4996,7 @@
       </c>
       <c r="H45" s="48" t="inlineStr">
         <is>
-          <t>Other energy use flat with GDP: about -46 ktoe (2030) and -124 ktoe (2040) for Egypt. MVP: Fixed in the MVP: other energy use grows with GDP (oil, industry elasticities).</t>
+          <t>Other energy use flat with GDP: about -46 ktoe (2030) and -124 ktoe (2040) for Egypt. prototype: Fixed in the prototype: other energy use grows with GDP (oil, industry elasticities).</t>
         </is>
       </c>
       <c r="I45" s="48" t="inlineStr">
@@ -4834,6 +5045,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S45" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" s="48" t="inlineStr">
@@ -4873,7 +5089,7 @@
       </c>
       <c r="H46" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt today. MVP: Fixed in the MVP: own price.</t>
+          <t>None for Egypt today. prototype: Fixed in the prototype: own price.</t>
         </is>
       </c>
       <c r="I46" s="48" t="inlineStr">
@@ -4918,6 +5134,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S46" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="38.25" customHeight="1">
       <c r="A47" s="48" t="inlineStr">
@@ -4957,7 +5178,7 @@
       </c>
       <c r="H47" s="48" t="inlineStr">
         <is>
-          <t>None while BiomassLeakage = No. MVP: Fixed in v5.1 (feature built, section 6b): one row set per fuel with its own price and share; fuel use = elasticity model + cumulative change computed on last year's actual use; one switch (BiomassLeakage, Settings C59).</t>
+          <t>None while BiomassLeakage = No. prototype: Fixed in v5.1 (feature built, section 6b): one row set per fuel with its own price and share; fuel use = elasticity model + cumulative change computed on last year's actual use; one switch (BiomassLeakage, Settings C59).</t>
         </is>
       </c>
       <c r="I47" s="48" t="inlineStr">
@@ -5006,6 +5227,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S47" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: 10 of 12 planned cells fixed; M5588:AE5588 (change in kerosene) is unchanged (still $C5591 and the LPG share row 5582, plan: =-L5566*M5589*$E$1785) and M5590 is =M5589 (a percent change), not =M5588 (the energy change), so the kerosene equivalent biomass M5591 is in the wrong units</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="38.25" customHeight="1">
       <c r="A48" s="48" t="inlineStr">
@@ -5045,7 +5271,7 @@
       </c>
       <c r="H48" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt (no road biofuels). MVP: Not built in the MVP (road biofuels follow gasoline and diesel; none in Egypt).</t>
+          <t>None for Egypt (no road biofuels). prototype: Not built in the prototype (road biofuels follow gasoline and diesel; none in Egypt).</t>
         </is>
       </c>
       <c r="I48" s="48" t="inlineStr">
@@ -5090,6 +5316,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S48" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="38.25" customHeight="1">
       <c r="A49" s="48" t="inlineStr">
@@ -5129,7 +5360,7 @@
       </c>
       <c r="H49" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt (no self-generated renewables). MVP: Not built in the MVP (no self-generated renewables outside power).</t>
+          <t>None for Egypt (no self-generated renewables). prototype: Not built in the prototype (no self-generated renewables outside power).</t>
         </is>
       </c>
       <c r="I49" s="48" t="inlineStr">
@@ -5174,6 +5405,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S49" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="25.5" customHeight="1">
       <c r="A50" s="48" t="inlineStr">
@@ -5213,7 +5449,7 @@
       </c>
       <c r="H50" s="48" t="inlineStr">
         <is>
-          <t>None (the initial exempt share is 0). MVP: Not built (the D8 initially-exempt split stays dead; LegacyDiff 67). The starred AlwaysExemptResLPGKer test is fixed in v5.1 (LEFT(x,3)="Yes", rows exf).</t>
+          <t>None (the initial exempt share is 0). prototype: Not built (the D8 initially-exempt split stays dead; LegacyDiff 67). The starred AlwaysExemptResLPGKer test is fixed in v5.1 (LEFT(x,3)="Yes", rows exf).</t>
         </is>
       </c>
       <c r="I50" s="48" t="inlineStr">
@@ -5264,6 +5500,11 @@
       <c r="R50" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S50" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5546,7 @@
       </c>
       <c r="H51" s="48" t="inlineStr">
         <is>
-          <t>Reported balance of payments only: the oil effect is about twice too large (Egypt 2030: 3.2 bn USD). MVP: Fixed in v3.16: every fuel group applies its share (section 16b).</t>
+          <t>Reported balance of payments only: the oil effect is about twice too large (Egypt 2030: 3.2 bn USD). prototype: Fixed in v3.16: every fuel group applies its share (section 16b).</t>
         </is>
       </c>
       <c r="I51" s="48" t="inlineStr">
@@ -5354,6 +5595,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S51" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="63.75" customHeight="1">
       <c r="A52" s="48" t="inlineStr">
@@ -5393,7 +5639,7 @@
       </c>
       <c r="H52" s="48" t="inlineStr">
         <is>
-          <t>Reported balance of payments only (the % of GDP panel shows errors). MVP: Not replicated (v3.16): the energy trade balance (data) and its change in the scenario year, no current-account level until WEO data are added.</t>
+          <t>Reported balance of payments only (the % of GDP panel shows errors). prototype: Not replicated (v3.16): the energy trade balance (data) and its change in the scenario year, no current-account level until WEO data are added.</t>
         </is>
       </c>
       <c r="I52" s="48" t="inlineStr">
@@ -5442,6 +5688,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S52" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="38.25" customHeight="1">
       <c r="A53" s="48" t="inlineStr">
@@ -5487,7 +5738,7 @@
       </c>
       <c r="J53" s="48" t="inlineStr">
         <is>
-          <t>PowerPrices_Method_v7_0.md 3.9</t>
+          <t>Methods, chapter Power 3.9</t>
         </is>
       </c>
       <c r="K53" s="48" t="inlineStr">
@@ -5520,6 +5771,11 @@
       <c r="R53" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S53" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -5598,6 +5854,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S54" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="38.25" customHeight="1">
       <c r="A55" s="48" t="inlineStr">
@@ -5632,7 +5893,7 @@
       </c>
       <c r="G55" s="48" t="inlineStr">
         <is>
-          <t>The MVP baseline differs from the cached legacy run, mainly through the fuel-use shock (I22), jet fuel (I19), the electricity price data (I20) and the fixed legacy bugs.</t>
+          <t>The prototype baseline differs from the cached legacy run, mainly through the fuel-use shock (I22), jet fuel (I19), the electricity price data (I20) and the fixed legacy bugs.</t>
         </is>
       </c>
       <c r="H55" s="48" t="n"/>
@@ -5682,6 +5943,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S55" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="51" customHeight="1">
       <c r="A56" s="48" t="inlineStr">
@@ -5727,7 +5993,7 @@
       </c>
       <c r="J56" s="48" t="inlineStr">
         <is>
-          <t>PowerPrices_Method_v7_0.md; LegacyDiff</t>
+          <t>Methods, chapter Power; LegacyDiff</t>
         </is>
       </c>
       <c r="K56" s="48" t="inlineStr">
@@ -5758,6 +6024,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S56" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="63.75" customHeight="1">
       <c r="A57" s="48" t="inlineStr">
@@ -5792,7 +6063,7 @@
       </c>
       <c r="G57" s="48" t="inlineStr">
         <is>
-          <t>Legacy allocates by one auctioned share path (MTInputs rows 90-92, default 0: everything allocated free), the same for every sector. The MVP had benchmarks by sector group typed on Constants (v1.02), so an MTInputs auctioned share had no effect; since v4.15 the benchmarks are 1 - the MTInputs share of the scenario (user 2026-10-18), as legacy. Benchmarks by sector (output-based) come later.</t>
+          <t>Legacy allocates by one auctioned share path (MTInputs rows 90-92, default 0: everything allocated free), the same for every sector. The prototype had benchmarks by sector group typed on Constants (v1.02), so an MTInputs auctioned share had no effect; since v4.15 the benchmarks are 1 - the MTInputs share of the scenario (user 2026-10-18), as legacy. Benchmarks by sector (output-based) come later.</t>
         </is>
       </c>
       <c r="H57" s="48" t="n"/>
@@ -5803,7 +6074,7 @@
       </c>
       <c r="J57" s="48" t="inlineStr">
         <is>
-          <t>ETS_Method_v7_0.md; ETS_Legacy_Algorithm_v7_0.md; LegacyDiff</t>
+          <t>Methods, chapter ETS; Methods, chapter ETS; LegacyDiff</t>
         </is>
       </c>
       <c r="K57" s="48" t="inlineStr">
@@ -5836,6 +6107,11 @@
       <c r="R57" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S57" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -5914,6 +6190,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S58" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="38.25" customHeight="1">
       <c r="A59" s="48" t="inlineStr">
@@ -5990,6 +6271,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S59" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="25.5" customHeight="1">
       <c r="A60" s="48" t="inlineStr">
@@ -6024,13 +6310,13 @@
       </c>
       <c r="G60" s="48" t="inlineStr">
         <is>
-          <t>Both follow increases in industrial energy CO2, yet the MVP is 57.2 against 66.5 Mt CO2e in 2024 and 94.9 against 119.2 in 2040.</t>
+          <t>Both follow increases in industrial energy CO2, yet the prototype is 57.2 against 66.5 Mt CO2e in 2024 and 94.9 against 119.2 in 2040.</t>
         </is>
       </c>
       <c r="H60" s="48" t="n"/>
       <c r="I60" s="48" t="inlineStr">
         <is>
-          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6590; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The MVP floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
+          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6590; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The prototype floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
         </is>
       </c>
       <c r="J60" s="48" t="inlineStr">
@@ -6070,6 +6356,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S60" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="38.25" customHeight="1">
       <c r="A61" s="48" t="inlineStr">
@@ -6115,7 +6406,7 @@
       </c>
       <c r="J61" s="48" t="inlineStr">
         <is>
-          <t>GHG_Method_v7_0.md; CAVEATS v2.8</t>
+          <t>Methods, chapter Emissions; CAVEATS v2.8</t>
         </is>
       </c>
       <c r="K61" s="48" t="inlineStr">
@@ -6148,6 +6439,11 @@
       <c r="R61" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S61" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -6226,6 +6522,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S62" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="76.5" customHeight="1">
       <c r="A63" s="48" t="inlineStr">
@@ -6260,7 +6561,7 @@
       </c>
       <c r="G63" s="48" t="inlineStr">
         <is>
-          <t>Legacy F5b-c averages the after-tax price of each fuel over sectors with each scenario's own consumption of the year (a unit value) and reports the policy / baseline ratio and an index 2022 = 100 as price changes (Egypt 2030: gas +71%, oil +104%). A shift of consumption between sectors with different prices moves the "price change" with no price moving. Survey v4.15: coal and gas are averaged over power generation, residential and the 8 industry subsectors with baseline quantities (a Laspeyres index), electricity with each scenario's own consumption, oil products are single prices. v4.15 replicates legacy as the default (Settings C54 Legacy*; pav.leg, pav.lidx, pav.idx), the MVP's Laspeyres index over all final uses as the option.</t>
+          <t>Legacy F5b-c averages the after-tax price of each fuel over sectors with each scenario's own consumption of the year (a unit value) and reports the policy / baseline ratio and an index 2022 = 100 as price changes (Egypt 2030: gas +71%, oil +104%). A shift of consumption between sectors with different prices moves the "price change" with no price moving. Survey v4.15: coal and gas are averaged over power generation, residential and the 8 industry subsectors with baseline quantities (a Laspeyres index), electricity with each scenario's own consumption, oil products are single prices. v4.15 replicates legacy as the default (Settings C54 Legacy*; pav.leg, pav.lidx, pav.idx), the prototype's Laspeyres index over all final uses as the option.</t>
         </is>
       </c>
       <c r="H63" s="48" t="n"/>
@@ -6271,7 +6572,7 @@
       </c>
       <c r="J63" s="48" t="inlineStr">
         <is>
-          <t>Reviews_and_Surveys_v7_0.md (section Downstream_Survey) F5; PriceProjection_Method</t>
+          <t>Reviews_and_Surveys.md (section Downstream_Survey) F5; PriceProjection_Method</t>
         </is>
       </c>
       <c r="K63" s="48" t="inlineStr">
@@ -6310,6 +6611,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S63" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="102" customHeight="1">
       <c r="A64" s="48" t="inlineStr">
@@ -6344,7 +6650,7 @@
       </c>
       <c r="G64" s="48" t="inlineStr">
         <is>
-          <t>Legacy row 7534 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the MVP calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
+          <t>Legacy row 7534 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the prototype calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
         </is>
       </c>
       <c r="H64" s="48" t="n"/>
@@ -6355,7 +6661,7 @@
       </c>
       <c r="J64" s="48" t="inlineStr">
         <is>
-          <t>ResultsSections_Method_v7_0.md; CO2Calibration_Method_v7_0.md; CAVEATS v4.11</t>
+          <t>Methods, chapter Macro and results; Methods, chapter Emissions; CAVEATS v4.11</t>
         </is>
       </c>
       <c r="K64" s="48" t="inlineStr">
@@ -6390,6 +6696,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S64" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="76.5" customHeight="1">
       <c r="A65" s="48" t="inlineStr">
@@ -6435,7 +6746,7 @@
       </c>
       <c r="J65" s="48" t="inlineStr">
         <is>
-          <t>legacy_comparison_v6_4.md; PriceProjection_Method_v7_0.md A7</t>
+          <t>legacy_comparison_v6_4.md; Methods, chapter Prices A7</t>
         </is>
       </c>
       <c r="K65" s="48" t="inlineStr">
@@ -6468,6 +6779,11 @@
       <c r="R65" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S65" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -6546,6 +6862,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S66" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="76.5" customHeight="1">
       <c r="A67" s="48" t="inlineStr">
@@ -6591,7 +6912,7 @@
       </c>
       <c r="J67" s="48" t="inlineStr">
         <is>
-          <t>GHG_Method_v7_0.md (Data); CAVEATS v2.8</t>
+          <t>Methods, chapter Emissions (Data); CAVEATS v2.8</t>
         </is>
       </c>
       <c r="K67" s="48" t="inlineStr">
@@ -6626,6 +6947,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S67" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="63.75" customHeight="1">
       <c r="A68" s="48" t="inlineStr">
@@ -6671,7 +6997,7 @@
       </c>
       <c r="J68" s="48" t="inlineStr">
         <is>
-          <t>CO2Calibration_Method_v7_0.md; CAVEATS v3.2</t>
+          <t>Methods, chapter Emissions; CAVEATS v3.2</t>
         </is>
       </c>
       <c r="K68" s="48" t="inlineStr">
@@ -6706,6 +7032,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S68" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: a prototype issue resolved in the prototype, not a legacy cell: nothing to confirm in 465</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="51" customHeight="1">
       <c r="A69" s="48" t="inlineStr">
@@ -6740,7 +7071,7 @@
       </c>
       <c r="G69" s="48" t="inlineStr">
         <is>
-          <t>Legacy domestic aviation burns jet fuel (707 ktoe in 2022). Since v3.11 the MVP has the fuel jfu (aviation only, kerosene price build-up, legacy EF row 1011, kerosene carbon-tax coverage switch); the legacy comparison includes it.</t>
+          <t>Legacy domestic aviation burns jet fuel (707 ktoe in 2022). Since v3.11 the prototype has the fuel jfu (aviation only, kerosene price build-up, legacy EF row 1011, kerosene carbon-tax coverage switch); the legacy comparison includes it.</t>
         </is>
       </c>
       <c r="H69" s="48" t="n"/>
@@ -6751,7 +7082,7 @@
       </c>
       <c r="J69" s="48" t="inlineStr">
         <is>
-          <t>Reviews_and_Surveys_v7_0.md (section Sector_Equations_Survey) D1; CAVEATS v3.11</t>
+          <t>Reviews_and_Surveys.md (section Sector_Equations_Survey) D1; CAVEATS v3.11</t>
         </is>
       </c>
       <c r="K69" s="48" t="inlineStr">
@@ -6790,6 +7121,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S69" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="76.5" customHeight="1">
       <c r="A70" s="48" t="inlineStr">
@@ -6835,7 +7171,7 @@
       </c>
       <c r="J70" s="48" t="inlineStr">
         <is>
-          <t>Reviews_and_Surveys_v7_0.md (section Sector_Equations_Survey) D2; LegacyDiff</t>
+          <t>Reviews_and_Surveys.md (section Sector_Equations_Survey) D2; LegacyDiff</t>
         </is>
       </c>
       <c r="K70" s="48" t="inlineStr">
@@ -6870,6 +7206,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S70" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="51" customHeight="1">
       <c r="A71" s="48" t="inlineStr">
@@ -6915,7 +7256,7 @@
       </c>
       <c r="J71" s="48" t="inlineStr">
         <is>
-          <t>Transport_vs_Legacy_v7_0.md</t>
+          <t>Methods, chapter Transport</t>
         </is>
       </c>
       <c r="K71" s="48" t="inlineStr">
@@ -6950,6 +7291,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S71" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="89.25" customHeight="1">
       <c r="A72" s="48" t="inlineStr">
@@ -6995,7 +7341,7 @@
       </c>
       <c r="J72" s="48" t="inlineStr">
         <is>
-          <t>AirPollutants_Method_v7_0.md; CAVEATS v3.12</t>
+          <t>Methods, chapter Emissions; CAVEATS v3.12</t>
         </is>
       </c>
       <c r="K72" s="48" t="inlineStr">
@@ -7030,6 +7376,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S72" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="102" customHeight="1">
       <c r="A73" s="48" t="inlineStr">
@@ -7110,6 +7461,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S73" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="76.5" customHeight="1">
       <c r="A74" s="48" t="inlineStr">
@@ -7144,7 +7500,7 @@
       </c>
       <c r="G74" s="48" t="inlineStr">
         <is>
-          <t>Legacy's effective carbon rate (row 16662) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The MVP replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
+          <t>Legacy's effective carbon rate (row 16662) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The prototype replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
         </is>
       </c>
       <c r="H74" s="48" t="n"/>
@@ -7155,7 +7511,7 @@
       </c>
       <c r="J74" s="48" t="inlineStr">
         <is>
-          <t>ResultsSections_Method_v7_0.md; CAVEATS v3.15</t>
+          <t>Methods, chapter Macro and results; CAVEATS v3.15</t>
         </is>
       </c>
       <c r="K74" s="48" t="inlineStr">
@@ -7190,6 +7546,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S74" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="63.75" customHeight="1">
       <c r="A75" s="48" t="inlineStr">
@@ -7235,7 +7596,7 @@
       </c>
       <c r="J75" s="48" t="inlineStr">
         <is>
-          <t>ResultsSections_Method_v7_0.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K75" s="48" t="inlineStr">
@@ -7270,6 +7631,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S75" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="25.5" customHeight="1">
       <c r="A76" s="48" t="inlineStr">
@@ -7304,7 +7670,7 @@
       </c>
       <c r="G76" s="48" t="inlineStr">
         <is>
-          <t>Legacy: Industry elasticities (cpat_coded EC_SECTORS)</t>
+          <t>Legacy: Industry elasticities (coded EC_SECTORS)</t>
         </is>
       </c>
       <c r="H76" s="48" t="inlineStr">
@@ -7342,6 +7708,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S76" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="51" customHeight="1">
       <c r="A77" s="48" t="inlineStr">
@@ -7418,6 +7789,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S77" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="76.5" customHeight="1">
       <c r="A78" s="48" t="inlineStr">
@@ -7492,6 +7868,11 @@
       <c r="R78" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S78" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -7566,6 +7947,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S79" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="48" t="inlineStr">
@@ -7642,6 +8028,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S80" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="140.25" customHeight="1">
       <c r="A81" s="48" t="inlineStr">
@@ -7718,6 +8109,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S81" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="89.25" customHeight="1">
       <c r="A82" s="48" t="inlineStr">
@@ -7796,6 +8192,11 @@
       <c r="R82" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S82" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -7874,6 +8275,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S83" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="38.25" customHeight="1">
       <c r="A84" s="48" t="inlineStr">
@@ -7954,6 +8360,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S84" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="76.5" customHeight="1">
       <c r="A85" s="48" t="inlineStr">
@@ -8026,6 +8437,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S85" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="25.5" customHeight="1">
       <c r="A86" s="48" t="inlineStr">
@@ -8098,6 +8514,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S86" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="51" customHeight="1">
       <c r="A87" s="48" t="inlineStr">
@@ -8170,6 +8591,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S87" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="89.25" customHeight="1">
       <c r="A88" s="48" t="inlineStr">
@@ -8246,6 +8672,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S88" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="25.5" customHeight="1">
       <c r="A89" s="48" t="inlineStr">
@@ -8280,7 +8711,7 @@
       </c>
       <c r="G89" s="48" t="inlineStr">
         <is>
-          <t>Legacy: cpat_coded applies no inflation conversion</t>
+          <t>Legacy: coded applies no inflation conversion</t>
         </is>
       </c>
       <c r="H89" s="48" t="inlineStr">
@@ -8318,6 +8749,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S89" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="51" customHeight="1">
       <c r="A90" s="48" t="inlineStr">
@@ -8394,6 +8830,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S90" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="25.5" customHeight="1">
       <c r="A91" s="48" t="inlineStr">
@@ -8470,6 +8911,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S91" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="48" t="inlineStr">
@@ -8544,6 +8990,11 @@
       <c r="R92" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S92" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -8622,6 +9073,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S93" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="76.5" customHeight="1">
       <c r="A94" s="48" t="inlineStr">
@@ -8700,6 +9156,11 @@
       <c r="R94" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S94" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -8778,6 +9239,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S95" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="38.25" customHeight="1">
       <c r="A96" s="48" t="inlineStr">
@@ -8856,6 +9322,11 @@
       <c r="R96" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S96" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -8934,6 +9405,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S97" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="63.75" customHeight="1">
       <c r="A98" s="48" t="inlineStr">
@@ -9010,6 +9486,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S98" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="51" customHeight="1">
       <c r="A99" s="48" t="inlineStr">
@@ -9082,6 +9563,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S99" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="38.25" customHeight="1">
       <c r="A100" s="48" t="inlineStr">
@@ -9162,6 +9648,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S100" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="127.5" customHeight="1">
       <c r="A101" s="48" t="inlineStr">
@@ -9242,6 +9733,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S101" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="191.25" customHeight="1">
       <c r="A102" s="48" t="inlineStr">
@@ -9320,6 +9816,11 @@
       <c r="R102" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S102" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -9398,6 +9899,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S103" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="63.75" customHeight="1">
       <c r="A104" s="48" t="inlineStr">
@@ -9478,6 +9984,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S104" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="51" customHeight="1">
       <c r="A105" s="48" t="inlineStr">
@@ -9554,6 +10065,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S105" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="102" customHeight="1">
       <c r="A106" s="48" t="inlineStr">
@@ -9632,6 +10148,11 @@
       <c r="R106" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S106" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -9710,6 +10231,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S107" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="51" customHeight="1">
       <c r="A108" s="48" t="inlineStr">
@@ -9782,6 +10308,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S108" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="89.25" customHeight="1">
       <c r="A109" s="48" t="inlineStr">
@@ -9858,6 +10389,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S109" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="25.5" customHeight="1">
       <c r="A110" s="48" t="inlineStr">
@@ -9934,6 +10470,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S110" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="76.5" customHeight="1">
       <c r="A111" s="48" t="inlineStr">
@@ -10010,6 +10551,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S111" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="112" ht="51" customHeight="1">
       <c r="A112" s="48" t="inlineStr">
@@ -10086,6 +10632,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S112" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="114.75" customHeight="1">
       <c r="A113" s="48" t="inlineStr">
@@ -10164,6 +10715,11 @@
       <c r="R113" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S113" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -10238,6 +10794,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S114" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="114.75" customHeight="1">
       <c r="A115" s="48" t="inlineStr">
@@ -10267,7 +10828,7 @@
       </c>
       <c r="F115" s="48" t="inlineStr">
         <is>
-          <t>Departs from legacy: Section 5b of every scenario group, every row live (Transport_Workbook_Notes_v7_0.md); TrModel default Elasticity, Engineer by switch; the 17 legacy bugs of Transport_vs_Legacy_v7_0.md section 3 fixed (B1-B23)</t>
+          <t>Departs from legacy: Section 5b of every scenario group, every row live (Methods, chapter Transport); TrModel default Elasticity, Engineer by switch; the 17 legacy bugs of Methods, chapter Transport section 3 fixed (B1-B23)</t>
         </is>
       </c>
       <c r="G115" s="48" t="inlineStr">
@@ -10277,7 +10838,7 @@
       </c>
       <c r="H115" s="48" t="inlineStr">
         <is>
-          <t>None by default; with Engineer: road fuel use and EV shares as in Transport_vs_Legacy_v7_0.md section 4</t>
+          <t>None by default; with Engineer: road fuel use and EV shares as in Methods, chapter Transport section 4</t>
         </is>
       </c>
       <c r="I115" s="48" t="n"/>
@@ -10314,6 +10875,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S115" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="165.75" customHeight="1">
       <c r="A116" s="48" t="inlineStr">
@@ -10386,6 +10952,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S116" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="204" customHeight="1">
       <c r="A117" s="48" t="inlineStr">
@@ -10458,6 +11029,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S117" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="63.75" customHeight="1">
       <c r="A118" s="48" t="inlineStr">
@@ -10532,6 +11108,11 @@
       <c r="R118" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S118" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>
@@ -10606,6 +11187,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S119" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="51" customHeight="1">
       <c r="A120" s="48" t="inlineStr">
@@ -10678,6 +11264,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S120" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="51" customHeight="1">
       <c r="A121" s="48" t="inlineStr">
@@ -10712,7 +11303,7 @@
       </c>
       <c r="G121" s="48" t="inlineStr">
         <is>
-          <t>The workbook and its VBA project were generated and tested without Excel (LibreOffice). Open it, enable macros and run CheckBatchRun once; if Excel rejects the VBA project, import CPATScenarios_v7_0.bas.</t>
+          <t>The workbook and its VBA project were generated and tested without Excel (LibreOffice). Open it, enable macros and run CheckBatchRun once; if Excel rejects the VBA project, import CPATScenarios.bas.</t>
         </is>
       </c>
       <c r="H121" s="48" t="n"/>
@@ -10723,7 +11314,7 @@
       </c>
       <c r="J121" s="48" t="inlineStr">
         <is>
-          <t>TODO; Scenarios_Method_v7_0.md</t>
+          <t>TODO; Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K121" s="48" t="inlineStr">
@@ -10754,6 +11345,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S121" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="25.5" customHeight="1">
       <c r="A122" s="48" t="inlineStr">
@@ -10826,6 +11422,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S122" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="38.25" customHeight="1">
       <c r="A123" s="48" t="inlineStr">
@@ -10902,6 +11503,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S123" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="25.5" customHeight="1">
       <c r="A124" s="48" t="inlineStr">
@@ -10978,6 +11584,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S124" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="38.25" customHeight="1">
       <c r="A125" s="48" t="inlineStr">
@@ -11050,6 +11661,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S125" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="63.75" customHeight="1">
       <c r="A126" s="48" t="inlineStr">
@@ -11091,7 +11707,7 @@
       <c r="I126" s="48" t="n"/>
       <c r="J126" s="48" t="inlineStr">
         <is>
-          <t>check report section 1; PowerModel_Method_v7_0.md</t>
+          <t>check report section 1; Methods, chapter Power</t>
         </is>
       </c>
       <c r="K126" s="48" t="inlineStr">
@@ -11122,6 +11738,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S126" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="38.25" customHeight="1">
       <c r="A127" s="48" t="inlineStr">
@@ -11194,6 +11815,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S127" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="25.5" customHeight="1">
       <c r="A128" s="48" t="inlineStr">
@@ -11270,6 +11896,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S128" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="38.25" customHeight="1">
       <c r="A129" s="48" t="inlineStr">
@@ -11346,6 +11977,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S129" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="38.25" customHeight="1">
       <c r="A130" s="48" t="inlineStr">
@@ -11422,6 +12058,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S130" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="38.25" customHeight="1">
       <c r="A131" s="48" t="inlineStr">
@@ -11494,6 +12135,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S131" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="51" customHeight="1">
       <c r="A132" s="48" t="inlineStr">
@@ -11539,7 +12185,7 @@
       </c>
       <c r="J132" s="48" t="inlineStr">
         <is>
-          <t>CAVEATS v3.6 (variants entry); check_quick_v7_0.py</t>
+          <t>CAVEATS v3.6 (variants entry); check_quick.py</t>
         </is>
       </c>
       <c r="K132" s="48" t="inlineStr">
@@ -11574,6 +12220,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S132" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: a prototype issue resolved in the prototype, not a legacy cell: nothing to confirm in 465</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="76.5" customHeight="1">
       <c r="A133" s="48" t="inlineStr">
@@ -11619,7 +12270,7 @@
       </c>
       <c r="J133" s="48" t="inlineStr">
         <is>
-          <t>ets_goalseek_v7_0.py; CAVEATS v3.7</t>
+          <t>ets_goalseek.py; CAVEATS v3.7</t>
         </is>
       </c>
       <c r="K133" s="48" t="inlineStr">
@@ -11654,6 +12305,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S133" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="51" customHeight="1">
       <c r="A134" s="48" t="inlineStr">
@@ -11734,6 +12390,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S134" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="48" t="inlineStr">
@@ -11773,7 +12434,7 @@
       </c>
       <c r="H135" s="48" t="inlineStr">
         <is>
-          <t>Reported energy trade balance only (Egypt: about 0.6 bn USD a year). MVP: Fixed in v4.6: coal at the coal price (data step Inputs_macro, from Balances and the international prices).</t>
+          <t>Reported energy trade balance only (Egypt: about 0.6 bn USD a year). prototype: Fixed in v4.6: coal at the coal price (data step Inputs_macro, from Balances and the international prices).</t>
         </is>
       </c>
       <c r="I135" s="48" t="inlineStr">
@@ -11806,7 +12467,11 @@
           <t>4.6</t>
         </is>
       </c>
-      <c r="O135" s="53" t="inlineStr"/>
+      <c r="O135" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P135" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -11818,6 +12483,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S135" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="48" t="inlineStr">
@@ -11857,7 +12527,7 @@
       </c>
       <c r="H136" s="48" t="inlineStr">
         <is>
-          <t>Power: solar fixed O&amp;M of Egypt 11.831 instead of 15 $/kW/y (other renewables: no country data). MVP: Fixed in v4.10: every type takes the country value where it exists, else the world value (Egypt: solar fixed O&amp;M 11.831 $/kW/y).</t>
+          <t>Power: solar fixed O&amp;M of Egypt 11.831 instead of 15 $/kW/y (other renewables: no country data). prototype: Fixed in v4.10: every type takes the country value where it exists, else the world value (Egypt: solar fixed O&amp;M 11.831 $/kW/y).</t>
         </is>
       </c>
       <c r="I136" s="48" t="inlineStr">
@@ -11906,6 +12576,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S136" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="48" t="inlineStr">
@@ -11945,7 +12620,7 @@
       </c>
       <c r="H137" s="48" t="inlineStr">
         <is>
-          <t>Power: actual capacity factors where data exist (Egypt: all types with capacity), base capacities change. MVP: Fixed in v4.10: installed capacity of the base year from Power rows 358-1635 (all year columns); the actual capacity factor (output / capacity) is used inside the CFOverride bounds, else the studies value (Egypt: gas 0.385, wind 0.436, solar 0.347, hydro 0.592; base-year gas capacity 52 GW instead of 35).</t>
+          <t>Power: actual capacity factors where data exist (Egypt: all types with capacity), base capacities change. prototype: Fixed in v4.10: installed capacity of the base year from Power rows 358-1635 (all year columns); the actual capacity factor (output / capacity) is used inside the CFOverride bounds, else the studies value (Egypt: gas 0.385, wind 0.436, solar 0.347, hydro 0.592; base-year gas capacity 52 GW instead of 35).</t>
         </is>
       </c>
       <c r="I137" s="48" t="inlineStr">
@@ -11994,6 +12669,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S137" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="48" t="inlineStr">
@@ -12033,7 +12713,7 @@
       </c>
       <c r="H138" s="48" t="inlineStr">
         <is>
-          <t>Power: hydro investment from NewInvHydYear (2030) unless hydro is above 50%. MVP: Fixed in v4.10: the base year only when the hydro generation share is above HydInvShare (50%), else NewInvHydYear (Egypt: 2030).</t>
+          <t>Power: hydro investment from NewInvHydYear (2030) unless hydro is above 50%. prototype: Fixed in v4.10: the base year only when the hydro generation share is above HydInvShare (50%), else NewInvHydYear (Egypt: 2030).</t>
         </is>
       </c>
       <c r="I138" s="48" t="inlineStr">
@@ -12084,6 +12764,11 @@
       <c r="R138" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S138" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
         </is>
       </c>
     </row>
@@ -12125,7 +12810,7 @@
       </c>
       <c r="H139" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt. MVP: Fixed in v4.10: the country rows are looked up in the country block (Power rows 112-294) first; no effect for Egypt.</t>
+          <t>None for Egypt. prototype: Fixed in v4.10: the country rows are looked up in the country block (Power rows 112-294) first; no effect for Egypt.</t>
         </is>
       </c>
       <c r="I139" s="48" t="inlineStr">
@@ -12174,6 +12859,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S139" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="48" t="inlineStr">
@@ -12213,7 +12903,7 @@
       </c>
       <c r="H140" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt. MVP: Fixed in v4.10: such countries take the default WACC (as countries missing from CoC), flagged on Inputs (PsCoCData); no effect for Egypt.</t>
+          <t>None for Egypt. prototype: Fixed in v4.10: such countries take the default WACC (as countries missing from CoC), flagged on Inputs (PsCoCData); no effect for Egypt.</t>
         </is>
       </c>
       <c r="I140" s="48" t="inlineStr">
@@ -12262,6 +12952,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S140" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: still Sri Lanka, now an explicit Default row 198 (=row 172); no flag, as the user noted</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="48" t="inlineStr">
@@ -12301,7 +12996,7 @@
       </c>
       <c r="H141" s="48" t="inlineStr">
         <is>
-          <t>New ETS scenarios: the quick estimate meets the cap (legacy relies on the VBA goal seek). MVP: Fixed (v1.02; bug by user decision 2026-10-18, was LegacyDiff row 6): the fast estimate in log form, LN(cap / baseline) / (semi-elasticity x effectiveness x volatility adjustment); the build stores it (no goal seek).</t>
+          <t>New ETS scenarios: the quick estimate meets the cap (legacy relies on the VBA goal seek). prototype: Fixed (v1.02; bug by user decision 2026-10-18, was LegacyDiff row 6): the fast estimate in log form, LN(cap / baseline) / (semi-elasticity x effectiveness x volatility adjustment); the build stores it (no goal seek).</t>
         </is>
       </c>
       <c r="I141" s="48" t="inlineStr">
@@ -12334,7 +13029,11 @@
           <t>1.02</t>
         </is>
       </c>
-      <c r="O141" s="53" t="inlineStr"/>
+      <c r="O141" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P141" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12346,6 +13045,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S141" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed: log form as planned, plus a guard for a zero semi-elasticity</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="48" t="inlineStr">
@@ -12385,7 +13089,7 @@
       </c>
       <c r="H142" s="48" t="inlineStr">
         <is>
-          <t>Local pollutants of services, rail and industry no longer zero. MVP: Fixed (v2.9; bug by user decision 2026-10-18, was issue I27 and LegacyDiff row 49): each subsector takes the GAINS subsector of its CH4 factor (services as residential, rail as road, industry as manufacturing).</t>
+          <t>Local pollutants of services, rail and industry no longer zero. prototype: Fixed (v2.9; bug by user decision 2026-10-18, was issue I27 and LegacyDiff row 49): each subsector takes the GAINS subsector of its CH4 factor (services as residential, rail as road, industry as manufacturing).</t>
         </is>
       </c>
       <c r="I142" s="48" t="inlineStr">
@@ -12418,7 +13122,11 @@
           <t>2.9</t>
         </is>
       </c>
-      <c r="O142" s="53" t="inlineStr"/>
+      <c r="O142" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P142" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12430,6 +13138,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S142" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="48" t="inlineStr">
@@ -12469,7 +13182,7 @@
       </c>
       <c r="H143" s="48" t="inlineStr">
         <is>
-          <t>Egypt 2022: NOx +11%, PM2.5 +5%, combustion CH4 +20%. MVP: Fixed (v4.12; bug by user decision 2026-10-18, was issue I35): the nearest GAINS match (LPG: natural gas of the same GAINS subsector; food &amp; forestry: construction, off-road machinery; biomass: residential; else manufacturing). A fuel the subsector has factors for keeps a missing pollutant at 0 (GAINS omits zero factors).</t>
+          <t>Egypt 2022: NOx +11%, PM2.5 +5%, combustion CH4 +20%. prototype: Fixed (v4.12; bug by user decision 2026-10-18, was issue I35): the nearest GAINS match (LPG: natural gas of the same GAINS subsector; food &amp; forestry: construction, off-road machinery; biomass: residential; else manufacturing). A fuel the subsector has factors for keeps a missing pollutant at 0 (GAINS omits zero factors).</t>
         </is>
       </c>
       <c r="I143" s="48" t="inlineStr">
@@ -12502,7 +13215,11 @@
           <t>4.12</t>
         </is>
       </c>
-      <c r="O143" s="53" t="inlineStr"/>
+      <c r="O143" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P143" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12514,6 +13231,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S143" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="48" t="inlineStr">
@@ -12553,7 +13275,7 @@
       </c>
       <c r="H144" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt (VAT 0 on oil). MVP: Fixed (v4.12): VAT = (supply cost + taxes) x rate x share, consistent with the retail price.</t>
+          <t>None for Egypt (VAT 0 on oil). prototype: Fixed (v4.12): VAT = (supply cost + taxes) x rate x share, consistent with the retail price.</t>
         </is>
       </c>
       <c r="I144" s="48" t="inlineStr">
@@ -12586,7 +13308,11 @@
           <t>4.12</t>
         </is>
       </c>
-      <c r="O144" s="53" t="inlineStr"/>
+      <c r="O144" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P144" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12598,6 +13324,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S144" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="48" t="inlineStr">
@@ -12637,7 +13368,7 @@
       </c>
       <c r="H145" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt. MVP: Fixed (v4.12): ETS prices grow with ExistingETSGrowth, carbon tax rates with ExistingCTGrowth.</t>
+          <t>None for Egypt. prototype: Fixed (v4.12): ETS prices grow with ExistingETSGrowth, carbon tax rates with ExistingCTGrowth.</t>
         </is>
       </c>
       <c r="I145" s="48" t="inlineStr">
@@ -12670,7 +13401,11 @@
           <t>4.12</t>
         </is>
       </c>
-      <c r="O145" s="53" t="inlineStr"/>
+      <c r="O145" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P145" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12682,6 +13417,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S145" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="48" t="inlineStr">
@@ -12721,7 +13461,7 @@
       </c>
       <c r="H146" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt. MVP: Fixed (v4.12): every fuel takes rate x sector coverage x fuel coverage, the fuel rate only where the country has one and no single price.</t>
+          <t>None for Egypt. prototype: Fixed (v4.12): every fuel takes rate x sector coverage x fuel coverage, the fuel rate only where the country has one and no single price.</t>
         </is>
       </c>
       <c r="I146" s="48" t="inlineStr">
@@ -12754,7 +13494,11 @@
           <t>4.12</t>
         </is>
       </c>
-      <c r="O146" s="53" t="inlineStr"/>
+      <c r="O146" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P146" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12766,6 +13510,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S146" s="53" t="inlineStr">
+        <is>
+          <t>Not fixed: L1760:AE1762 are unchanged from 456 (still rate x rate x coverage)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="48" t="inlineStr">
@@ -12805,7 +13554,7 @@
       </c>
       <c r="H147" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt. MVP: Fixed (v4.12): each scheme is looked up in its whole block (Inputs_ecp columns K:L).</t>
+          <t>None for Egypt. prototype: Fixed (v4.12): each scheme is looked up in its whole block (Inputs_ecp columns K:L).</t>
         </is>
       </c>
       <c r="I147" s="48" t="inlineStr">
@@ -12838,7 +13587,11 @@
           <t>4.12</t>
         </is>
       </c>
-      <c r="O147" s="53" t="inlineStr"/>
+      <c r="O147" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P147" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12850,6 +13603,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S147" s="53" t="inlineStr">
+        <is>
+          <t>Not fixed: J1741:J1749 still MATCH on ECP!$E$133:$E$403, while the ECP block still runs to row 425 (Ukraine, Uruguay, United Kingdom miss out)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="48" t="inlineStr">
@@ -12889,7 +13647,7 @@
       </c>
       <c r="H148" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt. MVP: Fixed (v4.12): other oil products take the industry coverage of both schemes.</t>
+          <t>None for Egypt. prototype: Fixed (v4.12): other oil products take the industry coverage of both schemes.</t>
         </is>
       </c>
       <c r="I148" s="48" t="inlineStr">
@@ -12922,7 +13680,11 @@
           <t>4.12</t>
         </is>
       </c>
-      <c r="O148" s="53" t="inlineStr"/>
+      <c r="O148" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P148" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -12934,6 +13696,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S148" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="48" t="inlineStr">
@@ -12973,7 +13740,7 @@
       </c>
       <c r="H149" s="48" t="inlineStr">
         <is>
-          <t>None for Egypt. MVP: Fixed (v4.12): the coverage of the year (the same from 2026, coverage being held after the last data year).</t>
+          <t>None for Egypt. prototype: Fixed (v4.12): the coverage of the year (the same from 2026, coverage being held after the last data year).</t>
         </is>
       </c>
       <c r="I149" s="48" t="inlineStr">
@@ -13006,7 +13773,11 @@
           <t>4.12</t>
         </is>
       </c>
-      <c r="O149" s="53" t="inlineStr"/>
+      <c r="O149" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P149" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13018,6 +13789,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S149" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="48" t="inlineStr">
@@ -13057,7 +13833,7 @@
       </c>
       <c r="H150" s="48" t="inlineStr">
         <is>
-          <t>None while the input is 0. MVP: Fixed (v4.13): other energy use takes the industrial gain on every fuel.</t>
+          <t>None while the input is 0. prototype: Fixed (v4.13): other energy use takes the industrial gain on every fuel.</t>
         </is>
       </c>
       <c r="I150" s="48" t="inlineStr">
@@ -13090,7 +13866,11 @@
           <t>4.13</t>
         </is>
       </c>
-      <c r="O150" s="53" t="inlineStr"/>
+      <c r="O150" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P150" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13102,6 +13882,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S150" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="48" t="inlineStr">
@@ -13141,7 +13926,7 @@
       </c>
       <c r="H151" s="48" t="inlineStr">
         <is>
-          <t>Egypt (legacy inputs, v6.2 estimate): capacity 77.9 GW in 2030 and 109.6 GW in 2040 against legacy 75.2 and 107.3 (next year read directly: 77.3, 109.5); the need follows the 2023-2024 demand shock (4.3 GW in 2024, 0 in 2025). MVP: Fixed (v4.14; bug by user decision 2026-10-18, was issue I8). v6.2 (user 2026-10-20): next year's required generation is estimated as this year's x (1 + growth from last year to this year), so neither legacy nor the MVP reads a later year and the GDP feedback (last year's effect) cannot loop; legacy kept as a switch in power_model_ref only.</t>
+          <t>Egypt (legacy inputs, v6.2 estimate): capacity 77.9 GW in 2030 and 109.6 GW in 2040 against legacy 75.2 and 107.3 (next year read directly: 77.3, 109.5); the need follows the 2023-2024 demand shock (4.3 GW in 2024, 0 in 2025). prototype: Fixed (v4.14; bug by user decision 2026-10-18, was issue I8). v6.2 (user 2026-10-20): next year's required generation is estimated as this year's x (1 + growth from last year to this year), so neither legacy nor the prototype reads a later year and the GDP feedback (last year's effect) cannot loop; legacy kept as a switch in power_model_ref only.</t>
         </is>
       </c>
       <c r="I151" s="48" t="inlineStr">
@@ -13190,6 +13975,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S151" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="48" t="inlineStr">
@@ -13229,7 +14019,7 @@
       </c>
       <c r="H152" s="48" t="inlineStr">
         <is>
-          <t>The GDP effect of every impulse comes one year early. MVP: Fixed (v4.15): lag 0 in the impulse year (multiplier 0), lag 1 the year after.</t>
+          <t>The GDP effect of every impulse comes one year early. prototype: Fixed (v4.15): lag 0 in the impulse year (multiplier 0), lag 1 the year after.</t>
         </is>
       </c>
       <c r="I152" s="48" t="inlineStr">
@@ -13262,7 +14052,11 @@
           <t>4.15</t>
         </is>
       </c>
-      <c r="O152" s="53" t="inlineStr"/>
+      <c r="O152" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P152" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13274,6 +14068,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S152" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="48" t="inlineStr">
@@ -13313,7 +14112,7 @@
       </c>
       <c r="H153" s="48" t="inlineStr">
         <is>
-          <t>The first year's revenue has no contractionary effect (Egypt about 3e-5 of GDP). MVP: Fixed: every cohort counts its revenue use (share -1).</t>
+          <t>The first year's revenue has no contractionary effect (Egypt about 3e-5 of GDP). prototype: Fixed: every cohort counts its revenue use (share -1).</t>
         </is>
       </c>
       <c r="I153" s="48" t="inlineStr">
@@ -13342,7 +14141,11 @@
         </is>
       </c>
       <c r="N153" s="53" t="inlineStr"/>
-      <c r="O153" s="53" t="inlineStr"/>
+      <c r="O153" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P153" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13354,6 +14157,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S153" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="48" t="inlineStr">
@@ -13393,7 +14201,7 @@
       </c>
       <c r="H154" s="48" t="inlineStr">
         <is>
-          <t>Gas industry excise revenue is wrong wherever coal and gas excises differ (none for Egypt). MVP: Fixed: each subsector and fuel takes its own excise and use (rex, v4.15).</t>
+          <t>Gas industry excise revenue is wrong wherever coal and gas excises differ (none for Egypt). prototype: Fixed: each subsector and fuel takes its own excise and use (rex, v4.15).</t>
         </is>
       </c>
       <c r="I154" s="48" t="inlineStr">
@@ -13426,7 +14234,11 @@
           <t>4.15</t>
         </is>
       </c>
-      <c r="O154" s="53" t="inlineStr"/>
+      <c r="O154" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P154" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13438,6 +14250,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S154" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="48" t="inlineStr">
@@ -13477,7 +14294,7 @@
       </c>
       <c r="H155" s="48" t="inlineStr">
         <is>
-          <t>Biomass taxes, subsidies and VAT are 0. MVP: Fixed: fuel use x PJ/ktoe x rate for every fuel.</t>
+          <t>Biomass taxes, subsidies and VAT are 0. prototype: Fixed: fuel use x PJ/ktoe x rate for every fuel.</t>
         </is>
       </c>
       <c r="I155" s="48" t="inlineStr">
@@ -13506,7 +14323,11 @@
         </is>
       </c>
       <c r="N155" s="53" t="inlineStr"/>
-      <c r="O155" s="53" t="inlineStr"/>
+      <c r="O155" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P155" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13520,6 +14341,11 @@
       <c r="R155" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S155" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -13561,7 +14387,7 @@
       </c>
       <c r="H156" s="48" t="inlineStr">
         <is>
-          <t>Revenue of the year uses next year's rate. MVP: Fixed: the year's own column.</t>
+          <t>Revenue of the year uses next year's rate. prototype: Fixed: the year's own column.</t>
         </is>
       </c>
       <c r="I156" s="48" t="inlineStr">
@@ -13590,7 +14416,11 @@
         </is>
       </c>
       <c r="N156" s="53" t="inlineStr"/>
-      <c r="O156" s="53" t="inlineStr"/>
+      <c r="O156" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P156" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13604,6 +14434,11 @@
       <c r="R156" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S156" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -13645,7 +14480,7 @@
       </c>
       <c r="H157" s="48" t="inlineStr">
         <is>
-          <t>Coverage shares of gas industry and kerosene power are wrong (info rows). MVP: Fixed: coverage by subsector and fuel (ctxnew, covct).</t>
+          <t>Coverage shares of gas industry and kerosene power are wrong (info rows). prototype: Fixed: coverage by subsector and fuel (ctxnew, covct).</t>
         </is>
       </c>
       <c r="I157" s="48" t="inlineStr">
@@ -13674,7 +14509,11 @@
         </is>
       </c>
       <c r="N157" s="53" t="inlineStr"/>
-      <c r="O157" s="53" t="inlineStr"/>
+      <c r="O157" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P157" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13686,6 +14525,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S157" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="48" t="inlineStr">
@@ -13725,7 +14569,7 @@
       </c>
       <c r="H158" s="48" t="inlineStr">
         <is>
-          <t>The excise report is all zeros; revenue by fuel mixes totals. MVP: Fixed: 12d and 12e read the revenue rows (v3.13, v4.15).</t>
+          <t>The excise report is all zeros; revenue by fuel mixes totals. prototype: Fixed: 12d and 12e read the revenue rows (v3.13, v4.15).</t>
         </is>
       </c>
       <c r="I158" s="48" t="inlineStr">
@@ -13758,7 +14602,11 @@
           <t>3.13</t>
         </is>
       </c>
-      <c r="O158" s="53" t="inlineStr"/>
+      <c r="O158" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P158" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13770,6 +14618,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S158" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="48" t="inlineStr">
@@ -13809,7 +14662,7 @@
       </c>
       <c r="H159" s="48" t="inlineStr">
         <is>
-          <t>Estimated multipliers: CIT 0, WAGE = GNFS, a missing country takes its neighbour's. MVP: Fixed (v4.15): CIT and WAGE take the income group, exact match with the income group as fallback, unknown text the income group.</t>
+          <t>Estimated multipliers: CIT 0, WAGE = GNFS, a missing country takes its neighbour's. prototype: Fixed (v4.15): CIT and WAGE take the income group, exact match with the income group as fallback, unknown text the income group.</t>
         </is>
       </c>
       <c r="I159" s="48" t="inlineStr">
@@ -13842,7 +14695,11 @@
           <t>4.15</t>
         </is>
       </c>
-      <c r="O159" s="53" t="inlineStr"/>
+      <c r="O159" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P159" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13854,6 +14711,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S159" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="48" t="inlineStr">
@@ -13893,7 +14755,7 @@
       </c>
       <c r="H160" s="48" t="inlineStr">
         <is>
-          <t>The reported price indices are of the wrong fuels. MVP: Fixed (v4.15): pav.leg and pav.lidx per fuel against scenario 1.</t>
+          <t>The reported price indices are of the wrong fuels. prototype: Fixed (v4.15): pav.leg and pav.lidx per fuel against scenario 1.</t>
         </is>
       </c>
       <c r="I160" s="48" t="inlineStr">
@@ -13926,7 +14788,11 @@
           <t>4.15</t>
         </is>
       </c>
-      <c r="O160" s="53" t="inlineStr"/>
+      <c r="O160" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P160" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -13940,6 +14806,11 @@
       <c r="R160" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S160" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -13981,7 +14852,7 @@
       </c>
       <c r="H161" s="48" t="inlineStr">
         <is>
-          <t>An auctioned share drops to 0 (all free) after the target year. MVP: Fixed (v4.15): the target share is held after the target year.</t>
+          <t>An auctioned share drops to 0 (all free) after the target year. prototype: Fixed (v4.15): the target share is held after the target year.</t>
         </is>
       </c>
       <c r="I161" s="48" t="inlineStr">
@@ -14014,7 +14885,11 @@
           <t>4.15</t>
         </is>
       </c>
-      <c r="O161" s="53" t="inlineStr"/>
+      <c r="O161" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P161" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14026,6 +14901,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S161" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="48" t="inlineStr">
@@ -14065,7 +14945,7 @@
       </c>
       <c r="H162" s="48" t="inlineStr">
         <is>
-          <t>Uncovered industry and transport subsectors pay the permit price; revenue on the whole sector's CO2. MVP: Fixed: coverage, price and revenue by subsector (etsc, v1.07).</t>
+          <t>Uncovered industry and transport subsectors pay the permit price; revenue on the whole sector's CO2. prototype: Fixed: coverage, price and revenue by subsector (etsc, v1.07).</t>
         </is>
       </c>
       <c r="I162" s="48" t="inlineStr">
@@ -14098,7 +14978,11 @@
           <t>1.07</t>
         </is>
       </c>
-      <c r="O162" s="53" t="inlineStr"/>
+      <c r="O162" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P162" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14110,6 +14994,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S162" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="48" t="inlineStr">
@@ -14149,7 +15038,7 @@
       </c>
       <c r="H163" s="48" t="inlineStr">
         <is>
-          <t>The carbon tax outside the ETS is cut by the volatility ratio. MVP: Fixed: the carbon tax path is the MTInputs path; the volatility adjustment acts on the ETS price only.</t>
+          <t>The carbon tax outside the ETS is cut by the volatility ratio. prototype: Fixed: the carbon tax path is the MTInputs path; the volatility adjustment acts on the ETS price only.</t>
         </is>
       </c>
       <c r="I163" s="48" t="inlineStr">
@@ -14178,7 +15067,11 @@
         </is>
       </c>
       <c r="N163" s="53" t="inlineStr"/>
-      <c r="O163" s="53" t="inlineStr"/>
+      <c r="O163" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P163" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14190,6 +15083,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S163" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="48" t="inlineStr">
@@ -14229,7 +15127,7 @@
       </c>
       <c r="H164" s="48" t="inlineStr">
         <is>
-          <t>A consumer subsidy phase-out starts and ends a year late. MVP: Fixed (v4.16): every wedge takes the factor of its year.</t>
+          <t>A consumer subsidy phase-out starts and ends a year late. prototype: Fixed (v4.16): every wedge takes the factor of its year.</t>
         </is>
       </c>
       <c r="I164" s="48" t="inlineStr">
@@ -14262,7 +15160,11 @@
           <t>4.16</t>
         </is>
       </c>
-      <c r="O164" s="53" t="inlineStr"/>
+      <c r="O164" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P164" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14274,6 +15176,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S164" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="48" t="inlineStr">
@@ -14313,7 +15220,7 @@
       </c>
       <c r="H165" s="48" t="inlineStr">
         <is>
-          <t>Residential gas takes the oil producer subsidy. MVP: Fixed (v4.16): producer subsidies by fuel (pros, psf); no price effect in the MVP (issue I49).</t>
+          <t>Residential gas takes the oil producer subsidy. prototype: Fixed (v4.16): producer subsidies by fuel (pros, psf); no price effect in the prototype (issue I49).</t>
         </is>
       </c>
       <c r="I165" s="48" t="inlineStr">
@@ -14346,7 +15253,11 @@
           <t>4.16</t>
         </is>
       </c>
-      <c r="O165" s="53" t="inlineStr"/>
+      <c r="O165" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P165" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14358,6 +15269,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S165" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="48" t="inlineStr">
@@ -14397,7 +15313,7 @@
       </c>
       <c r="H166" s="48" t="inlineStr">
         <is>
-          <t>Electricity producer subsidies fall too fast (compounding) and a year late. MVP: Fixed (v4.16): base value x the factor of the year (fiscal line rpsu; the electricity price effect waits for the power features).</t>
+          <t>Electricity producer subsidies fall too fast (compounding) and a year late. prototype: Fixed (v4.16): base value x the factor of the year (fiscal line rpsu; the electricity price effect waits for the power features).</t>
         </is>
       </c>
       <c r="I166" s="48" t="inlineStr">
@@ -14446,6 +15362,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S166" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed: all three cells as planned</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="48" t="inlineStr">
@@ -14485,7 +15406,7 @@
       </c>
       <c r="H167" s="48" t="inlineStr">
         <is>
-          <t>An electricity subsidy reform follows the price-control timing. MVP: Not built (power parked); to fix with the power features: the consumer factor, one option text.</t>
+          <t>An electricity subsidy reform follows the price-control timing. prototype: Not built (power parked); to fix with the power features: the consumer factor, one option text.</t>
         </is>
       </c>
       <c r="I167" s="48" t="inlineStr">
@@ -14530,6 +15451,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S167" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: the formulas are fixed (O2214); the option text MTInputs!C138 still reads “Exempt/Include*” (plan: “DoNotPhaseOut*/Include”)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="48" t="inlineStr">
@@ -14569,7 +15495,7 @@
       </c>
       <c r="H168" s="48" t="inlineStr">
         <is>
-          <t>Reported electricity consumer subsidies wrong. MVP: Not applicable (info row; the MVP subsidy gap rgap sums both groups).</t>
+          <t>Reported electricity consumer subsidies wrong. prototype: Not applicable (info row; the prototype subsidy gap rgap sums both groups).</t>
         </is>
       </c>
       <c r="I168" s="48" t="inlineStr">
@@ -14598,7 +15524,11 @@
         </is>
       </c>
       <c r="N168" s="53" t="inlineStr"/>
-      <c r="O168" s="53" t="inlineStr"/>
+      <c r="O168" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P168" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14610,6 +15540,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S168" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="48" t="inlineStr">
@@ -14649,7 +15584,7 @@
       </c>
       <c r="H169" s="48" t="inlineStr">
         <is>
-          <t>Manual values ignored. MVP: Not built (Manual inputs to come).</t>
+          <t>Manual values ignored. prototype: Not built (Manual inputs to come).</t>
         </is>
       </c>
       <c r="I169" s="48" t="inlineStr">
@@ -14678,7 +15613,11 @@
         </is>
       </c>
       <c r="N169" s="53" t="inlineStr"/>
-      <c r="O169" s="53" t="inlineStr"/>
+      <c r="O169" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P169" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14692,6 +15631,11 @@
       <c r="R169" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S169" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
         </is>
       </c>
     </row>
@@ -14733,7 +15677,7 @@
       </c>
       <c r="H170" s="48" t="inlineStr">
         <is>
-          <t>Regulation scenarios have no effect at all. MVP: Fixed (v4.16): regulation shadow price = shadow carbon price x the scenario's adjustment x sector coverage.</t>
+          <t>Regulation scenarios have no effect at all. prototype: Fixed (v4.16): regulation shadow price = shadow carbon price x the scenario's adjustment x sector coverage.</t>
         </is>
       </c>
       <c r="I170" s="48" t="inlineStr">
@@ -14766,7 +15710,11 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="O170" s="53" t="inlineStr"/>
+      <c r="O170" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P170" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14778,6 +15726,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S170" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: C2371 fixed as planned; I2403:I2419 (and policy I8719:I8735) dropped the E2189="Yes" condition as well as adding *$F$90: the share now applies whether or not that switch is on; check this is intended</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="48" t="inlineStr">
@@ -14817,7 +15770,7 @@
       </c>
       <c r="H171" s="48" t="inlineStr">
         <is>
-          <t>Economy-wide regulations skip power. MVP: Fixed (v4.16): shpx.pow includes reg.pow.</t>
+          <t>Economy-wide regulations skip power. prototype: Fixed (v4.16): shpx.pow includes reg.pow.</t>
         </is>
       </c>
       <c r="I171" s="48" t="inlineStr">
@@ -14866,6 +15819,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S171" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="48" t="inlineStr">
@@ -14905,7 +15863,7 @@
       </c>
       <c r="H172" s="48" t="inlineStr">
         <is>
-          <t>Coal in road and services takes the residential shadow price (minor). MVP: Fixed: shadow prices by coverage sector x EF (shp).</t>
+          <t>Coal in road and services takes the residential shadow price (minor). prototype: Fixed: shadow prices by coverage sector x EF (shp).</t>
         </is>
       </c>
       <c r="I172" s="48" t="inlineStr">
@@ -14934,7 +15892,11 @@
         </is>
       </c>
       <c r="N172" s="53" t="inlineStr"/>
-      <c r="O172" s="53" t="inlineStr"/>
+      <c r="O172" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P172" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -14946,6 +15908,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S172" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="48" t="inlineStr">
@@ -14985,7 +15952,7 @@
       </c>
       <c r="H173" s="48" t="inlineStr">
         <is>
-          <t>None on values (increment 0 by default); a reader of the row label takes the efficiency term for a trade term. MVP: Fixed in the MVP (v5.1 register; the power-demand efficiency term has its own labelled row, AdditionalEfficiencyPower).</t>
+          <t>None on values (increment 0 by default); a reader of the row label takes the efficiency term for a trade term. prototype: Fixed in the prototype (v5.1 register; the power-demand efficiency term has its own labelled row, AdditionalEfficiencyPower).</t>
         </is>
       </c>
       <c r="I173" s="48" t="inlineStr">
@@ -15036,6 +16003,11 @@
       <c r="R173" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S173" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: rows 3691-3709 and 2827, 2828, 2834 read M2198 and row 3719 was cleared, but P2823:AE2823 (total power demand) and M2836:AE2836 (direct rebound) still read $M3719, now empty, so the additional power-demand efficiency drops out of those rows (same in the policy block, $M10035); point them at $M2198</t>
         </is>
       </c>
     </row>
@@ -15077,7 +16049,7 @@
       </c>
       <c r="H174" s="48" t="inlineStr">
         <is>
-          <t>None on values; formula audits misread the additional-efficiency term as a carbon-price setting. MVP: Fixed in the MVP (v5.1 register; own labels: additional efficiency, shadow prices by coverage sector, fuel names).</t>
+          <t>None on values; formula audits misread the additional-efficiency term as a carbon-price setting. prototype: Fixed in the prototype (v5.1 register; own labels: additional efficiency, shadow prices by coverage sector, fuel names).</t>
         </is>
       </c>
       <c r="I174" s="48" t="inlineStr">
@@ -15110,7 +16082,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="O174" s="53" t="inlineStr"/>
+      <c r="O174" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P174" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15124,6 +16100,11 @@
       <c r="R174" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S174" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15165,7 +16146,7 @@
       </c>
       <c r="H175" s="48" t="inlineStr">
         <is>
-          <t>None (dead calculation); would be wrong if anything used it. MVP: Not built in the MVP (dead memo rows).</t>
+          <t>None (dead calculation); would be wrong if anything used it. prototype: Not built in the prototype (dead memo rows).</t>
         </is>
       </c>
       <c r="I175" s="48" t="inlineStr">
@@ -15194,7 +16175,11 @@
         </is>
       </c>
       <c r="N175" s="53" t="inlineStr"/>
-      <c r="O175" s="53" t="inlineStr"/>
+      <c r="O175" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P175" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15208,6 +16193,11 @@
       <c r="R175" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S175" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15278,7 +16268,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O176" s="53" t="inlineStr"/>
+      <c r="O176" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P176" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15292,6 +16286,11 @@
       <c r="R176" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S176" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15362,7 +16361,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O177" s="53" t="inlineStr"/>
+      <c r="O177" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P177" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15376,6 +16379,11 @@
       <c r="R177" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S177" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15446,7 +16454,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O178" s="53" t="inlineStr"/>
+      <c r="O178" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P178" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15460,6 +16472,11 @@
       <c r="R178" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S178" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15530,7 +16547,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O179" s="53" t="inlineStr"/>
+      <c r="O179" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P179" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15544,6 +16565,11 @@
       <c r="R179" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S179" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15614,7 +16640,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O180" s="53" t="inlineStr"/>
+      <c r="O180" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P180" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15628,6 +16658,11 @@
       <c r="R180" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S180" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15698,7 +16733,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O181" s="53" t="inlineStr"/>
+      <c r="O181" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P181" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15712,6 +16751,11 @@
       <c r="R181" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S181" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15782,7 +16826,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O182" s="53" t="inlineStr"/>
+      <c r="O182" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P182" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15796,6 +16844,11 @@
       <c r="R182" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S182" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15866,7 +16919,11 @@
           <t>4.4</t>
         </is>
       </c>
-      <c r="O183" s="53" t="inlineStr"/>
+      <c r="O183" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P183" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15880,6 +16937,11 @@
       <c r="R183" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S183" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -15922,7 +16984,7 @@
       <c r="H184" s="48" t="n"/>
       <c r="I184" s="48" t="inlineStr">
         <is>
-          <t>Fixed in the MVP (v5.1 register; own labels, rural and urban rows by key; one code oop paired by code).</t>
+          <t>Fixed in the prototype (v5.1 register; own labels, rural and urban rows by key; one code oop paired by code).</t>
         </is>
       </c>
       <c r="J184" s="48" t="inlineStr">
@@ -15950,7 +17012,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="O184" s="53" t="inlineStr"/>
+      <c r="O184" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P184" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -15964,6 +17030,11 @@
       <c r="R184" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S184" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -16042,6 +17113,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S185" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="48" t="inlineStr">
@@ -16118,6 +17194,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S186" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="48" t="inlineStr">
@@ -16194,6 +17275,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S187" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="48" t="inlineStr">
@@ -16270,6 +17356,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S188" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="48" t="inlineStr">
@@ -16346,6 +17437,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S189" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="48" t="inlineStr">
@@ -16422,6 +17518,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S190" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="48" t="inlineStr">
@@ -16498,6 +17599,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S191" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="48" t="inlineStr">
@@ -16574,6 +17680,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S192" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="48" t="inlineStr">
@@ -16650,6 +17761,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S193" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="48" t="inlineStr">
@@ -16726,6 +17842,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S194" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="48" t="inlineStr">
@@ -16802,6 +17923,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S195" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="48" t="inlineStr">
@@ -16878,6 +18004,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S196" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="48" t="inlineStr">
@@ -16954,6 +18085,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S197" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="48" t="inlineStr">
@@ -16988,7 +18124,7 @@
       </c>
       <c r="G198" s="48" t="inlineStr">
         <is>
-          <t>Legacy Mitigation reads the capital cost time factors of wind and solar from the Power tab; its cached values for 2039-2041 (wind 0.920, 0.915, 0.909) disagree with the cached Power cells they reference (0.923, 0.920, 0.918), apparently a stale cache in the distributed file. Since v4.7 the MVP computes the factors from the Power tab by formula, so its power results (new capacity and investment of solar, wind and gas, then power fuel use and emissions) depart from legacy's stored run from 2039; nothing changes before 2039.</t>
+          <t>Legacy Mitigation reads the capital cost time factors of wind and solar from the Power tab; its cached values for 2039-2041 (wind 0.920, 0.915, 0.909) disagree with the cached Power cells they reference (0.923, 0.920, 0.918), apparently a stale cache in the distributed file. Since v4.7 the prototype computes the factors from the Power tab by formula, so its power results (new capacity and investment of solar, wind and gas, then power fuel use and emissions) depart from legacy's stored run from 2039; nothing changes before 2039.</t>
         </is>
       </c>
       <c r="H198" s="48" t="n"/>
@@ -16999,7 +18135,7 @@
       </c>
       <c r="J198" s="48" t="inlineStr">
         <is>
-          <t>DataTabs_v7_0.md; CAVEATS v4.7</t>
+          <t>Methods, chapter Data tabs; CAVEATS v4.7</t>
         </is>
       </c>
       <c r="K198" s="48" t="inlineStr">
@@ -17034,6 +18170,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S198" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="48" t="inlineStr">
@@ -17079,7 +18220,7 @@
       </c>
       <c r="J199" s="48" t="inlineStr">
         <is>
-          <t>PriceProjection_Method_v7_0.md 5; LegacyDiff</t>
+          <t>Methods, chapter Prices 5; LegacyDiff</t>
         </is>
       </c>
       <c r="K199" s="48" t="inlineStr">
@@ -17114,6 +18255,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S199" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="48" t="inlineStr">
@@ -17159,7 +18305,7 @@
       </c>
       <c r="J200" s="48" t="inlineStr">
         <is>
-          <t>Transport_Method_v7_0.md; LegacyDiff</t>
+          <t>Methods, chapter Transport; LegacyDiff</t>
         </is>
       </c>
       <c r="K200" s="48" t="inlineStr">
@@ -17194,6 +18340,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S200" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="48" t="inlineStr">
@@ -17234,12 +18385,12 @@
       <c r="H201" s="48" t="n"/>
       <c r="I201" s="48" t="inlineStr">
         <is>
-          <t>Replicated v4.15 (user 2026-10-18); the MVP form (change of the GDP share) is one line.</t>
+          <t>Replicated v4.15 (user 2026-10-18); the prototype form (change of the GDP share) is one line.</t>
         </is>
       </c>
       <c r="J201" s="48" t="inlineStr">
         <is>
-          <t>GDP_Method_v7_0.md; LegacyDiff</t>
+          <t>Methods, chapter Macro and results; LegacyDiff</t>
         </is>
       </c>
       <c r="K201" s="48" t="inlineStr">
@@ -17274,6 +18425,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S201" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="48" t="inlineStr">
@@ -17319,7 +18475,7 @@
       </c>
       <c r="J202" s="48" t="inlineStr">
         <is>
-          <t>GDP_Method_v7_0.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K202" s="48" t="inlineStr">
@@ -17354,6 +18510,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S202" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="48" t="inlineStr">
@@ -17388,7 +18549,7 @@
       </c>
       <c r="G203" s="48" t="inlineStr">
         <is>
-          <t>Legacy rows 96-100 set the revenue-use shares to 0 before CPIntro, so an impulse of those years counts only as an excise drag. The MVP applies the shares in every year (per-cohort shares would need one share row per cohort). Tiny for Egypt (the revenue gain before CPIntro is nearly 0).</t>
+          <t>Legacy rows 96-100 set the revenue-use shares to 0 before CPIntro, so an impulse of those years counts only as an excise drag. The prototype applies the shares in every year (per-cohort shares would need one share row per cohort). Tiny for Egypt (the revenue gain before CPIntro is nearly 0).</t>
         </is>
       </c>
       <c r="H203" s="48" t="n"/>
@@ -17399,7 +18560,7 @@
       </c>
       <c r="J203" s="48" t="inlineStr">
         <is>
-          <t>GDP_Method_v7_0.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K203" s="48" t="inlineStr">
@@ -17434,6 +18595,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S203" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="48" t="inlineStr">
@@ -17479,7 +18645,7 @@
       </c>
       <c r="J204" s="48" t="inlineStr">
         <is>
-          <t>GDP_Method_v7_0.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K204" s="48" t="inlineStr">
@@ -17514,6 +18680,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S204" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="48" t="inlineStr">
@@ -17559,7 +18730,7 @@
       </c>
       <c r="J205" s="48" t="inlineStr">
         <is>
-          <t>GDP_Method_v7_0.md</t>
+          <t>Methods, chapter Macro and results</t>
         </is>
       </c>
       <c r="K205" s="48" t="inlineStr">
@@ -17594,6 +18765,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S205" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="48" t="inlineStr">
@@ -17628,7 +18804,7 @@
       </c>
       <c r="G206" s="48" t="inlineStr">
         <is>
-          <t>Legacy total revenue (row 8026) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7913-7999) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7896-7904). The MVP 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
+          <t>Legacy total revenue (row 8026) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7913-7999) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7896-7904). The prototype 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
         </is>
       </c>
       <c r="H206" s="48" t="n"/>
@@ -17674,6 +18850,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S206" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="48" t="inlineStr">
@@ -17708,7 +18889,7 @@
       </c>
       <c r="G207" s="48" t="inlineStr">
         <is>
-          <t>Legacy counts the methane fee in total revenue (row 8024) and so in the fiscal space, on the scenario's own activity. The MVP counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
+          <t>Legacy counts the methane fee in total revenue (row 8024) and so in the fiscal space, on the scenario's own activity. The prototype counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
         </is>
       </c>
       <c r="H207" s="48" t="n"/>
@@ -17719,7 +18900,7 @@
       </c>
       <c r="J207" s="48" t="inlineStr">
         <is>
-          <t>GDP_Method_v7_0.md; LegacyDiff 55</t>
+          <t>Methods, chapter Macro and results; LegacyDiff 55</t>
         </is>
       </c>
       <c r="K207" s="48" t="inlineStr">
@@ -17754,6 +18935,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S207" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="48" t="inlineStr">
@@ -17799,7 +18985,7 @@
       </c>
       <c r="J208" s="48" t="inlineStr">
         <is>
-          <t>PriceProjection_Method_v7_0.md 6</t>
+          <t>Methods, chapter Prices 6</t>
         </is>
       </c>
       <c r="K208" s="48" t="inlineStr">
@@ -17834,6 +19020,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S208" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="48" t="inlineStr">
@@ -17868,7 +19059,7 @@
       </c>
       <c r="G209" s="48" t="inlineStr">
         <is>
-          <t>Legacy spreads a producer subsidy over world demand (oil) or half world, half domestic demand (coal, gas), and over domestic use (biomass): the per-unit subsidy is then near zero for oil, coal and gas, and enters the supply cost (the pass-through share reaches retail). The MVP has the fiscal line (pros x factor, rpsu) and no price effect; electricity producer subsidies enter the power price in legacy (power parked). None for Egypt (data 0).</t>
+          <t>Legacy spreads a producer subsidy over world demand (oil) or half world, half domestic demand (coal, gas), and over domestic use (biomass): the per-unit subsidy is then near zero for oil, coal and gas, and enters the supply cost (the pass-through share reaches retail). The prototype has the fiscal line (pros x factor, rpsu) and no price effect; electricity producer subsidies enter the power price in legacy (power parked). None for Egypt (data 0).</t>
         </is>
       </c>
       <c r="H209" s="48" t="n"/>
@@ -17879,7 +19070,7 @@
       </c>
       <c r="J209" s="48" t="inlineStr">
         <is>
-          <t>PriceProjection_Method_v7_0.md 6</t>
+          <t>Methods, chapter Prices 6</t>
         </is>
       </c>
       <c r="K209" s="48" t="inlineStr">
@@ -17912,6 +19103,11 @@
       <c r="R209" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S209" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -17951,7 +19147,7 @@
       <c r="I210" s="48" t="n"/>
       <c r="J210" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K210" s="48" t="inlineStr">
@@ -17982,6 +19178,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S210" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="48" t="inlineStr">
@@ -18019,7 +19220,7 @@
       <c r="I211" s="48" t="n"/>
       <c r="J211" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K211" s="48" t="inlineStr">
@@ -18050,6 +19251,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S211" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="48" t="inlineStr">
@@ -18087,7 +19293,7 @@
       <c r="I212" s="48" t="n"/>
       <c r="J212" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K212" s="48" t="inlineStr">
@@ -18118,6 +19324,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S212" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="48" t="inlineStr">
@@ -18155,7 +19366,7 @@
       <c r="I213" s="48" t="n"/>
       <c r="J213" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K213" s="48" t="inlineStr">
@@ -18190,6 +19401,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S213" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="48" t="inlineStr">
@@ -18227,7 +19443,7 @@
       <c r="I214" s="48" t="n"/>
       <c r="J214" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K214" s="48" t="inlineStr">
@@ -18258,6 +19474,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S214" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="48" t="inlineStr">
@@ -18295,7 +19516,7 @@
       <c r="I215" s="48" t="n"/>
       <c r="J215" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K215" s="48" t="inlineStr">
@@ -18330,6 +19551,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S215" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="48" t="inlineStr">
@@ -18367,7 +19593,7 @@
       <c r="I216" s="48" t="n"/>
       <c r="J216" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K216" s="48" t="inlineStr">
@@ -18400,6 +19626,11 @@
       <c r="R216" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S216" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -18439,7 +19670,7 @@
       <c r="I217" s="48" t="n"/>
       <c r="J217" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K217" s="48" t="inlineStr">
@@ -18472,6 +19703,11 @@
       <c r="R217" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S217" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -18511,7 +19747,7 @@
       <c r="I218" s="48" t="n"/>
       <c r="J218" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K218" s="48" t="inlineStr">
@@ -18544,6 +19780,11 @@
       <c r="R218" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S218" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -18583,7 +19824,7 @@
       <c r="I219" s="48" t="n"/>
       <c r="J219" s="48" t="inlineStr">
         <is>
-          <t>Distribution_Method_v7_0.md</t>
+          <t>Methods, chapter Distribution</t>
         </is>
       </c>
       <c r="K219" s="48" t="inlineStr">
@@ -18618,6 +19859,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S219" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="48" t="inlineStr">
@@ -18657,7 +19903,7 @@
       </c>
       <c r="H220" s="48" t="inlineStr">
         <is>
-          <t>Biomass gain 5 times too small when leakage is on. MVP: Fixed in v5.1 (lkb = -lkd x e_m / e_b).</t>
+          <t>Biomass gain 5 times too small when leakage is on. prototype: Fixed in v5.1 (lkb = -lkd x e_m / e_b).</t>
         </is>
       </c>
       <c r="I220" s="48" t="inlineStr">
@@ -18690,7 +19936,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="O220" s="53" t="inlineStr"/>
+      <c r="O220" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P220" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -18702,6 +19952,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S220" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed: fixed in the L45 form (=-(M5578+M5584+M5591)), which the plan says covers L90</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="48" t="inlineStr">
@@ -18741,7 +19996,7 @@
       </c>
       <c r="H221" s="48" t="inlineStr">
         <is>
-          <t>An exempt LPG still leaks to biomass. MVP: Fixed in v5.1 (lkt reads the row's own new policy nce).</t>
+          <t>An exempt LPG still leaks to biomass. prototype: Fixed in v5.1 (lkt reads the row's own new policy nce).</t>
         </is>
       </c>
       <c r="I221" s="48" t="inlineStr">
@@ -18774,7 +20029,11 @@
           <t>5.1</t>
         </is>
       </c>
-      <c r="O221" s="53" t="inlineStr"/>
+      <c r="O221" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P221" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -18786,6 +20045,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S221" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="48" t="inlineStr">
@@ -18825,7 +20089,7 @@
       </c>
       <c r="H222" s="48" t="inlineStr">
         <is>
-          <t>ExemptMostCook has no effect on fuel use or revenue. MVP: Not built (D8; LegacyDiff 67).</t>
+          <t>ExemptMostCook has no effect on fuel use or revenue. prototype: Not built (D8; LegacyDiff 67).</t>
         </is>
       </c>
       <c r="I222" s="48" t="inlineStr">
@@ -18858,7 +20122,11 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="O222" s="53" t="inlineStr"/>
+      <c r="O222" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P222" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -18870,6 +20138,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S222" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="48" t="inlineStr">
@@ -18909,7 +20182,7 @@
       </c>
       <c r="H223" s="48" t="inlineStr">
         <is>
-          <t>None (dead branch). MVP: Not built (coverage by switch).</t>
+          <t>None (dead branch). prototype: Not built (coverage by switch).</t>
         </is>
       </c>
       <c r="I223" s="48" t="inlineStr">
@@ -18938,7 +20211,11 @@
         </is>
       </c>
       <c r="N223" s="53" t="inlineStr"/>
-      <c r="O223" s="53" t="inlineStr"/>
+      <c r="O223" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P223" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -18950,6 +20227,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S223" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="48" t="inlineStr">
@@ -18989,7 +20271,7 @@
       </c>
       <c r="H224" s="48" t="inlineStr">
         <is>
-          <t>Biomass, renewables and jet fuel phase in differently from the other fuels. MVP: Not built (LegacyDiff 67).</t>
+          <t>Biomass, renewables and jet fuel phase in differently from the other fuels. prototype: Not built (LegacyDiff 67).</t>
         </is>
       </c>
       <c r="I224" s="48" t="inlineStr">
@@ -19018,7 +20300,11 @@
         </is>
       </c>
       <c r="N224" s="53" t="inlineStr"/>
-      <c r="O224" s="53" t="inlineStr"/>
+      <c r="O224" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P224" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19030,6 +20316,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S224" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="48" t="inlineStr">
@@ -19075,7 +20366,7 @@
       </c>
       <c r="J225" s="48" t="inlineStr">
         <is>
-          <t>PriceProjection_Method_v7_0.md 5; LegacyDiff 66</t>
+          <t>Methods, chapter Prices 5; LegacyDiff 66</t>
         </is>
       </c>
       <c r="K225" s="48" t="inlineStr">
@@ -19106,6 +20397,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S225" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="48" t="inlineStr">
@@ -19151,7 +20447,7 @@
       </c>
       <c r="J226" s="48" t="inlineStr">
         <is>
-          <t>Equations_v7_0.md 4a; LegacyDiff 65</t>
+          <t>Equations.md 4a; LegacyDiff 65</t>
         </is>
       </c>
       <c r="K226" s="48" t="inlineStr">
@@ -19182,6 +20478,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S226" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="48" t="inlineStr">
@@ -19258,6 +20559,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S227" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="48" t="inlineStr">
@@ -19297,7 +20603,7 @@
       </c>
       <c r="H228" s="48" t="inlineStr">
         <is>
-          <t>Industry feebate coverage follows the ETS switch on the Dashboard. MVP: Not applicable in the MVP (feebate coverage typed per scenario, MTInputs rows 66-82).</t>
+          <t>Industry feebate coverage follows the ETS switch on the Dashboard. prototype: Not applicable in the prototype (feebate coverage typed per scenario, MTInputs rows 66-82).</t>
         </is>
       </c>
       <c r="I228" s="48" t="inlineStr">
@@ -19326,7 +20632,11 @@
         </is>
       </c>
       <c r="N228" s="53" t="inlineStr"/>
-      <c r="O228" s="53" t="inlineStr"/>
+      <c r="O228" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P228" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19338,6 +20648,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S228" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="48" t="inlineStr">
@@ -19377,7 +20692,7 @@
       </c>
       <c r="H229" s="48" t="inlineStr">
         <is>
-          <t>Machinery and other manufacturing join the ETS with buildings, not industry. MVP: Not applicable in the MVP (ETS coverage typed per scenario, MTInputs rows 99-115).</t>
+          <t>Machinery and other manufacturing join the ETS with buildings, not industry. prototype: Not applicable in the prototype (ETS coverage typed per scenario, MTInputs rows 99-115).</t>
         </is>
       </c>
       <c r="I229" s="48" t="inlineStr">
@@ -19406,7 +20721,11 @@
         </is>
       </c>
       <c r="N229" s="53" t="inlineStr"/>
-      <c r="O229" s="53" t="inlineStr"/>
+      <c r="O229" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P229" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19418,6 +20737,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S229" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="48" t="inlineStr">
@@ -19457,7 +20781,7 @@
       </c>
       <c r="H230" s="48" t="inlineStr">
         <is>
-          <t>Manual electricity prices ignored. MVP: Not applicable in the MVP (manual domestic prices not built; block placed, not read).</t>
+          <t>Manual electricity prices ignored. prototype: Not applicable in the prototype (manual domestic prices not built; block placed, not read).</t>
         </is>
       </c>
       <c r="I230" s="48" t="inlineStr">
@@ -19486,7 +20810,11 @@
         </is>
       </c>
       <c r="N230" s="53" t="inlineStr"/>
-      <c r="O230" s="53" t="inlineStr"/>
+      <c r="O230" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P230" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19498,6 +20826,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S230" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="48" t="inlineStr">
@@ -19537,7 +20870,7 @@
       </c>
       <c r="H231" s="48" t="inlineStr">
         <is>
-          <t>Manual services income elasticities equal the industry ones. MVP: Not applicable in the MVP (manual elasticities not built; block placed, not read).</t>
+          <t>Manual services income elasticities equal the industry ones. prototype: Not applicable in the prototype (manual elasticities not built; block placed, not read).</t>
         </is>
       </c>
       <c r="I231" s="48" t="inlineStr">
@@ -19566,7 +20899,11 @@
         </is>
       </c>
       <c r="N231" s="53" t="inlineStr"/>
-      <c r="O231" s="53" t="inlineStr"/>
+      <c r="O231" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P231" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19578,6 +20915,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S231" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="48" t="inlineStr">
@@ -19617,7 +20959,7 @@
       </c>
       <c r="H232" s="48" t="inlineStr">
         <is>
-          <t>Manual non-energy elasticities ignored. MVP: Fixed in v5.2 (typed inputs on Manual inputs K325:M327, read directly; same values; LegacyDiff 72).</t>
+          <t>Manual non-energy elasticities ignored. prototype: Fixed in v5.2 (typed inputs on Manual inputs K325:M327, read directly; same values; LegacyDiff 72).</t>
         </is>
       </c>
       <c r="I232" s="48" t="inlineStr">
@@ -19650,7 +20992,11 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O232" s="53" t="inlineStr"/>
+      <c r="O232" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P232" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19662,6 +21008,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S232" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="48" t="inlineStr">
@@ -19701,7 +21052,7 @@
       </c>
       <c r="H233" s="48" t="inlineStr">
         <is>
-          <t>Manual SCC entered on Manual inputs is ignored. MVP: Fixed in v5.2 (scc.man reads Manual inputs row 237 by year; names SCCManVal, SCCManYear). No effect on the shipped scenarios (SCC source Target).</t>
+          <t>Manual SCC entered on Manual inputs is ignored. prototype: Fixed in v5.2 (scc.man reads Manual inputs row 237 by year; names SCCManVal, SCCManYear). No effect on the shipped scenarios (SCC source Target).</t>
         </is>
       </c>
       <c r="I233" s="48" t="inlineStr">
@@ -19734,7 +21085,11 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O233" s="53" t="inlineStr"/>
+      <c r="O233" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P233" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19746,6 +21101,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S233" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="48" t="inlineStr">
@@ -19785,7 +21145,7 @@
       </c>
       <c r="H234" s="48" t="inlineStr">
         <is>
-          <t>None (unused name). MVP: Not applicable in the MVP (name not used).</t>
+          <t>None (unused name). prototype: Not applicable in the prototype (name not used).</t>
         </is>
       </c>
       <c r="I234" s="48" t="inlineStr">
@@ -19814,7 +21174,11 @@
         </is>
       </c>
       <c r="N234" s="53" t="inlineStr"/>
-      <c r="O234" s="53" t="inlineStr"/>
+      <c r="O234" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P234" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19826,6 +21190,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S234" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="48" t="inlineStr">
@@ -19865,7 +21234,7 @@
       </c>
       <c r="H235" s="48" t="inlineStr">
         <is>
-          <t>Industry feebate rates set on the Dashboard have no effect. MVP: Not applicable in the MVP (feebate rates typed per scenario on MTInputs).</t>
+          <t>Industry feebate rates set on the Dashboard have no effect. prototype: Not applicable in the prototype (feebate rates typed per scenario on MTInputs).</t>
         </is>
       </c>
       <c r="I235" s="48" t="inlineStr">
@@ -19894,7 +21263,11 @@
         </is>
       </c>
       <c r="N235" s="53" t="inlineStr"/>
-      <c r="O235" s="53" t="inlineStr"/>
+      <c r="O235" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P235" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19906,6 +21279,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S235" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="48" t="inlineStr">
@@ -19945,7 +21323,7 @@
       </c>
       <c r="H236" s="48" t="inlineStr">
         <is>
-          <t>None (memo only). MVP: Fixed in the placed memo (display only).</t>
+          <t>None (memo only). prototype: Fixed in the placed memo (display only).</t>
         </is>
       </c>
       <c r="I236" s="48" t="inlineStr">
@@ -19974,7 +21352,11 @@
         </is>
       </c>
       <c r="N236" s="53" t="inlineStr"/>
-      <c r="O236" s="53" t="inlineStr"/>
+      <c r="O236" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P236" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -19986,6 +21368,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S236" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="48" t="inlineStr">
@@ -20020,13 +21407,13 @@
       </c>
       <c r="G237" s="48" t="inlineStr">
         <is>
-          <t>Manual inputs V11:X11 read Dashboard Q30 (buildings) for construction, fuel transformation and other energy use: a grouping choice. The MVP types ETS coverage per scenario (MTInputs rows 99-115).</t>
+          <t>Manual inputs V11:X11 read Dashboard Q30 (buildings) for construction, fuel transformation and other energy use: a grouping choice. The prototype types ETS coverage per scenario (MTInputs rows 99-115).</t>
         </is>
       </c>
       <c r="H237" s="48" t="n"/>
       <c r="I237" s="48" t="inlineStr">
         <is>
-          <t>Conditional: nothing to replicate now (the MVP types ETS coverage per sector). Decided (user 2026-10-19): replicate the legacy grouping when ETS coverage by Dashboard groups is built.</t>
+          <t>Conditional: nothing to replicate now (the prototype types ETS coverage per sector). Decided (user 2026-10-19): replicate the legacy grouping when ETS coverage by Dashboard groups is built.</t>
         </is>
       </c>
       <c r="J237" s="48" t="inlineStr">
@@ -20066,6 +21453,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S237" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="48" t="inlineStr">
@@ -20100,13 +21492,13 @@
       </c>
       <c r="G238" s="48" t="inlineStr">
         <is>
-          <t>A manual price row is "Manual" only if its 2021 value is filled (Mitigation F765:F829 test K$764); years without a value fall back to the data year by year. Could be a bug (intent unclear). The MVP does not build manual domestic prices (block placed, not read).</t>
+          <t>A manual price row is "Manual" only if its 2021 value is filled (Mitigation F765:F829 test K$764); years without a value fall back to the data year by year. Could be a bug (intent unclear). The prototype does not build manual domestic prices (block placed, not read).</t>
         </is>
       </c>
       <c r="H238" s="48" t="n"/>
       <c r="I238" s="48" t="inlineStr">
         <is>
-          <t>Conditional: nothing to replicate now (the MVP does not build manual domestic prices). Decided (user 2026-10-19): an issue; replicate legacy when manual domestic prices are built; ask the CPAT team about the intent.</t>
+          <t>Conditional: nothing to replicate now (the prototype does not build manual domestic prices). Decided (user 2026-10-19): an issue; replicate legacy when manual domestic prices are built; ask the CPAT team about the intent.</t>
         </is>
       </c>
       <c r="J238" s="48" t="inlineStr">
@@ -20146,6 +21538,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S238" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="48" t="inlineStr">
@@ -20175,7 +21572,7 @@
       </c>
       <c r="F239" s="48" t="inlineStr">
         <is>
-          <t>Departs from legacy: The same cells and names, read by the macro SolveETS and ets_goalseek_v7_0.py (before v5.2: constants in the code); values 20, Continue, 0.005, the MVP error being the worst yearly /covered / cap - 1/; StartFresh starts from the fast estimate ets.est, Continue from the override row if it holds prices</t>
+          <t>Departs from legacy: The same cells and names, read by the macro SolveETS and ets_goalseek.py (before v5.2: constants in the code); values 20, Continue, 0.005, the prototype error being the worst yearly /covered / cap - 1/; StartFresh starts from the fast estimate ets.est, Continue from the override row if it holds prices</t>
         </is>
       </c>
       <c r="G239" s="48" t="inlineStr">
@@ -20222,6 +21619,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S239" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="48" t="inlineStr">
@@ -20298,6 +21700,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S240" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="48" t="inlineStr">
@@ -20337,7 +21744,7 @@
       </c>
       <c r="H241" s="48" t="inlineStr">
         <is>
-          <t>The two policies cannot be timed apart. MVP: Fixed (v5.4): own input RenSubsidyAddStartYear (MTInputs row 482, default 2027 = the default of row 132); rows rnsp, rns.</t>
+          <t>The two policies cannot be timed apart. prototype: Fixed (v5.4): own input RenSubsidyAddStartYear (MTInputs row 482, default 2027 = the default of row 132); rows rnsp, rns.</t>
         </is>
       </c>
       <c r="I241" s="48" t="inlineStr">
@@ -20386,6 +21793,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S241" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="48" t="inlineStr">
@@ -20425,7 +21837,7 @@
       </c>
       <c r="H242" s="48" t="inlineStr">
         <is>
-          <t>Wrong total revenue whenever a renewable subsidy is set. MVP: Fixed (v5.4): revenue = subsidy x generation by type (row prrns), hydro by its switch, biomass included; in rsub.pow and rpol.ren.</t>
+          <t>Wrong total revenue whenever a renewable subsidy is set. prototype: Fixed (v5.4): revenue = subsidy x generation by type (row prrns), hydro by its switch, biomass included; in rsub.pow and rpol.ren.</t>
         </is>
       </c>
       <c r="I242" s="48" t="inlineStr">
@@ -20474,6 +21886,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S242" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="48" t="inlineStr">
@@ -20513,7 +21930,7 @@
       </c>
       <c r="H243" s="48" t="inlineStr">
         <is>
-          <t>Low and Vhigh options give errors. MVP: Fixed (v5.4): the older series of the same option (wind, solar) or Medium (other renewables, Vhigh), Inputs_ppath tcf|&lt;type&gt;|&lt;option&gt;. User to confirm the fallback.</t>
+          <t>Low and Vhigh options give errors. prototype: Fixed (v5.4): the older series of the same option (wind, solar) or Medium (other renewables, Vhigh), Inputs_ppath tcf|&lt;type&gt;|&lt;option&gt;. User to confirm the fallback.</t>
         </is>
       </c>
       <c r="I243" s="48" t="inlineStr">
@@ -20562,6 +21979,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S243" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: fallback implemented as planned and accepted (user 2026-10-19); the real Low and Vhigh series are still missing (data gap)</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="48" t="inlineStr">
@@ -20601,7 +22023,7 @@
       </c>
       <c r="H244" s="48" t="inlineStr">
         <is>
-          <t>Revenue split inconsistent (total unchanged). MVP: Fixed (v5.4): the rebate returns the carbon cost passed through (row rreb, without VAT) and the VAT on it is not collected (rnvat); the total change equals legacy's.</t>
+          <t>Revenue split inconsistent (total unchanged). prototype: Fixed (v5.4): the rebate returns the carbon cost passed through (row rreb, without VAT) and the VAT on it is not collected (rnvat); the total change equals legacy's.</t>
         </is>
       </c>
       <c r="I244" s="48" t="inlineStr">
@@ -20650,6 +22072,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S244" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="48" t="inlineStr">
@@ -20689,7 +22116,7 @@
       </c>
       <c r="H245" s="48" t="inlineStr">
         <is>
-          <t>Excise revenue overstated when AdditionalExcise is on. MVP: Fixed (v5.4): excise revenue = the excise in the price x consumption (rows pex, rpex, rexm).</t>
+          <t>Excise revenue overstated when AdditionalExcise is on. prototype: Fixed (v5.4): excise revenue = the excise in the price x consumption (rows pex, rpex, rexm).</t>
         </is>
       </c>
       <c r="I245" s="48" t="inlineStr">
@@ -20738,6 +22165,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S245" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="48" t="inlineStr">
@@ -20783,7 +22215,7 @@
       </c>
       <c r="J246" s="48" t="inlineStr">
         <is>
-          <t>PowerModel_Method_v7_0.md; LegacyDiff 75</t>
+          <t>Methods, chapter Power; LegacyDiff 75</t>
         </is>
       </c>
       <c r="K246" s="48" t="inlineStr">
@@ -20814,6 +22246,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S246" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="48" t="inlineStr">
@@ -20859,7 +22296,7 @@
       </c>
       <c r="J247" s="48" t="inlineStr">
         <is>
-          <t>PowerPrices_Method_v7_0.md; LegacyDiff 76</t>
+          <t>Methods, chapter Power; LegacyDiff 76</t>
         </is>
       </c>
       <c r="K247" s="48" t="inlineStr">
@@ -20890,6 +22327,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S247" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="48" t="inlineStr">
@@ -20924,7 +22366,7 @@
       </c>
       <c r="G248" s="48" t="inlineStr">
         <is>
-          <t>The excise per kWh = CO2 of the fuel input to power / power output of the base-year balance x carbon price, the same intensity in every year and scenario (Mitigation C2253, row 2253). Replicated (row exs, PwGInt) with the MVP's calibrated power EFs.</t>
+          <t>The excise per kWh = CO2 of the fuel input to power / power output of the base-year balance x carbon price, the same intensity in every year and scenario (Mitigation C2253, row 2253). Replicated (row exs, PwGInt) with the prototype's calibrated power EFs.</t>
         </is>
       </c>
       <c r="H248" s="48" t="n"/>
@@ -20935,7 +22377,7 @@
       </c>
       <c r="J248" s="48" t="inlineStr">
         <is>
-          <t>PowerPrices_Method_v7_0.md; LegacyDiff 77</t>
+          <t>Methods, chapter Power; LegacyDiff 77</t>
         </is>
       </c>
       <c r="K248" s="48" t="inlineStr">
@@ -20966,6 +22408,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S248" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="48" t="inlineStr">
@@ -21011,7 +22458,7 @@
       </c>
       <c r="J249" s="48" t="inlineStr">
         <is>
-          <t>PowerModel_Method_v7_0.md; LegacyDiff 78</t>
+          <t>Methods, chapter Power; LegacyDiff 78</t>
         </is>
       </c>
       <c r="K249" s="48" t="inlineStr">
@@ -21042,6 +22489,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S249" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="48" t="inlineStr">
@@ -21076,7 +22528,7 @@
       </c>
       <c r="G250" s="48" t="inlineStr">
         <is>
-          <t>PowerRebates (G261), RenewableSubsidyHydro (row 3150) and AdditionalExcise (F201) count a starred "Yes*" as No. The MVP accepts Yes or Yes* (LEFT 3), as I54 and the other MVP switches.</t>
+          <t>PowerRebates (G261), RenewableSubsidyHydro (row 3150) and AdditionalExcise (F201) count a starred "Yes*" as No. The prototype accepts Yes or Yes* (LEFT 3), as I54 and the other prototype switches.</t>
         </is>
       </c>
       <c r="H250" s="48" t="n"/>
@@ -21087,7 +22539,7 @@
       </c>
       <c r="J250" s="48" t="inlineStr">
         <is>
-          <t>PowerPrices_Method_v7_0.md; LegacyDiff 77</t>
+          <t>Methods, chapter Power; LegacyDiff 77</t>
         </is>
       </c>
       <c r="K250" s="48" t="inlineStr">
@@ -21118,6 +22570,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S250" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="48" t="inlineStr">
@@ -21152,7 +22609,7 @@
       </c>
       <c r="G251" s="48" t="inlineStr">
         <is>
-          <t>Legacy adds the electricity fuel price reform (MTInputs 148/162) to the excise (row 216); the MVP computes fpr.ecy but does not apply it to the electricity price.</t>
+          <t>Legacy adds the electricity fuel price reform (MTInputs 148/162) to the excise (row 216); the prototype computes fpr.ecy but does not apply it to the electricity price.</t>
         </is>
       </c>
       <c r="H251" s="48" t="n"/>
@@ -21163,7 +22620,7 @@
       </c>
       <c r="J251" s="48" t="inlineStr">
         <is>
-          <t>PowerPrices_Method_v7_0.md</t>
+          <t>Methods, chapter Power</t>
         </is>
       </c>
       <c r="K251" s="48" t="inlineStr">
@@ -21198,6 +22655,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S251" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="48" t="inlineStr">
@@ -21232,7 +22694,7 @@
       </c>
       <c r="G252" s="48" t="inlineStr">
         <is>
-          <t>Legacy floors the end-user electricity price at MinPostSubsidyPowerPrice (rows 3617, 3646); the MVP has no floor (MinPostSubsidyPowerPrice is read per scenario since v5.4 but used only where legacy uses it in the cost side).</t>
+          <t>Legacy floors the end-user electricity price at MinPostSubsidyPowerPrice (rows 3617, 3646); the prototype has no floor (MinPostSubsidyPowerPrice is read per scenario since v5.4 but used only where legacy uses it in the cost side).</t>
         </is>
       </c>
       <c r="H252" s="48" t="n"/>
@@ -21243,7 +22705,7 @@
       </c>
       <c r="J252" s="48" t="inlineStr">
         <is>
-          <t>PowerPrices_Method_v7_0.md</t>
+          <t>Methods, chapter Power</t>
         </is>
       </c>
       <c r="K252" s="48" t="inlineStr">
@@ -21276,6 +22738,11 @@
       <c r="R252" s="53" t="inlineStr">
         <is>
           <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S252" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
         </is>
       </c>
     </row>
@@ -21350,6 +22817,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S253" s="53" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="48" t="inlineStr">
@@ -21389,7 +22861,7 @@
       </c>
       <c r="H254" s="48" t="inlineStr">
         <is>
-          <t>Regulations have no effect in the policy run even after the L87 fix. MVP: Not replicated: the MVP's regulation shadow price is per scenario group (reg rows, v4.16).</t>
+          <t>Regulations have no effect in the policy run even after the L87 fix. prototype: Not replicated: the prototype's regulation shadow price is per scenario group (reg rows, v4.16).</t>
         </is>
       </c>
       <c r="I254" s="48" t="inlineStr">
@@ -21422,7 +22894,11 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="O254" s="53" t="inlineStr"/>
+      <c r="O254" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P254" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -21434,6 +22910,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S254" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed: the switch still reads $D$2369, which is the same formula as the policy switch (both from G259)</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="48" t="inlineStr">
@@ -21473,7 +22954,7 @@
       </c>
       <c r="H255" s="48" t="inlineStr">
         <is>
-          <t>Choosing the default option ("Yes*") of PowerRebates, RenewableSubsidyHydro or AdditionalExcise switches the feature off. MVP: Fixed (v5.4): the MVP accepts Yes or Yes* (LEFT 3).</t>
+          <t>Choosing the default option ("Yes*") of PowerRebates, RenewableSubsidyHydro or AdditionalExcise switches the feature off. prototype: Fixed (v5.4): the prototype accepts Yes or Yes* (LEFT 3).</t>
         </is>
       </c>
       <c r="I255" s="48" t="inlineStr">
@@ -21506,7 +22987,11 @@
           <t>5.4</t>
         </is>
       </c>
-      <c r="O255" s="53" t="inlineStr"/>
+      <c r="O255" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P255" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -21518,6 +23003,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S255" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="48" t="inlineStr">
@@ -21557,7 +23047,7 @@
       </c>
       <c r="H256" s="48" t="inlineStr">
         <is>
-          <t>Renewable subsidies too large in real terms in later years (nominal value read as real). MVP: Fixed (v5.6): the inputs are converted to real with the CPI factor of the year (row rnsp).</t>
+          <t>Renewable subsidies too large in real terms in later years (nominal value read as real). prototype: Fixed (v5.6): the inputs are converted to real with the CPI factor of the year (row rnsp).</t>
         </is>
       </c>
       <c r="I256" s="48" t="inlineStr">
@@ -21590,7 +23080,11 @@
           <t>5.6</t>
         </is>
       </c>
-      <c r="O256" s="53" t="inlineStr"/>
+      <c r="O256" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P256" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -21602,6 +23096,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S256" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="48" t="inlineStr">
@@ -21641,7 +23140,7 @@
       </c>
       <c r="H257" s="48" t="inlineStr">
         <is>
-          <t>Residential gas price carries the LPG permit price wherever an existing ETS covers either fuel. MVP: Fixed by design: the MVP reads the existing ETS price by fuel and sector (section 2).</t>
+          <t>Residential gas price carries the LPG permit price wherever an existing ETS covers either fuel. prototype: Fixed by design: the prototype reads the existing ETS price by fuel and sector (section 2).</t>
         </is>
       </c>
       <c r="I257" s="48" t="inlineStr">
@@ -21670,7 +23169,11 @@
         </is>
       </c>
       <c r="N257" s="53" t="inlineStr"/>
-      <c r="O257" s="53" t="inlineStr"/>
+      <c r="O257" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P257" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -21682,6 +23185,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S257" s="53" t="inlineStr">
+        <is>
+          <t>Fixed with caveats: changed, but to the wrong row: K2555:AE2555 and the policy copy read K$1735 (existing carbon tax fuel rate, biomass), not K$1715 (ETS, natural gas, residential)</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="48" t="inlineStr">
@@ -21721,7 +23229,7 @@
       </c>
       <c r="H258" s="48" t="inlineStr">
         <is>
-          <t>None today (equal values); wrong step-change elasticity for services gasoline and diesel when regional values differ. MVP: Not built: the MVP reads the income elasticities by code from the data step.</t>
+          <t>None today (equal values); wrong step-change elasticity for services gasoline and diesel when regional values differ. prototype: Not built: the prototype reads the income elasticities by code from the data step.</t>
         </is>
       </c>
       <c r="I258" s="48" t="inlineStr">
@@ -21750,7 +23258,11 @@
         </is>
       </c>
       <c r="N258" s="53" t="inlineStr"/>
-      <c r="O258" s="53" t="inlineStr"/>
+      <c r="O258" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P258" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -21762,6 +23274,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S258" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="48" t="inlineStr">
@@ -21801,7 +23318,7 @@
       </c>
       <c r="H259" s="48" t="inlineStr">
         <is>
-          <t>None today (lag 0 is 0); the lag-0 transfers multiplier would come from the wrong country. MVP: Not replicated: the MVP reads the multiplier table by country code.</t>
+          <t>None today (lag 0 is 0); the lag-0 transfers multiplier would come from the wrong country. prototype: Not replicated: the prototype reads the multiplier table by country code.</t>
         </is>
       </c>
       <c r="I259" s="48" t="inlineStr">
@@ -21830,7 +23347,11 @@
         </is>
       </c>
       <c r="N259" s="53" t="inlineStr"/>
-      <c r="O259" s="53" t="inlineStr"/>
+      <c r="O259" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P259" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -21842,6 +23363,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S259" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="48" t="inlineStr">
@@ -21887,7 +23413,7 @@
       </c>
       <c r="J260" s="48" t="inlineStr">
         <is>
-          <t>Transport_Method_v7_0.md; TODO</t>
+          <t>Methods, chapter Transport; TODO</t>
         </is>
       </c>
       <c r="K260" s="48" t="inlineStr">
@@ -21922,6 +23448,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S260" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="48" t="inlineStr">
@@ -21962,12 +23493,12 @@
       <c r="H261" s="48" t="n"/>
       <c r="I261" s="48" t="inlineStr">
         <is>
-          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the MVP (user 2026-10-20); replicated as legacy. Recommendation: add a partial-adjustment option: fuel use moves a share of the way to its long-run level each year (short-run and long-run elasticities), as an upgrade over legacy, switch off = legacy.</t>
+          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the prototype (user 2026-10-20); replicated as legacy. Recommendation: add a partial-adjustment option: fuel use moves a share of the way to its long-run level each year (short-run and long-run elasticities), as an upgrade over legacy, switch off = legacy.</t>
         </is>
       </c>
       <c r="J261" s="48" t="inlineStr">
         <is>
-          <t>PriceProjection_Method_v7_0.md; TODO</t>
+          <t>Methods, chapter Prices; TODO</t>
         </is>
       </c>
       <c r="K261" s="48" t="inlineStr">
@@ -21998,6 +23529,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S261" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="48" t="inlineStr">
@@ -22043,7 +23579,7 @@
       </c>
       <c r="J262" s="48" t="inlineStr">
         <is>
-          <t>PriceProjection_Method_v7_0.md; TODO</t>
+          <t>Methods, chapter Prices; TODO</t>
         </is>
       </c>
       <c r="K262" s="48" t="inlineStr">
@@ -22074,6 +23610,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S262" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="48" t="inlineStr">
@@ -22108,18 +23649,18 @@
       </c>
       <c r="G263" s="48" t="inlineStr">
         <is>
-          <t>Legacy reads GAINS combustion factor paths by year; in the NoPropData file they are zero (proprietary). The MVP uses the GAINS base and final factors (EF_PM), linear to EFEndYear (2039), flat after (LegacyDiff LD47). Combustion CH4 is scaled to the inventory by the calibration. Data issue: no legacy formula is wrong.</t>
+          <t>Legacy reads GAINS combustion factor paths by year; in the NoPropData file they are zero (proprietary). The prototype uses the GAINS base and final factors (EF_PM), linear to EFEndYear (2039), flat after (LegacyDiff LD47). Combustion CH4 is scaled to the inventory by the calibration. Data issue: no legacy formula is wrong.</t>
         </is>
       </c>
       <c r="H263" s="48" t="n"/>
       <c r="I263" s="48" t="inlineStr">
         <is>
-          <t>MVP fill kept (user 2026-10-19). Data request: a legacy file with the GAINS combustion factor paths (high priority, user 2026-10-19).</t>
+          <t>prototype fill kept (user 2026-10-19). Data request: a legacy file with the GAINS combustion factor paths (high priority, user 2026-10-19).</t>
         </is>
       </c>
       <c r="J263" s="48" t="inlineStr">
         <is>
-          <t>GHG_Method_v7_0.md; LegacyDiff</t>
+          <t>Methods, chapter Emissions; LegacyDiff</t>
         </is>
       </c>
       <c r="K263" s="48" t="inlineStr">
@@ -22150,6 +23691,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S263" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="48" t="inlineStr">
@@ -22184,18 +23730,18 @@
       </c>
       <c r="G264" s="48" t="inlineStr">
         <is>
-          <t>Some VAT cells of the IMF price dataset are blank; legacy then uses 0. The MVP fills blank cells with the general VAT rate (VAT_WEO) for residential coal and gas and all-sector oil products, 0 for power, industry and biomass (LegacyDiff LD3). None for Egypt since v0.14 (corrected data fill every VAT cell). Data issue.</t>
+          <t>Some VAT cells of the IMF price dataset are blank; legacy then uses 0. The prototype fills blank cells with the general VAT rate (VAT_WEO) for residential coal and gas and all-sector oil products, 0 for power, industry and biomass (LegacyDiff LD3). None for Egypt since v0.14 (corrected data fill every VAT cell). Data issue.</t>
         </is>
       </c>
       <c r="H264" s="48" t="n"/>
       <c r="I264" s="48" t="inlineStr">
         <is>
-          <t>MVP fill kept (user 2026-10-19). Data request: raise the blank VAT cells with the data team (high priority, user 2026-10-19); the MVP fill stays until then.</t>
+          <t>prototype fill kept (user 2026-10-19). Data request: raise the blank VAT cells with the data team (high priority, user 2026-10-19); the prototype fill stays until then.</t>
         </is>
       </c>
       <c r="J264" s="48" t="inlineStr">
         <is>
-          <t>PriceProjection_Method_v7_0.md; LegacyDiff</t>
+          <t>Methods, chapter Prices; LegacyDiff</t>
         </is>
       </c>
       <c r="K264" s="48" t="inlineStr">
@@ -22230,6 +23776,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S264" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="48" t="inlineStr">
@@ -22269,7 +23820,7 @@
       </c>
       <c r="H265" s="48" t="inlineStr">
         <is>
-          <t>Over-investment whenever a type is set to Manual: logit investment comes on top of the manual capacity path. MVP: Fixed (v5.6, P3): rows needm, first and deficit use the need net of manual investment.</t>
+          <t>Over-investment whenever a type is set to Manual: logit investment comes on top of the manual capacity path. prototype: Fixed (v5.6, P3): rows needm, first and deficit use the need net of manual investment.</t>
         </is>
       </c>
       <c r="I265" s="48" t="inlineStr">
@@ -22302,7 +23853,11 @@
           <t>5.6</t>
         </is>
       </c>
-      <c r="O265" s="53" t="inlineStr"/>
+      <c r="O265" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P265" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -22314,6 +23869,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S265" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="48" t="inlineStr">
@@ -22348,7 +23908,7 @@
       </c>
       <c r="G266" s="48" t="inlineStr">
         <is>
-          <t>Legacy grows crude oil, natural gas and coal production (rows 6146-6149) from 2024 with the producer-price response to the methane fee (rows 6137-6144: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The MVP holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
+          <t>Legacy grows crude oil, natural gas and coal production (rows 6146-6149) from 2024 with the producer-price response to the methane fee (rows 6137-6144: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The prototype holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
         </is>
       </c>
       <c r="H266" s="48" t="n"/>
@@ -22359,7 +23919,7 @@
       </c>
       <c r="J266" s="48" t="inlineStr">
         <is>
-          <t>GHG_Method_v7_0.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K266" s="48" t="inlineStr">
@@ -22394,6 +23954,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S266" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="48" t="inlineStr">
@@ -22433,7 +23998,7 @@
       </c>
       <c r="H267" s="48" t="inlineStr">
         <is>
-          <t>BAU targets before 2030 scaled twice; Fixed and Historical never adjusted. MVP: Fixed (v5.7, NDC comparison 14c): the MVP compares every NDC in its own target year (each year is modelled), so no adjustment is needed.</t>
+          <t>BAU targets before 2030 scaled twice; Fixed and Historical never adjusted. prototype: Fixed (v5.7, NDC comparison 14c): the prototype compares every NDC in its own target year (each year is modelled), so no adjustment is needed.</t>
         </is>
       </c>
       <c r="I267" s="48" t="inlineStr">
@@ -22466,7 +24031,11 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O267" s="53" t="inlineStr"/>
+      <c r="O267" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P267" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -22478,6 +24047,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S267" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="48" t="inlineStr">
@@ -22517,7 +24091,7 @@
       </c>
       <c r="H268" s="48" t="inlineStr">
         <is>
-          <t>Conditional NDC line plotted as the inverse ratio. MVP: Fixed (v5.7, NDC comparison 14c): ndc.idx = target / base-year GHGs incl. LULUCF for both.</t>
+          <t>Conditional NDC line plotted as the inverse ratio. prototype: Fixed (v5.7, NDC comparison 14c): ndc.idx = target / base-year GHGs incl. LULUCF for both.</t>
         </is>
       </c>
       <c r="I268" s="48" t="inlineStr">
@@ -22550,7 +24124,11 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O268" s="53" t="inlineStr"/>
+      <c r="O268" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P268" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -22562,6 +24140,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S268" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="48" t="inlineStr">
@@ -22601,7 +24184,7 @@
       </c>
       <c r="H269" s="48" t="inlineStr">
         <is>
-          <t>None today (branch never runs); a cut would be read as a level. MVP: Fixed (v5.7, NDC comparison 14c): level = reference-year emissions x (1 - reduction).</t>
+          <t>None today (branch never runs); a cut would be read as a level. prototype: Fixed (v5.7, NDC comparison 14c): level = reference-year emissions x (1 - reduction).</t>
         </is>
       </c>
       <c r="I269" s="48" t="inlineStr">
@@ -22634,7 +24217,11 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O269" s="53" t="inlineStr"/>
+      <c r="O269" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P269" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -22646,6 +24233,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S269" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="48" t="inlineStr">
@@ -22685,7 +24277,7 @@
       </c>
       <c r="H270" s="48" t="inlineStr">
         <is>
-          <t>Intensity targets incl. LULUCF count non-CO2 twice and miss LULUCF. MVP: Fixed (v5.7, NDC comparison 14c): the reduction is computed on the NDC basis and applied to the BAU incl. LULUCF, as for the other types.</t>
+          <t>Intensity targets incl. LULUCF count non-CO2 twice and miss LULUCF. prototype: Fixed (v5.7, NDC comparison 14c): the reduction is computed on the NDC basis and applied to the BAU incl. LULUCF, as for the other types.</t>
         </is>
       </c>
       <c r="I270" s="48" t="inlineStr">
@@ -22718,7 +24310,11 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O270" s="53" t="inlineStr"/>
+      <c r="O270" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P270" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -22730,6 +24326,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S270" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="48" t="inlineStr">
@@ -22764,12 +24365,12 @@
       </c>
       <c r="G271" s="48" t="inlineStr">
         <is>
-          <t>Not reproduced in the .xlsb (cell plan 2026-10-20): G469 = _NDC_Year, so G470 is the WEO real GDP of the reference year and F18466 = G470 is right; the fixed-cell reading came from the LibreOffice conversion. Only gap: reference years before 2000 find no GDP (#VALUE! or N/A; the MVP also gives N/A). Kept for the record. Found by the item 8 plan (v5.7).</t>
+          <t>Not reproduced in the .xlsb (cell plan 2026-10-20): G469 = _NDC_Year, so G470 is the WEO real GDP of the reference year and F18466 = G470 is right; the fixed-cell reading came from the LibreOffice conversion. Only gap: reference years before 2000 find no GDP (#VALUE! or N/A; the prototype also gives N/A). Kept for the record. Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="H271" s="48" t="inlineStr">
         <is>
-          <t>None. MVP: Fixed (v5.7, NDC comparison 14c): ndc.gdp.ref looks the reference year up (WEO real GDP; N/A when the year is not in the data).</t>
+          <t>None. prototype: Fixed (v5.7, NDC comparison 14c): ndc.gdp.ref looks the reference year up (WEO real GDP; N/A when the year is not in the data).</t>
         </is>
       </c>
       <c r="I271" s="48" t="inlineStr">
@@ -22802,7 +24403,11 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O271" s="53" t="inlineStr"/>
+      <c r="O271" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P271" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -22814,6 +24419,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S271" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="48" t="inlineStr">
@@ -22848,7 +24458,7 @@
       </c>
       <c r="G272" s="48" t="inlineStr">
         <is>
-          <t>Legacy row 18464 H uses 5665 (Mt CO2) for China instead of the data (row 889). The MVP reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
+          <t>Legacy row 18464 H uses 5665 (Mt CO2) for China instead of the data (row 889). The prototype reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
         </is>
       </c>
       <c r="H272" s="48" t="n"/>
@@ -22859,7 +24469,7 @@
       </c>
       <c r="J272" s="48" t="inlineStr">
         <is>
-          <t>GHG_Method_v7_0.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K272" s="48" t="inlineStr">
@@ -22894,6 +24504,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S272" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="48" t="inlineStr">
@@ -22939,7 +24554,7 @@
       </c>
       <c r="J273" s="48" t="inlineStr">
         <is>
-          <t>GHG_Method_v7_0.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K273" s="48" t="inlineStr">
@@ -22974,6 +24589,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S273" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="48" t="inlineStr">
@@ -23042,7 +24662,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O274" s="53" t="inlineStr"/>
+      <c r="O274" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P274" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23054,6 +24678,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S274" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="48" t="inlineStr">
@@ -23122,7 +24751,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O275" s="53" t="inlineStr"/>
+      <c r="O275" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P275" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23134,6 +24767,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S275" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="48" t="inlineStr">
@@ -23202,7 +24840,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O276" s="53" t="inlineStr"/>
+      <c r="O276" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P276" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23214,6 +24856,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S276" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="48" t="inlineStr">
@@ -23282,7 +24929,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O277" s="53" t="inlineStr"/>
+      <c r="O277" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P277" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23294,6 +24945,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S277" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="48" t="inlineStr">
@@ -23362,7 +25018,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O278" s="53" t="inlineStr"/>
+      <c r="O278" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P278" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23374,6 +25034,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S278" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="48" t="inlineStr">
@@ -23442,7 +25107,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O279" s="53" t="inlineStr"/>
+      <c r="O279" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P279" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23454,6 +25123,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S279" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="48" t="inlineStr">
@@ -23518,7 +25192,11 @@
         </is>
       </c>
       <c r="N280" s="53" t="inlineStr"/>
-      <c r="O280" s="53" t="inlineStr"/>
+      <c r="O280" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P280" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23530,6 +25208,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S280" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="48" t="inlineStr">
@@ -23598,7 +25281,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O281" s="53" t="inlineStr"/>
+      <c r="O281" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P281" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23610,6 +25297,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S281" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="48" t="inlineStr">
@@ -23678,7 +25370,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O282" s="53" t="inlineStr"/>
+      <c r="O282" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P282" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23690,6 +25386,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S282" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="48" t="inlineStr">
@@ -23758,7 +25459,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O283" s="53" t="inlineStr"/>
+      <c r="O283" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P283" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23770,6 +25475,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S283" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="48" t="inlineStr">
@@ -23838,7 +25548,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O284" s="53" t="inlineStr"/>
+      <c r="O284" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P284" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23850,6 +25564,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S284" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="48" t="inlineStr">
@@ -23918,7 +25637,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O285" s="53" t="inlineStr"/>
+      <c r="O285" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P285" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -23930,6 +25653,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S285" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="48" t="inlineStr">
@@ -23998,7 +25726,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O286" s="53" t="inlineStr"/>
+      <c r="O286" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P286" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24010,6 +25742,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S286" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="48" t="inlineStr">
@@ -24078,7 +25815,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O287" s="53" t="inlineStr"/>
+      <c r="O287" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P287" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24090,6 +25831,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S287" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="48" t="inlineStr">
@@ -24158,7 +25904,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O288" s="53" t="inlineStr"/>
+      <c r="O288" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P288" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24170,6 +25920,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S288" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="48" t="inlineStr">
@@ -24238,7 +25993,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O289" s="53" t="inlineStr"/>
+      <c r="O289" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P289" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24250,6 +26009,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S289" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="48" t="inlineStr">
@@ -24318,7 +26082,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O290" s="53" t="inlineStr"/>
+      <c r="O290" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P290" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24330,6 +26098,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S290" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="48" t="inlineStr">
@@ -24398,7 +26171,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O291" s="53" t="inlineStr"/>
+      <c r="O291" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P291" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24410,6 +26187,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S291" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="48" t="inlineStr">
@@ -24450,7 +26232,7 @@
       <c r="H292" s="48" t="n"/>
       <c r="I292" s="48" t="inlineStr">
         <is>
-          <t>Not replicated: the MVP writes the right codes.</t>
+          <t>Not replicated: the prototype writes the right codes.</t>
         </is>
       </c>
       <c r="J292" s="48" t="inlineStr">
@@ -24474,7 +26256,11 @@
         </is>
       </c>
       <c r="N292" s="53" t="inlineStr"/>
-      <c r="O292" s="53" t="inlineStr"/>
+      <c r="O292" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P292" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24486,6 +26272,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S292" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="48" t="inlineStr">
@@ -24554,7 +26345,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O293" s="53" t="inlineStr"/>
+      <c r="O293" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P293" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24566,6 +26361,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S293" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="48" t="inlineStr">
@@ -24634,7 +26434,11 @@
           <t>6.0</t>
         </is>
       </c>
-      <c r="O294" s="53" t="inlineStr"/>
+      <c r="O294" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P294" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24646,6 +26450,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S294" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="48" t="inlineStr">
@@ -24686,7 +26495,7 @@
       <c r="H295" s="48" t="n"/>
       <c r="I295" s="48" t="inlineStr">
         <is>
-          <t>Not replicated: the MVP builds codes from the row ids.</t>
+          <t>Not replicated: the prototype builds codes from the row ids.</t>
         </is>
       </c>
       <c r="J295" s="48" t="inlineStr">
@@ -24710,7 +26519,11 @@
         </is>
       </c>
       <c r="N295" s="53" t="inlineStr"/>
-      <c r="O295" s="53" t="inlineStr"/>
+      <c r="O295" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P295" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24722,6 +26535,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S295" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="48" t="inlineStr">
@@ -24761,7 +26579,7 @@
       </c>
       <c r="H296" s="48" t="inlineStr">
         <is>
-          <t>A gas producer subsidy misses residential gas, which takes the oil value instead. MVP: Fixed (v6.1, I49): every block reads the per-unit subsidy of its own fuel by its international price position (psp).</t>
+          <t>A gas producer subsidy misses residential gas, which takes the oil value instead. prototype: Fixed (v6.1, I49): every block reads the per-unit subsidy of its own fuel by its international price position (psp).</t>
         </is>
       </c>
       <c r="I296" s="48" t="inlineStr">
@@ -24794,7 +26612,11 @@
           <t>6.1</t>
         </is>
       </c>
-      <c r="O296" s="53" t="inlineStr"/>
+      <c r="O296" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P296" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24806,6 +26628,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S296" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed: K2547:N2547 and the policy copy now read row 826 (the L82 change)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="48" t="inlineStr">
@@ -24845,7 +26672,7 @@
       </c>
       <c r="H297" s="48" t="inlineStr">
         <is>
-          <t>The oil producer subsidy is about 159 times too small for other oil products. MVP: Fixed (v6.1, I49): x liters per barrel (LitersPerBbl) for a barrel-priced block.</t>
+          <t>The oil producer subsidy is about 159 times too small for other oil products. prototype: Fixed (v6.1, I49): x liters per barrel (LitersPerBbl) for a barrel-priced block.</t>
         </is>
       </c>
       <c r="I297" s="48" t="inlineStr">
@@ -24878,7 +26705,11 @@
           <t>6.1</t>
         </is>
       </c>
-      <c r="O297" s="53" t="inlineStr"/>
+      <c r="O297" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P297" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -24890,6 +26721,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S297" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed: exactly the planned fix</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="48" t="inlineStr">
@@ -24924,7 +26760,7 @@
       </c>
       <c r="G298" s="48" t="inlineStr">
         <is>
-          <t>Legacy computes air-pollution mortality and its valuation from fuel use (sheets AP and the Mitigation co-benefit rows). The MVP keeps local pollutant emissions (section 15) only. Dropped by the user (2026-10-20); the plan stays for reference.</t>
+          <t>Legacy computes air-pollution mortality and its valuation from fuel use (sheets AP and the Mitigation co-benefit rows). The prototype keeps local pollutant emissions (section 15) only. Dropped by the user (2026-10-20); the plan stays for reference.</t>
         </is>
       </c>
       <c r="H298" s="48" t="n"/>
@@ -24935,7 +26771,7 @@
       </c>
       <c r="J298" s="48" t="inlineStr">
         <is>
-          <t>Plans_v7_0.md (section Plan_AirPollution)</t>
+          <t>excel_ai/plans/Air_pollution.md</t>
         </is>
       </c>
       <c r="K298" s="48" t="inlineStr">
@@ -24970,6 +26806,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S298" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="48" t="inlineStr">
@@ -25004,7 +26845,7 @@
       </c>
       <c r="G299" s="48" t="inlineStr">
         <is>
-          <t>Legacy values the transport externalities of road fuel use and vehicle-km. Not in the MVP. Dropped by the user (2026-10-20); the plan stays for reference.</t>
+          <t>Legacy values the transport externalities of road fuel use and vehicle-km. Not in the prototype. Dropped by the user (2026-10-20); the plan stays for reference.</t>
         </is>
       </c>
       <c r="H299" s="48" t="n"/>
@@ -25015,7 +26856,7 @@
       </c>
       <c r="J299" s="48" t="inlineStr">
         <is>
-          <t>Plans_v7_0.md (section Plan_TransportExternalities)</t>
+          <t>excel_ai/plans/Transport_cobenefits.md</t>
         </is>
       </c>
       <c r="K299" s="48" t="inlineStr">
@@ -25050,6 +26891,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S299" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="48" t="inlineStr">
@@ -25090,12 +26936,12 @@
       <c r="H300" s="48" t="n"/>
       <c r="I300" s="48" t="inlineStr">
         <is>
-          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the MVP (user 2026-10-20); replicated as legacy. Recommendation: split the driver: fuel use x (1 + population growth)^1 x (1 + per-capita income growth)^income elasticity, keeping the price and efficiency terms separate; switch off = legacy.</t>
+          <t>Legacy issue, not a bug: high priority for the CPAT team, not for the prototype (user 2026-10-20); replicated as legacy. Recommendation: split the driver: fuel use x (1 + population growth)^1 x (1 + per-capita income growth)^income elasticity, keeping the price and efficiency terms separate; switch off = legacy.</t>
         </is>
       </c>
       <c r="J300" s="48" t="inlineStr">
         <is>
-          <t>Equations_v7_0.md E53-E56; PriceProjection_Method_v7_0.md</t>
+          <t>Equations.md E53-E56; Methods, chapter Prices</t>
         </is>
       </c>
       <c r="K300" s="48" t="inlineStr">
@@ -25126,6 +26972,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S300" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="48" t="inlineStr">
@@ -25165,7 +27016,7 @@
       </c>
       <c r="H301" s="48" t="inlineStr">
         <is>
-          <t>Power costs read the next two years' prices: a circular reference as soon as a price depends on quantities. MVP: Fixed (v6.2): trailing average t-4 .. t (fpp over the row fpn; AVERAGEIFS on the year row keeps the scenario's own years). Price changes reach power costs about two years later than in legacy.</t>
+          <t>Power costs read the next two years' prices: a circular reference as soon as a price depends on quantities. prototype: Fixed (v6.2): trailing average t-4 .. t (fpp over the row fpn; AVERAGEIFS on the year row keeps the scenario's own years). Price changes reach power costs about two years later than in legacy.</t>
         </is>
       </c>
       <c r="I301" s="48" t="inlineStr">
@@ -25185,7 +27036,7 @@
       </c>
       <c r="L301" s="53" t="inlineStr">
         <is>
-          <t>Other mitigation</t>
+          <t>Engineer power</t>
         </is>
       </c>
       <c r="M301" s="53" t="inlineStr">
@@ -25214,6 +27065,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S301" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="48" t="inlineStr">
@@ -25253,7 +27109,7 @@
       </c>
       <c r="H302" s="48" t="inlineStr">
         <is>
-          <t>Latent: investment would read future quantities through the cost path. MVP: Fixed (v6.2) as a rule with a test: the levelised cost reads only input-driven costs (tvc: fuel price for power, variable O&amp;M, policy rates, shadow price, rebate); the quick check tests that no other row reads a later year and that tvc reaches no fuel use, GDP or power quantity row.</t>
+          <t>Latent: investment would read future quantities through the cost path. prototype: Fixed (v6.2) as a rule with a test: the levelised cost reads only input-driven costs (tvc: fuel price for power, variable O&amp;M, policy rates, shadow price, rebate); the quick check tests that no other row reads a later year and that tvc reaches no fuel use, GDP or power quantity row.</t>
         </is>
       </c>
       <c r="I302" s="48" t="inlineStr">
@@ -25273,7 +27129,7 @@
       </c>
       <c r="L302" s="53" t="inlineStr">
         <is>
-          <t>Other mitigation</t>
+          <t>Engineer power</t>
         </is>
       </c>
       <c r="M302" s="53" t="inlineStr">
@@ -25302,6 +27158,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S302" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="48" t="inlineStr">
@@ -25336,18 +27197,18 @@
       </c>
       <c r="G303" s="48" t="inlineStr">
         <is>
-          <t>Legacy and the MVP let revenue of year t move GDP only from year t+1 (legacy row 8776 reads the previous column; MVP gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
+          <t>Legacy and the prototype let revenue of year t move GDP only from year t+1 (legacy row 8776 reads the previous column; prototype gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
         </is>
       </c>
       <c r="H303" s="48" t="n"/>
       <c r="I303" s="48" t="inlineStr">
         <is>
-          <t>Stated as a rule (user 2026-10-20): GDP_Method_v7_0.md section Timing rule and NORMS (circular references): revenue of year t moves GDP only from year t+1, the fiscal space reads revenue of year t only, and no same-year GDP effect reaches same-year demand. Recommendation to the CPAT team: state it in the legacy method too.</t>
+          <t>Stated as a rule (user 2026-10-20): Methods, chapter Macro and results section Timing rule and NORMS (circular references): revenue of year t moves GDP only from year t+1, the fiscal space reads revenue of year t only, and no same-year GDP effect reaches same-year demand. Recommendation to the CPAT team: state it in the legacy method too.</t>
         </is>
       </c>
       <c r="J303" s="48" t="inlineStr">
         <is>
-          <t>GDP_Method_v7_0.md; NORMS (circular references)</t>
+          <t>Methods, chapter Macro and results; NORMS (circular references)</t>
         </is>
       </c>
       <c r="K303" s="48" t="inlineStr">
@@ -25378,6 +27239,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S303" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="48" t="inlineStr">
@@ -25412,13 +27278,13 @@
       </c>
       <c r="G304" s="48" t="inlineStr">
         <is>
-          <t>Lookups of the scenario-1 value of the same year (INDEX over a row, MATCH on the year) must not range over later columns: in a recalculation that evaluates the range, a lookup over the whole row reads its own scenario's later years and closes a circular reference (the MVP had one such row, ener.ref, fixed in v6.2; all others end at the current column). Recommendation to the CPAT team: check the legacy lookups the same way.</t>
+          <t>Lookups of the scenario-1 value of the same year (INDEX over a row, MATCH on the year) must not range over later columns: in a recalculation that evaluates the range, a lookup over the whole row reads its own scenario's later years and closes a circular reference (the prototype had one such row, ener.ref, fixed in v6.2; all others end at the current column). Recommendation to the CPAT team: check the legacy lookups the same way.</t>
         </is>
       </c>
       <c r="H304" s="48" t="n"/>
       <c r="I304" s="48" t="inlineStr">
         <is>
-          <t>Legacy checked (v6.2 scan of every Mitigation formula for reads of later years): no scenario-1 lookup over whole rows (the policy block reads the baseline block in the same column); the cost breakdown (rows 3509-3517) reads the user's CostBreakdownYear, a report only; the net revenue report rows read the next year: legacy bug L128. MVP: every lookup ends at the current column (ener.ref fixed in v6.2); the quick check tests reads of later years.</t>
+          <t>Legacy checked (v6.2 scan of every Mitigation formula for reads of later years): no scenario-1 lookup over whole rows (the policy block reads the baseline block in the same column); the cost breakdown (rows 3509-3517) reads the user's CostBreakdownYear, a report only; the net revenue report rows read the next year: legacy bug L128. prototype: every lookup ends at the current column (ener.ref fixed in v6.2); the quick check tests reads of later years.</t>
         </is>
       </c>
       <c r="J304" s="48" t="inlineStr">
@@ -25458,6 +27324,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S304" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="48" t="inlineStr">
@@ -25492,18 +27363,18 @@
       </c>
       <c r="G305" s="48" t="inlineStr">
         <is>
-          <t>Source allocations and intensities of the methane fee must be calibrated on data or base-year activity, never on a later model year: legacy read GHGYear (2024) activity in the earlier years, a read of later years that becomes circular as soon as the fee revenue feeds the GDP effects. The MVP uses data activity since v6.0 and, for the fiscal space, the stored scenario-1 gas and biomass activity (I47). Recommendation to the CPAT team.</t>
+          <t>Source allocations and intensities of the methane fee must be calibrated on data or base-year activity, never on a later model year: legacy read GHGYear (2024) activity in the earlier years, a read of later years that becomes circular as soon as the fee revenue feeds the GDP effects. The prototype uses data activity since v6.0 and, for the fiscal space, the stored scenario-1 gas and biomass activity (I47). Recommendation to the CPAT team.</t>
         </is>
       </c>
       <c r="H305" s="48" t="n"/>
       <c r="I305" s="48" t="inlineStr">
         <is>
-          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7562) uses the first two years and applies the factor from the third (it reads only earlier years). The MVP calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
+          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7562) uses the first two years and applies the factor from the third (it reads only earlier years). The prototype calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
         </is>
       </c>
       <c r="J305" s="48" t="inlineStr">
         <is>
-          <t>GHG_Method_v7_0.md</t>
+          <t>Methods, chapter Emissions</t>
         </is>
       </c>
       <c r="K305" s="48" t="inlineStr">
@@ -25538,6 +27409,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S305" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="48" t="inlineStr">
@@ -25577,7 +27453,7 @@
       </c>
       <c r="H306" s="48" t="inlineStr">
         <is>
-          <t>Each year reports the next year's net revenue (USD and % of GDP). MVP: Not in the MVP (its revenue rows read the same year; reporting rebuilt). Legacy fix: K6252 =K8038 and K6257 =K8043, filled K:AD.</t>
+          <t>Each year reports the next year's net revenue (USD and % of GDP). prototype: Not in the prototype (its revenue rows read the same year; reporting rebuilt). Legacy fix: K6252 =K8038 and K6257 =K8043, filled K:AD.</t>
         </is>
       </c>
       <c r="I306" s="48" t="inlineStr">
@@ -25610,7 +27486,11 @@
           <t>6.2</t>
         </is>
       </c>
-      <c r="O306" s="53" t="inlineStr"/>
+      <c r="O306" s="53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P306" s="53" t="inlineStr">
         <is>
           <t>Not reconciled yet</t>
@@ -25622,6 +27502,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S306" s="53" t="inlineStr">
+        <is>
+          <t>Confirmed fixed</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="48" t="inlineStr">
@@ -25661,7 +27546,7 @@
       </c>
       <c r="H307" s="48" t="inlineStr">
         <is>
-          <t>With a baseline renewable subsidy (MTInputs 354) the subsidy cost is counted twice. MVP: Fixed (MVP: one renewable subsidy row rnsp = baseline + additional, counted once).</t>
+          <t>With a baseline renewable subsidy (MTInputs 354) the subsidy cost is counted twice. prototype: Fixed (prototype: one renewable subsidy row rnsp = baseline + additional, counted once).</t>
         </is>
       </c>
       <c r="I307" s="48" t="inlineStr">
@@ -25702,6 +27587,11 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S307" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="48" t="inlineStr">
@@ -25741,7 +27631,7 @@
       </c>
       <c r="H308" s="48" t="inlineStr">
         <is>
-          <t>Conditional and unconditional intensity targets are not comparable. MVP: Fixed (MVP 14c: ndc.hi applies the cut to the reference-year intensity x target-year GDP, for both).</t>
+          <t>Conditional and unconditional intensity targets are not comparable. prototype: Fixed (prototype 14c: ndc.hi applies the cut to the reference-year intensity x target-year GDP, for both).</t>
         </is>
       </c>
       <c r="I308" s="48" t="inlineStr">
@@ -25782,9 +27672,366 @@
           <t>v7.0</t>
         </is>
       </c>
+      <c r="S308" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="48" t="inlineStr">
+        <is>
+          <t>L131</t>
+        </is>
+      </c>
+      <c r="B309" s="48" t="inlineStr">
+        <is>
+          <t>Legacy bug</t>
+        </is>
+      </c>
+      <c r="C309" s="48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D309" s="48" t="inlineStr">
+        <is>
+          <t>Codes: one output code on rows with different contents</t>
+        </is>
+      </c>
+      <c r="E309" s="49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F309" s="48" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G309" s="48" t="inlineStr">
+        <is>
+          <t>Legacy reuses a code for other quantities: gdp.pre.lvl for ln(GDP pc), GDP in $mn and in bn US$; sub.new.usd for revenue subtotals; rev.ctr.coa for the gasoline to electricity rows. A lookup by code finds the first row only. Found by the codes crosswalk (v7.1).</t>
+        </is>
+      </c>
+      <c r="H309" s="48" t="inlineStr">
+        <is>
+          <t>Lookups by code (MTOutputs, the data link) return the first row of a reused code. prototype: Fixed (v7.2, codes R7): every prototype code is unique (check_codes; the 18 copy rows carry no code).</t>
+        </is>
+      </c>
+      <c r="I309" s="48" t="inlineStr">
+        <is>
+          <t>Give each row its own code (e.g. gdp.pre.ln, gdp.pre.mn; sub.new.usd only on its own subtotal).</t>
+        </is>
+      </c>
+      <c r="J309" s="48" t="inlineStr">
+        <is>
+          <t>Mitigation rows 466, 2442, 16185 (gdp.pre.lvl); 7736, 7756, 7999 (sub.new.usd); 7652-13977 (rev.ctr.coa)</t>
+        </is>
+      </c>
+      <c r="K309" s="48" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="L309" s="53" t="inlineStr">
+        <is>
+          <t>Other mitigation</t>
+        </is>
+      </c>
+      <c r="M309" s="53" t="inlineStr">
+        <is>
+          <t>Legacy bug (mitigation)</t>
+        </is>
+      </c>
+      <c r="N309" s="53" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O309" s="53" t="inlineStr"/>
+      <c r="P309" s="53" t="inlineStr">
+        <is>
+          <t>Not reconciled yet</t>
+        </is>
+      </c>
+      <c r="Q309" s="53" t="inlineStr"/>
+      <c r="R309" s="53" t="inlineStr">
+        <is>
+          <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S309" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="48" t="inlineStr">
+        <is>
+          <t>L132</t>
+        </is>
+      </c>
+      <c r="B310" s="48" t="inlineStr">
+        <is>
+          <t>Legacy bug</t>
+        </is>
+      </c>
+      <c r="C310" s="48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D310" s="48" t="inlineStr">
+        <is>
+          <t>Codes: capitals and empty tokens</t>
+        </is>
+      </c>
+      <c r="E310" s="49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F310" s="48" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G310" s="48" t="inlineStr">
+        <is>
+          <t>Legacy codes mix capitals (All) into the lower-case protocol and end with an empty token (oc.tot., no scenario number), so a lookup of the protocol code fails. Found by the codes crosswalk (v7.1).</t>
+        </is>
+      </c>
+      <c r="H310" s="48" t="inlineStr">
+        <is>
+          <t>Lookups of the protocol codes fail. prototype: Fixed (v7.2): prototype codes are lower case with no empty token (code formula; check_codes).</t>
+        </is>
+      </c>
+      <c r="I310" s="48" t="inlineStr">
+        <is>
+          <t>Write the codes in lower case and with a scenario number: em.pm2.all.&lt;sector&gt;, nox.tot.&lt;n&gt;.</t>
+        </is>
+      </c>
+      <c r="J310" s="48" t="inlineStr">
+        <is>
+          <t>Mitigation rows 7620, 13937 (oc.tot.); em.pm2.All.&lt;sector&gt; rows</t>
+        </is>
+      </c>
+      <c r="K310" s="48" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="L310" s="53" t="inlineStr">
+        <is>
+          <t>Other mitigation</t>
+        </is>
+      </c>
+      <c r="M310" s="53" t="inlineStr">
+        <is>
+          <t>Legacy bug (mitigation)</t>
+        </is>
+      </c>
+      <c r="N310" s="53" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O310" s="53" t="inlineStr"/>
+      <c r="P310" s="53" t="inlineStr">
+        <is>
+          <t>Not reconciled yet</t>
+        </is>
+      </c>
+      <c r="Q310" s="53" t="inlineStr"/>
+      <c r="R310" s="53" t="inlineStr">
+        <is>
+          <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S310" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="48" t="inlineStr">
+        <is>
+          <t>L133</t>
+        </is>
+      </c>
+      <c r="B311" s="48" t="inlineStr">
+        <is>
+          <t>Legacy bug</t>
+        </is>
+      </c>
+      <c r="C311" s="48" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D311" s="48" t="inlineStr">
+        <is>
+          <t>Codes: nox.tot holds N2O, oc.tot. holds NOx</t>
+        </is>
+      </c>
+      <c r="E311" s="49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F311" s="48" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="G311" s="48" t="inlineStr">
+        <is>
+          <t>The N2O total in CO2e carries the code nox.tot and the NOx forcing row the code oc.tot. (labels: Nitrous oxide; Nitrogen oxides): a reader of the codes takes one gas for the other. Found by the codes crosswalk (v7.1).</t>
+        </is>
+      </c>
+      <c r="H311" s="48" t="inlineStr">
+        <is>
+          <t>A reader of the codes takes one gas for the other. prototype: Fixed (v7.2, codes R5): n2o.tot and nox.tot carry their own gas.</t>
+        </is>
+      </c>
+      <c r="I311" s="48" t="inlineStr">
+        <is>
+          <t>Rename the N2O total n2o.tot and the NOx forcing row nox.tot.</t>
+        </is>
+      </c>
+      <c r="J311" s="48" t="inlineStr">
+        <is>
+          <t>Mitigation rows 7620, 13937 and the GHG total rows (nox.tot)</t>
+        </is>
+      </c>
+      <c r="K311" s="48" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="L311" s="53" t="inlineStr">
+        <is>
+          <t>Other mitigation</t>
+        </is>
+      </c>
+      <c r="M311" s="53" t="inlineStr">
+        <is>
+          <t>Legacy bug (mitigation)</t>
+        </is>
+      </c>
+      <c r="N311" s="53" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="O311" s="53" t="inlineStr"/>
+      <c r="P311" s="53" t="inlineStr">
+        <is>
+          <t>Not reconciled yet</t>
+        </is>
+      </c>
+      <c r="Q311" s="53" t="inlineStr"/>
+      <c r="R311" s="53" t="inlineStr">
+        <is>
+          <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S311" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="48" t="inlineStr">
+        <is>
+          <t>I75</t>
+        </is>
+      </c>
+      <c r="B312" s="48" t="inlineStr">
+        <is>
+          <t>Issue (departure from legacy)</t>
+        </is>
+      </c>
+      <c r="C312" s="48" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="D312" s="48" t="inlineStr">
+        <is>
+          <t>Legacy code inconsistencies (CPAT code protocol)</t>
+        </is>
+      </c>
+      <c r="E312" s="49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="F312" s="48" t="inlineStr">
+        <is>
+          <t>Departs from legacy; queued to replicate</t>
+        </is>
+      </c>
+      <c r="G312" s="48" t="inlineStr">
+        <is>
+          <t>Legacy codes do not follow one protocol: variable names differ by module (trevst vs stockcalc), slots differ in order (fuel.sector and sector.fuel), totals are written all or tot, model letters (.e, .a, .t) end some codes. The prototype follows the protocol from v7.2 (codes R0-R9: legacy variable names, sector before fuel, tot for totals, no model letters); legacy codes that differ are aliases in the crosswalk.</t>
+        </is>
+      </c>
+      <c r="H312" s="48" t="n"/>
+      <c r="I312" s="48" t="inlineStr">
+        <is>
+          <t>v7.2 (codes R0-R9): the prototype codes follow the protocol; legacy codes that differ are aliases (crosswalk, LiveOutputs alias column). Open review rows: excel_ai/plans/TODO_Codes.md.</t>
+        </is>
+      </c>
+      <c r="J312" s="48" t="inlineStr">
+        <is>
+          <t>Codes_Remediation_Plan_v7_1.md; codes_crosswalk_v7_1.csv; code_renames_v7_2.csv</t>
+        </is>
+      </c>
+      <c r="K312" s="48" t="inlineStr">
+        <is>
+          <t>Resolved</t>
+        </is>
+      </c>
+      <c r="L312" s="53" t="inlineStr">
+        <is>
+          <t>Issue</t>
+        </is>
+      </c>
+      <c r="M312" s="53" t="inlineStr">
+        <is>
+          <t>Issue (mitigation)</t>
+        </is>
+      </c>
+      <c r="N312" s="53" t="inlineStr">
+        <is>
+          <t>7.2</t>
+        </is>
+      </c>
+      <c r="O312" s="53" t="inlineStr"/>
+      <c r="P312" s="53" t="inlineStr">
+        <is>
+          <t>Not reconciled yet</t>
+        </is>
+      </c>
+      <c r="Q312" s="53" t="inlineStr"/>
+      <c r="R312" s="53" t="inlineStr">
+        <is>
+          <t>v7.0</t>
+        </is>
+      </c>
+      <c r="S312" s="53" t="inlineStr">
+        <is>
+          <t>Not marked fixed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:R308"/>
+  <autoFilter ref="A3:S312"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader/>

--- a/excel_ai/legacy/workbooks/Tracking issues.xlsx
+++ b/excel_ai/legacy/workbooks/Tracking issues.xlsx
@@ -1320,7 +1320,7 @@
       <c r="R4" s="58" t="inlineStr"/>
       <c r="S4" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T4" s="58" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="S5" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T5" s="58" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="S6" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T6" s="58" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="R7" s="58" t="inlineStr"/>
       <c r="S7" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T7" s="58" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="R8" s="58" t="inlineStr"/>
       <c r="S8" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T8" s="58" t="inlineStr">
@@ -1778,7 +1778,7 @@
       <c r="R9" s="58" t="inlineStr"/>
       <c r="S9" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T9" s="58" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="S10" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T10" s="58" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="S11" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T11" s="58" t="inlineStr">
@@ -2056,7 +2056,7 @@
       <c r="R12" s="58" t="inlineStr"/>
       <c r="S12" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T12" s="58" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="R13" s="58" t="inlineStr"/>
       <c r="S13" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T13" s="58" t="inlineStr">
@@ -2240,7 +2240,7 @@
       <c r="R14" s="58" t="inlineStr"/>
       <c r="S14" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T14" s="58" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="R15" s="58" t="inlineStr"/>
       <c r="S15" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T15" s="58" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="S16" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T16" s="58" t="inlineStr">
@@ -2522,7 +2522,7 @@
       <c r="R17" s="58" t="inlineStr"/>
       <c r="S17" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T17" s="58" t="inlineStr">
@@ -2616,7 +2616,7 @@
       <c r="R18" s="58" t="inlineStr"/>
       <c r="S18" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T18" s="58" t="inlineStr">
@@ -2714,7 +2714,7 @@
       <c r="R19" s="58" t="inlineStr"/>
       <c r="S19" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T19" s="58" t="inlineStr">
@@ -2757,17 +2757,17 @@
       </c>
       <c r="H20" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 6172-6227 (livestock, rice, waste)</t>
+          <t>Mitigation rows 6158-6213 (livestock, rice, waste)</t>
         </is>
       </c>
       <c r="I20" s="58" t="inlineStr">
         <is>
-          <t>Livestock, rice and waste CH4 are the inventory values divided by the GWP, constant over time; the abatement shares of the methane fee are computed (rows 6182, 6194, 6206) but not applied, so a methane fee on agriculture and waste has no effect.</t>
+          <t>Livestock, rice and waste CH4 are the inventory values divided by the GWP, constant over time; the abatement shares of the methane fee are computed (rows 6168, 6180, 6192) but not applied, so a methane fee on agriculture and waste has no effect.</t>
         </is>
       </c>
       <c r="J20" s="58" t="inlineStr">
         <is>
-          <t>Grow livestock, rice and waste methane with their drivers (income, population) and apply the abatement shares already computed in rows 6182, 6194, 6206.</t>
+          <t>Grow livestock, rice and waste methane with their drivers (income, population) and apply the abatement shares already computed in rows 6168, 6180, 6192.</t>
         </is>
       </c>
       <c r="K20" s="58" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="S20" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T20" s="58" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="H21" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 6155-6156</t>
+          <t>Mitigation rows 6141-6142</t>
         </is>
       </c>
       <c r="I21" s="58" t="inlineStr">
@@ -2906,7 +2906,7 @@
       <c r="R21" s="58" t="inlineStr"/>
       <c r="S21" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T21" s="58" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="S22" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T22" s="58" t="inlineStr">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="H23" s="58" t="inlineStr">
         <is>
-          <t>Mitigation row 6206</t>
+          <t>Mitigation row 6192</t>
         </is>
       </c>
       <c r="I23" s="58" t="inlineStr">
         <is>
-          <t>The abatement share of waste equals that of livestock (=M6182) instead of the waste curve of CH4Inputs.</t>
+          <t>The abatement share of waste equals that of livestock (=M6168) instead of the waste curve of CH4Inputs.</t>
         </is>
       </c>
       <c r="J23" s="58" t="inlineStr">
         <is>
-          <t>Use the waste curve of CH4Inputs for waste (row 6206 now = M6182, the livestock share).</t>
+          <t>Use the waste curve of CH4Inputs for waste (row 6192 now = M6168, the livestock share).</t>
         </is>
       </c>
       <c r="K23" s="58" t="inlineStr">
@@ -3098,7 +3098,7 @@
       <c r="R23" s="58" t="inlineStr"/>
       <c r="S23" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T23" s="58" t="inlineStr">
@@ -3192,7 +3192,7 @@
       <c r="R24" s="58" t="inlineStr"/>
       <c r="S24" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T24" s="58" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="H25" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 6704, 6806, ... (total emissions of each pollutant)</t>
+          <t>Mitigation rows 6690, 6792, ... (total emissions of each pollutant)</t>
         </is>
       </c>
       <c r="I25" s="58" t="inlineStr">
@@ -3286,7 +3286,7 @@
       <c r="R25" s="58" t="inlineStr"/>
       <c r="S25" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T25" s="58" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="H26" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 2443-2446, 8288</t>
+          <t>Mitigation rows 2443-2446, 8274</t>
         </is>
       </c>
       <c r="I26" s="58" t="inlineStr">
@@ -3380,7 +3380,7 @@
       <c r="R26" s="58" t="inlineStr"/>
       <c r="S26" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T26" s="58" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="R27" s="58" t="inlineStr"/>
       <c r="S27" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T27" s="58" t="inlineStr">
@@ -3568,7 +3568,7 @@
       <c r="R28" s="58" t="inlineStr"/>
       <c r="S28" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T28" s="58" t="inlineStr">
@@ -3662,7 +3662,7 @@
       <c r="R29" s="58" t="inlineStr"/>
       <c r="S29" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T29" s="58" t="inlineStr">
@@ -3756,7 +3756,7 @@
       <c r="R30" s="58" t="inlineStr"/>
       <c r="S30" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T30" s="58" t="inlineStr">
@@ -3850,7 +3850,7 @@
       <c r="R31" s="58" t="inlineStr"/>
       <c r="S31" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T31" s="58" t="inlineStr">
@@ -3944,7 +3944,7 @@
       <c r="R32" s="58" t="inlineStr"/>
       <c r="S32" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T32" s="58" t="inlineStr">
@@ -4038,7 +4038,7 @@
       <c r="R33" s="58" t="inlineStr"/>
       <c r="S33" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T33" s="58" t="inlineStr">
@@ -4132,7 +4132,7 @@
       <c r="R34" s="58" t="inlineStr"/>
       <c r="S34" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T34" s="58" t="inlineStr">
@@ -4226,7 +4226,7 @@
       <c r="R35" s="58" t="inlineStr"/>
       <c r="S35" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T35" s="58" t="inlineStr">
@@ -4320,7 +4320,7 @@
       <c r="R36" s="58" t="inlineStr"/>
       <c r="S36" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T36" s="58" t="inlineStr">
@@ -4414,7 +4414,7 @@
       <c r="R37" s="58" t="inlineStr"/>
       <c r="S37" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T37" s="58" t="inlineStr">
@@ -4508,7 +4508,7 @@
       <c r="R38" s="58" t="inlineStr"/>
       <c r="S38" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T38" s="58" t="inlineStr">
@@ -4602,7 +4602,7 @@
       <c r="R39" s="58" t="inlineStr"/>
       <c r="S39" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T39" s="58" t="inlineStr">
@@ -4696,7 +4696,7 @@
       <c r="R40" s="58" t="inlineStr"/>
       <c r="S40" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T40" s="58" t="inlineStr">
@@ -4790,7 +4790,7 @@
       <c r="R41" s="58" t="inlineStr"/>
       <c r="S41" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T41" s="58" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="R42" s="58" t="inlineStr"/>
       <c r="S42" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T42" s="58" t="inlineStr">
@@ -4978,7 +4978,7 @@
       <c r="R43" s="58" t="inlineStr"/>
       <c r="S43" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T43" s="58" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="S44" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T44" s="58" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="H45" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 6077-6085</t>
+          <t>Mitigation rows 6063-6071</t>
         </is>
       </c>
       <c r="I45" s="58" t="inlineStr">
         <is>
-          <t>The income factor points to the blank row 2440, so other energy use never grows with GDP; rows 6077-6084 have no additional-efficiency term.</t>
+          <t>The income factor points to the blank row 2440, so other energy use never grows with GDP; rows 6063-6070 have no additional-efficiency term.</t>
         </is>
       </c>
       <c r="J45" s="58" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="S45" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T45" s="58" t="inlineStr">
@@ -5260,7 +5260,7 @@
       <c r="R46" s="58" t="inlineStr"/>
       <c r="S46" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T46" s="58" t="inlineStr">
@@ -5358,7 +5358,7 @@
       <c r="R47" s="58" t="inlineStr"/>
       <c r="S47" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T47" s="58" t="inlineStr">
@@ -5448,7 +5448,7 @@
       <c r="R48" s="58" t="inlineStr"/>
       <c r="S48" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T48" s="58" t="inlineStr">
@@ -5538,7 +5538,7 @@
       <c r="R49" s="58" t="inlineStr"/>
       <c r="S49" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T49" s="58" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="S50" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T50" s="58" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="H51" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 18177-18181, 742</t>
+          <t>Mitigation rows 18162-18166, 742</t>
         </is>
       </c>
       <c r="I51" s="58" t="inlineStr">
@@ -5730,7 +5730,7 @@
       <c r="R51" s="58" t="inlineStr"/>
       <c r="S51" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T51" s="58" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="H52" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 18195-18213</t>
+          <t>Mitigation rows 18180-18198</t>
         </is>
       </c>
       <c r="I52" s="58" t="inlineStr">
@@ -5824,7 +5824,7 @@
       <c r="R52" s="58" t="inlineStr"/>
       <c r="S52" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T52" s="58" t="inlineStr">
@@ -5918,7 +5918,7 @@
       <c r="R53" s="58" t="inlineStr"/>
       <c r="S53" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T53" s="58" t="inlineStr">
@@ -6012,7 +6012,7 @@
       <c r="R54" s="58" t="inlineStr"/>
       <c r="S54" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T54" s="58" t="inlineStr">
@@ -6106,7 +6106,7 @@
       <c r="R55" s="58" t="inlineStr"/>
       <c r="S55" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T55" s="58" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="S56" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T56" s="58" t="inlineStr">
@@ -6298,7 +6298,7 @@
       <c r="R57" s="58" t="inlineStr"/>
       <c r="S57" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T57" s="58" t="inlineStr">
@@ -6396,7 +6396,7 @@
       <c r="R58" s="58" t="inlineStr"/>
       <c r="S58" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T58" s="58" t="inlineStr">
@@ -6494,7 +6494,7 @@
       <c r="R59" s="58" t="inlineStr"/>
       <c r="S59" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T59" s="58" t="inlineStr">
@@ -6537,7 +6537,7 @@
       </c>
       <c r="H60" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 15900-16700 (GAINS factor lookups)</t>
+          <t>Mitigation rows 15885-16685 (GAINS factor lookups)</t>
         </is>
       </c>
       <c r="I60" s="58" t="inlineStr">
@@ -6588,7 +6588,7 @@
       <c r="R60" s="58" t="inlineStr"/>
       <c r="S60" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T60" s="58" t="inlineStr">
@@ -6631,12 +6631,12 @@
       </c>
       <c r="H61" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 15900-16700 (GAINS factor lookups; sheet EF_PM)</t>
+          <t>Mitigation rows 15885-16685 (GAINS factor lookups; sheet EF_PM)</t>
         </is>
       </c>
       <c r="I61" s="58" t="inlineStr">
         <is>
-          <t>A fuel that its GAINS subsector has no factor for gets 0, although it burns: Egypt 2022 residential LPG (3,182 ktoe), other mining diesel (3,819), food &amp; forestry diesel (927), fuel transformation LPG (2,466); food &amp; forestry shows about 1 t of NOx (legacy row 15939).</t>
+          <t>A fuel that its GAINS subsector has no factor for gets 0, although it burns: Egypt 2022 residential LPG (3,182 ktoe), other mining diesel (3,819), food &amp; forestry diesel (927), fuel transformation LPG (2,466); food &amp; forestry shows about 1 t of NOx (legacy row 15924).</t>
         </is>
       </c>
       <c r="J61" s="58" t="inlineStr">
@@ -6682,7 +6682,7 @@
       <c r="R61" s="58" t="inlineStr"/>
       <c r="S61" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T61" s="58" t="inlineStr">
@@ -6776,7 +6776,7 @@
       <c r="R62" s="58" t="inlineStr"/>
       <c r="S62" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T62" s="58" t="inlineStr">
@@ -6870,7 +6870,7 @@
       <c r="R63" s="58" t="inlineStr"/>
       <c r="S63" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T63" s="58" t="inlineStr">
@@ -6968,7 +6968,7 @@
       <c r="R64" s="58" t="inlineStr"/>
       <c r="S64" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T64" s="58" t="inlineStr">
@@ -7066,7 +7066,7 @@
       <c r="R65" s="58" t="inlineStr"/>
       <c r="S65" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T65" s="58" t="inlineStr">
@@ -7160,7 +7160,7 @@
       <c r="R66" s="58" t="inlineStr"/>
       <c r="S66" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T66" s="58" t="inlineStr">
@@ -7254,7 +7254,7 @@
       <c r="R67" s="58" t="inlineStr"/>
       <c r="S67" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T67" s="58" t="inlineStr">
@@ -7348,7 +7348,7 @@
       <c r="R68" s="58" t="inlineStr"/>
       <c r="S68" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T68" s="58" t="inlineStr">
@@ -7442,7 +7442,7 @@
       <c r="R69" s="58" t="inlineStr"/>
       <c r="S69" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T69" s="58" t="inlineStr">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="H70" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 8267-8288 (policy 14584-14605)</t>
+          <t>Mitigation rows 8253-8274 (policy 14569-14590)</t>
         </is>
       </c>
       <c r="I70" s="58" t="inlineStr">
@@ -7536,7 +7536,7 @@
       <c r="R70" s="58" t="inlineStr"/>
       <c r="S70" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T70" s="58" t="inlineStr">
@@ -7579,17 +7579,17 @@
       </c>
       <c r="H71" s="58" t="inlineStr">
         <is>
-          <t>Mitigation row 8071 (policy 14388)</t>
+          <t>Mitigation row 8057 (policy 14373)</t>
         </is>
       </c>
       <c r="I71" s="58" t="inlineStr">
         <is>
-          <t>The excise (revenue) use of the first cohort looks up L$8127, a baseline-block cell (0), instead of the cohort's own row (L14387); the contractionary effect of the first year's revenue is dropped (Egypt about 3e-5 of GDP).</t>
+          <t>The excise (revenue) use of the first cohort looks up L$8113, a baseline-block cell (0), instead of the cohort's own row (L14372); the contractionary effect of the first year's revenue is dropped (Egypt about 3e-5 of GDP).</t>
         </is>
       </c>
       <c r="J71" s="58" t="inlineStr">
         <is>
-          <t>Match the first cohort's excise use on its own row (L14387, baseline L8070), not L$8127.</t>
+          <t>Match the first cohort's excise use on its own row (L14372, baseline L8056), not L$8113.</t>
         </is>
       </c>
       <c r="K71" s="58" t="inlineStr">
@@ -7626,7 +7626,7 @@
       <c r="R71" s="58" t="inlineStr"/>
       <c r="S71" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T71" s="58" t="inlineStr">
@@ -7669,17 +7669,17 @@
       </c>
       <c r="H72" s="58" t="inlineStr">
         <is>
-          <t>Mitigation row 7761 (policy 14078)</t>
+          <t>Mitigation row 7747 (policy 14063)</t>
         </is>
       </c>
       <c r="I72" s="58" t="inlineStr">
         <is>
-          <t>The additional excise of gas in industry is the coal industry tax (R2512) x coal industry use (R6436).</t>
+          <t>The additional excise of gas in industry is the coal industry tax (R2512) x coal industry use (R6422).</t>
         </is>
       </c>
       <c r="J72" s="58" t="inlineStr">
         <is>
-          <t>Use the gas industry excise rate (row 2581) and gas industry use in row 7761.</t>
+          <t>Use the gas industry excise rate (row 2581) and gas industry use in row 7747.</t>
         </is>
       </c>
       <c r="K72" s="58" t="inlineStr">
@@ -7720,7 +7720,7 @@
       <c r="R72" s="58" t="inlineStr"/>
       <c r="S72" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T72" s="58" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="H73" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 7805, 7819, 7873</t>
+          <t>Mitigation rows 7791, 7805, 7859</t>
         </is>
       </c>
       <c r="I73" s="58" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="J73" s="58" t="inlineStr">
         <is>
-          <t>Multiply by _conv_ktoe_to_gj in rows 7805, 7819, 7873.</t>
+          <t>Multiply by _conv_ktoe_to_gj in rows 7791, 7805, 7859.</t>
         </is>
       </c>
       <c r="K73" s="58" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="S73" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T73" s="58" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H74" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 7671, 7756</t>
+          <t>Mitigation rows 7657, 7742</t>
         </is>
       </c>
       <c r="I74" s="58" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="J74" s="58" t="inlineStr">
         <is>
-          <t>Read column R (the year) in rows 7671 and 7756.</t>
+          <t>Read column R (the year) in rows 7657 and 7742.</t>
         </is>
       </c>
       <c r="K74" s="58" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="S74" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T74" s="58" t="inlineStr">
@@ -7951,17 +7951,17 @@
       </c>
       <c r="H75" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 7691 (policy 14008), 7718</t>
+          <t>Mitigation rows 7677 (policy 13993), 7704</t>
         </is>
       </c>
       <c r="I75" s="58" t="inlineStr">
         <is>
-          <t>Gas industry coverage divides by R6041 instead of the industry gas total (6442); kerosene power coverage multiplies power by domestic shipping (R2270 x R2273).</t>
+          <t>Gas industry coverage divides by R6027 instead of the industry gas total (6428); kerosene power coverage multiplies power by domestic shipping (R2270 x R2273).</t>
         </is>
       </c>
       <c r="J75" s="58" t="inlineStr">
         <is>
-          <t>Divide by the industry gas total (6442) in row 7691; use power x kerosene coverage (R2265 x R2270) in row 7718.</t>
+          <t>Divide by the industry gas total (6428) in row 7677; use power x kerosene coverage (R2265 x R2270) in row 7704.</t>
         </is>
       </c>
       <c r="K75" s="58" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="R75" s="58" t="inlineStr"/>
       <c r="S75" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T75" s="58" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="H76" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 17160-17164, 17190, 17201</t>
+          <t>Mitigation rows 17145-17149, 17175, 17186</t>
         </is>
       </c>
       <c r="I76" s="58" t="inlineStr">
@@ -8092,7 +8092,7 @@
       <c r="R76" s="58" t="inlineStr"/>
       <c r="S76" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T76" s="58" t="inlineStr">
@@ -8186,7 +8186,7 @@
       <c r="R77" s="58" t="inlineStr"/>
       <c r="S77" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T77" s="58" t="inlineStr">
@@ -8229,17 +8229,17 @@
       </c>
       <c r="H78" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 16317, 16389-16405</t>
+          <t>Mitigation rows 16302, 16374-16390</t>
         </is>
       </c>
       <c r="I78" s="58" t="inlineStr">
         <is>
-          <t>The "indexed vs 2022" rows read rows 16331-16338 (electricity industry, electricity residential, coal industry, ...) under the labels electricity, coal, gas, oil, ...; E16317 tests the policy gas total instead of the baseline one; labels say 2022 = 100 where baseline = 100.</t>
+          <t>The "indexed vs 2022" rows read rows 16316-16323 (electricity industry, electricity residential, coal industry, ...) under the labels electricity, coal, gas, oil, ...; E16302 tests the policy gas total instead of the baseline one; labels say 2022 = 100 where baseline = 100.</t>
         </is>
       </c>
       <c r="J78" s="58" t="inlineStr">
         <is>
-          <t>Point rows 16398-16405 to the average-price rows of each fuel; test the baseline gas total in E16317; relabel "baseline = 100".</t>
+          <t>Point rows 16383-16390 to the average-price rows of each fuel; test the baseline gas total in E16302; relabel "baseline = 100".</t>
         </is>
       </c>
       <c r="K78" s="58" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="S78" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T78" s="58" t="inlineStr">
@@ -8378,7 +8378,7 @@
       <c r="R79" s="58" t="inlineStr"/>
       <c r="S79" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T79" s="58" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="H80" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 2322-2325 (policy 8653-8656), 7789-7792</t>
+          <t>Mitigation rows 2322-2325 (policy 8638-8641), 7775-7778</t>
         </is>
       </c>
       <c r="I80" s="58" t="inlineStr">
@@ -8472,7 +8472,7 @@
       <c r="R80" s="58" t="inlineStr"/>
       <c r="S80" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T80" s="58" t="inlineStr">
@@ -8562,7 +8562,7 @@
       <c r="R81" s="58" t="inlineStr"/>
       <c r="S81" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T81" s="58" t="inlineStr">
@@ -8656,7 +8656,7 @@
       <c r="R82" s="58" t="inlineStr"/>
       <c r="S82" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T82" s="58" t="inlineStr">
@@ -8750,7 +8750,7 @@
       <c r="R83" s="58" t="inlineStr"/>
       <c r="S83" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T83" s="58" t="inlineStr">
@@ -8848,7 +8848,7 @@
       <c r="R84" s="58" t="inlineStr"/>
       <c r="S84" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T84" s="58" t="inlineStr">
@@ -8942,7 +8942,7 @@
       <c r="R85" s="58" t="inlineStr"/>
       <c r="S85" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T85" s="58" t="inlineStr">
@@ -8985,7 +8985,7 @@
       </c>
       <c r="H86" s="58" t="inlineStr">
         <is>
-          <t>Mitigation row 7820</t>
+          <t>Mitigation row 7806</t>
         </is>
       </c>
       <c r="I86" s="58" t="inlineStr">
@@ -9032,7 +9032,7 @@
       <c r="R86" s="58" t="inlineStr"/>
       <c r="S86" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T86" s="58" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="S87" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T87" s="58" t="inlineStr">
@@ -9224,7 +9224,7 @@
       <c r="R88" s="58" t="inlineStr"/>
       <c r="S88" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T88" s="58" t="inlineStr">
@@ -9318,7 +9318,7 @@
       <c r="R89" s="58" t="inlineStr"/>
       <c r="S89" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T89" s="58" t="inlineStr">
@@ -9408,7 +9408,7 @@
       <c r="R90" s="58" t="inlineStr"/>
       <c r="S90" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T90" s="58" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="S91" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T91" s="58" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="H92" s="58" t="inlineStr">
         <is>
-          <t>Mitigation C2199:C2201 ('Tax in nominal or real terms?', 'Exponential option or linear' twice) beside K2199:M2201 (road, residential, industrial additional efficiency, MTInputs F243-F245); E2385 (LPG 'Road'), E2386 (kerosene 'Industry') on all-sector rows (codes shp.lpg.all, shp.ker.all); D5615, D5722, D6072, D6083 'Other oil pinducts'</t>
+          <t>Mitigation C2199:C2201 ('Tax in nominal or real terms?', 'Exponential option or linear' twice) beside K2199:M2201 (road, residential, industrial additional efficiency, MTInputs F243-F245); E2385 (LPG 'Road'), E2386 (kerosene 'Industry') on all-sector rows (codes shp.lpg.all, shp.ker.all); D5615, D5711, D6058, D6069 'Other oil pinducts'</t>
         </is>
       </c>
       <c r="I92" s="58" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="S92" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T92" s="58" t="inlineStr">
@@ -9651,12 +9651,12 @@
       </c>
       <c r="H93" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 5667-5676, 5714, 5727-5728 (iron &amp; steel block; M5667 = N2446)</t>
+          <t>Mitigation rows 5667-5676, 5703, 5727-5728 (iron &amp; steel block; M5667 = N2446)</t>
         </is>
       </c>
       <c r="I93" s="58" t="inlineStr">
         <is>
-          <t>An EF-weighted average price (5714), an elasticity table (5668-5676) and 'Fuel'/'Average' demand and efficiency multiples (5727-5728) are computed but referenced nowhere; M5667 takes next year's GDP growth (N2446).</t>
+          <t>An EF-weighted average price (5703), an elasticity table (5668-5676) and 'Fuel'/'Average' demand and efficiency multiples (5727-5728) are computed but referenced nowhere; M5667 takes next year's GDP growth (N2446).</t>
         </is>
       </c>
       <c r="J93" s="58" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="S93" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T93" s="58" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="S94" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T94" s="58" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="S95" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T95" s="58" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="S96" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T96" s="58" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="S97" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T97" s="58" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="S98" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T98" s="58" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="S99" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T99" s="58" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="S100" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T100" s="58" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="S101" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T101" s="58" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="S102" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T102" s="58" t="inlineStr">
@@ -10646,7 +10646,7 @@
       <c r="R103" s="58" t="inlineStr"/>
       <c r="S103" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T103" s="58" t="inlineStr">
@@ -10740,7 +10740,7 @@
       <c r="R104" s="58" t="inlineStr"/>
       <c r="S104" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T104" s="58" t="inlineStr">
@@ -10834,7 +10834,7 @@
       <c r="R105" s="58" t="inlineStr"/>
       <c r="S105" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T105" s="58" t="inlineStr">
@@ -10924,7 +10924,7 @@
       <c r="R106" s="58" t="inlineStr"/>
       <c r="S106" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T106" s="58" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="R107" s="58" t="inlineStr"/>
       <c r="S107" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T107" s="58" t="inlineStr">
@@ -11104,7 +11104,7 @@
       <c r="R108" s="58" t="inlineStr"/>
       <c r="S108" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T108" s="58" t="inlineStr">
@@ -11194,7 +11194,7 @@
       <c r="R109" s="58" t="inlineStr"/>
       <c r="S109" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T109" s="58" t="inlineStr">
@@ -11284,7 +11284,7 @@
       <c r="R110" s="58" t="inlineStr"/>
       <c r="S110" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T110" s="58" t="inlineStr">
@@ -11374,7 +11374,7 @@
       <c r="R111" s="58" t="inlineStr"/>
       <c r="S111" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T111" s="58" t="inlineStr">
@@ -11468,7 +11468,7 @@
       <c r="R112" s="58" t="inlineStr"/>
       <c r="S112" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T112" s="58" t="inlineStr">
@@ -11511,17 +11511,17 @@
       </c>
       <c r="H113" s="58" t="inlineStr">
         <is>
-          <t>Manual inputs rows 234-240; Mitigation row 17683</t>
+          <t>Manual inputs rows 234-240; Mitigation row 17668</t>
         </is>
       </c>
       <c r="I113" s="58" t="inlineStr">
         <is>
-          <t>The SCC block of Manual inputs is read by nothing; the Manual option of NSCCSource / GSCCSource takes the path typed on Mitigation row 17683.</t>
+          <t>The SCC block of Manual inputs is read by nothing; the Manual option of NSCCSource / GSCCSource takes the path typed on Mitigation row 17668.</t>
         </is>
       </c>
       <c r="J113" s="58" t="inlineStr">
         <is>
-          <t>Mitigation row 17683 = 'Manual inputs'!J237 (NSCC) / J240 (GSCC).</t>
+          <t>Mitigation row 17668 = 'Manual inputs'!J237 (NSCC) / J240 (GSCC).</t>
         </is>
       </c>
       <c r="K113" s="58" t="inlineStr">
@@ -11562,7 +11562,7 @@
       <c r="R113" s="58" t="inlineStr"/>
       <c r="S113" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T113" s="58" t="inlineStr">
@@ -11652,7 +11652,7 @@
       <c r="R114" s="58" t="inlineStr"/>
       <c r="S114" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T114" s="58" t="inlineStr">
@@ -11742,7 +11742,7 @@
       <c r="R115" s="58" t="inlineStr"/>
       <c r="S115" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T115" s="58" t="inlineStr">
@@ -11832,7 +11832,7 @@
       <c r="R116" s="58" t="inlineStr"/>
       <c r="S116" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T116" s="58" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="H117" s="58" t="inlineStr">
         <is>
-          <t>Mitigation E2736 (policy E9067) = row 270 = MTInputs F132 (YearConsSubPha)</t>
+          <t>Mitigation E2736 (policy E9052) = row 270 = MTInputs F132 (YearConsSubPha)</t>
         </is>
       </c>
       <c r="I117" s="58" t="inlineStr">
         <is>
-          <t>The additional renewable subsidy (MTInputs 355) starts in the year the consumer fuel subsidies start to be phased out; it has no start-year input of its own.</t>
+          <t>The additional renewable subsidy (MTInputs 353) starts in the year the consumer fuel subsidies start to be phased out; it has no start-year input of its own.</t>
         </is>
       </c>
       <c r="J117" s="58" t="inlineStr">
@@ -11926,7 +11926,7 @@
       <c r="R117" s="58" t="inlineStr"/>
       <c r="S117" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T117" s="58" t="inlineStr">
@@ -11969,17 +11969,17 @@
       </c>
       <c r="H118" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 7897-7903 (policy +6317)</t>
+          <t>Mitigation rows 7883-7889 (policy +6316)</t>
         </is>
       </c>
       <c r="I118" s="58" t="inlineStr">
         <is>
-          <t>Rows 7897-7900 = (row 2743 + row 2745) x generation, but row 2745 already equals row 2743 minus the additional subsidy, so the base subsidy enters twice; hydro (7899) ignores RenewableSubsidyHydro; biomass has no row; 7903 enters total revenue (row 8023).</t>
+          <t>Rows 7883-7886 = (row 2743 + row 2745) x generation, but row 2745 already equals row 2743 minus the additional subsidy, so the base subsidy enters twice; hydro (7885) ignores RenewableSubsidyHydro; biomass has no row; 7889 enters total revenue (row 8009).</t>
         </is>
       </c>
       <c r="J118" s="58" t="inlineStr">
         <is>
-          <t>Rows 7897-7901 = the subsidy by type (rows 3148-3152) x generation.</t>
+          <t>Rows 7883-7887 = the subsidy by type (rows 3148-3152) x generation.</t>
         </is>
       </c>
       <c r="K118" s="58" t="inlineStr">
@@ -12020,7 +12020,7 @@
       <c r="R118" s="58" t="inlineStr"/>
       <c r="S118" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T118" s="58" t="inlineStr">
@@ -12118,7 +12118,7 @@
       <c r="R119" s="58" t="inlineStr"/>
       <c r="S119" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T119" s="58" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="H120" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 3615, 3644, 3663, 7888, 7749 (policy +6331 / +6317)</t>
+          <t>Mitigation rows 3615, 3644, 3663, 7874, 7735 (policy +6316 / +6316)</t>
         </is>
       </c>
       <c r="I120" s="58" t="inlineStr">
         <is>
-          <t>The rebate includes VAT (carbon cost x pass-through x (1 + VAT)) and enters total revenue through row 7749, while the VAT on the carbon cost is never counted as revenue.</t>
+          <t>The rebate includes VAT (carbon cost x pass-through x (1 + VAT)) and enters total revenue through row 7735, while the VAT on the carbon cost is never counted as revenue.</t>
         </is>
       </c>
       <c r="J120" s="58" t="inlineStr">
@@ -12212,7 +12212,7 @@
       <c r="R120" s="58" t="inlineStr"/>
       <c r="S120" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T120" s="58" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H121" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 3602, 3631, 3660, 7885, 7762</t>
+          <t>Mitigation rows 3602, 3631, 3660, 7871, 7748</t>
         </is>
       </c>
       <c r="I121" s="58" t="inlineStr">
         <is>
-          <t>The revenue memo 3660 (and 7762) = manual excise x consumption in every year, while the price includes only the change since the last historical year x pass-through.</t>
+          <t>The revenue memo 3660 (and 7748) = manual excise x consumption in every year, while the price includes only the change since the last historical year x pass-through.</t>
         </is>
       </c>
       <c r="J121" s="58" t="inlineStr">
@@ -12306,7 +12306,7 @@
       <c r="R121" s="58" t="inlineStr"/>
       <c r="S121" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T121" s="58" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="H122" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 8708-8719 (policy copies of 2377-2388)</t>
+          <t>Mitigation rows 8693-8704 (policy copies of 2377-2388)</t>
         </is>
       </c>
       <c r="I122" s="58" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="J122" s="58" t="inlineStr">
         <is>
-          <t>In rows 8708-8719 refer to the policy block ($D$8700, L$8706) instead of $D$2369 and L$2375.</t>
+          <t>In rows 8693-8704 refer to the policy block ($D$8685, L$8691) instead of $D$2369 and L$2375.</t>
         </is>
       </c>
       <c r="K122" s="58" t="inlineStr">
@@ -12404,7 +12404,7 @@
       <c r="R122" s="58" t="inlineStr"/>
       <c r="S122" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T122" s="58" t="inlineStr">
@@ -12498,7 +12498,7 @@
       <c r="R123" s="58" t="inlineStr"/>
       <c r="S123" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T123" s="58" t="inlineStr">
@@ -12541,17 +12541,17 @@
       </c>
       <c r="H124" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 2734-2735, 2743, 2745 (MTInputs 354-355)</t>
+          <t>Mitigation rows 2734-2735, 2743, 2745 (MTInputs 352-353)</t>
         </is>
       </c>
       <c r="I124" s="58" t="inlineStr">
         <is>
-          <t>MTInputs 354-355 are labelled $/kWh nominal but enter the real cost and revenue without deflation (row 2743 = -E2734). A formula that contradicts its label: reclassified as a bug by the user (2026-10-19).</t>
+          <t>MTInputs 352-353 are labelled $/kWh nominal but enter the real cost and revenue without deflation (row 2743 = -E2734). A formula that contradicts its label: reclassified as a bug by the user (2026-10-19).</t>
         </is>
       </c>
       <c r="J124" s="58" t="inlineStr">
         <is>
-          <t>Deflate the nominal inputs (rows 2734-2735) by the CPI index before they enter row 2743, or relabel MTInputs 354-355 as real.</t>
+          <t>Deflate the nominal inputs (rows 2734-2735) by the CPI index before they enter row 2743, or relabel MTInputs 352-353 as real.</t>
         </is>
       </c>
       <c r="K124" s="58" t="inlineStr">
@@ -12592,7 +12592,7 @@
       <c r="R124" s="58" t="inlineStr"/>
       <c r="S124" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T124" s="58" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="H125" s="58" t="inlineStr">
         <is>
-          <t>Mitigation row 2555 (policy 8886)</t>
+          <t>Mitigation row 2555 (policy 8871)</t>
         </is>
       </c>
       <c r="I125" s="58" t="inlineStr">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="J125" s="58" t="inlineStr">
         <is>
-          <t>Point row 2555 (and policy 8886) at the residential gas ETS row 1715.</t>
+          <t>Point row 2555 (and policy 8871) at the residential gas ETS row 1715.</t>
         </is>
       </c>
       <c r="K125" s="58" t="inlineStr">
@@ -12686,7 +12686,7 @@
       <c r="R125" s="58" t="inlineStr"/>
       <c r="S125" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T125" s="58" t="inlineStr">
@@ -12776,7 +12776,7 @@
       <c r="R126" s="58" t="inlineStr"/>
       <c r="S126" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T126" s="58" t="inlineStr">
@@ -12866,7 +12866,7 @@
       <c r="R127" s="58" t="inlineStr"/>
       <c r="S127" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T127" s="58" t="inlineStr">
@@ -12960,7 +12960,7 @@
       <c r="R128" s="58" t="inlineStr"/>
       <c r="S128" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T128" s="58" t="inlineStr">
@@ -13003,12 +13003,12 @@
       </c>
       <c r="H129" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 18414, 18422-18427, 18441-18443, 18458-18460</t>
+          <t>Mitigation rows 18399, 18407-18412, 18426-18428, 18443-18445</t>
         </is>
       </c>
       <c r="I129" s="58" t="inlineStr">
         <is>
-          <t>F18414 = IF(target year &lt; 2030, (2030 - base)/(target year - base), 1) is at least 1, so the "&lt;1" branches of the Fixed and Historical blocks (rows 18441-18443, 18458-18460) never run, while the BAU block multiplies both the reduction (18422) and the level (18425: BAU x (1 - reduction x adj) x adj) by it: a 2025 BAU target is scaled up twice and the other types not at all. Found by the item 8 plan (v5.7).</t>
+          <t>F18399 = IF(target year &lt; 2030, (2030 - base)/(target year - base), 1) is at least 1, so the "&lt;1" branches of the Fixed and Historical blocks (rows 18426-18428, 18443-18445) never run, while the BAU block multiplies both the reduction (18407) and the level (18410: BAU x (1 - reduction x adj) x adj) by it: a 2025 BAU target is scaled up twice and the other types not at all. Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="J129" s="58" t="inlineStr">
@@ -13054,7 +13054,7 @@
       <c r="R129" s="58" t="inlineStr"/>
       <c r="S129" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T129" s="58" t="inlineStr">
@@ -13097,17 +13097,17 @@
       </c>
       <c r="H130" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 18497-18499</t>
+          <t>Mitigation rows 18482-18484</t>
         </is>
       </c>
       <c r="I130" s="58" t="inlineStr">
         <is>
-          <t>Rows 18497-18498 divide the start-year emissions by the target (G18446/F18494) while row 18499 divides the target by the start-year emissions; the chart rows 18509-18510 read 18499 for the unconditional line and 18498 (inverted) for the conditional one. Found by the item 8 plan (v5.7).</t>
+          <t>Rows 18482-18483 divide the start-year emissions by the target (G18431/F18479) while row 18484 divides the target by the start-year emissions; the chart rows 18494-18495 read 18484 for the unconditional line and 18483 (inverted) for the conditional one. Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="J130" s="58" t="inlineStr">
         <is>
-          <t>Use target / start-year emissions in rows 18497-18498, as 18499.</t>
+          <t>Use target / start-year emissions in rows 18482-18483, as 18484.</t>
         </is>
       </c>
       <c r="K130" s="58" t="inlineStr">
@@ -13148,7 +13148,7 @@
       <c r="R130" s="58" t="inlineStr"/>
       <c r="S130" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T130" s="58" t="inlineStr">
@@ -13191,17 +13191,17 @@
       </c>
       <c r="H131" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 18458-18460</t>
+          <t>Mitigation rows 18443-18445</t>
         </is>
       </c>
       <c r="I131" s="58" t="inlineStr">
         <is>
-          <t>Rows 18458-18460 return the cut (F18455 x adj) when adj &lt; 1 and the level otherwise; harmless today only because adj &lt; 1 never happens (L119). Found by the item 8 plan (v5.7).</t>
+          <t>Rows 18443-18445 return the cut (F18440 x adj) when adj &lt; 1 and the level otherwise; harmless today only because adj &lt; 1 never happens (L119). Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="J131" s="58" t="inlineStr">
         <is>
-          <t>Return F18452 - F18455 x adj (the level), as the Fixed block.</t>
+          <t>Return F18437 - F18440 x adj (the level), as the Fixed block.</t>
         </is>
       </c>
       <c r="K131" s="58" t="inlineStr">
@@ -13242,7 +13242,7 @@
       <c r="R131" s="58" t="inlineStr"/>
       <c r="S131" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T131" s="58" t="inlineStr">
@@ -13285,17 +13285,17 @@
       </c>
       <c r="H132" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 18476-18477</t>
+          <t>Mitigation rows 18461-18462</t>
         </is>
       </c>
       <c r="I132" s="58" t="inlineStr">
         <is>
-          <t>The excludes-LULUCF branch adds $J$18465 where the LULUCF emissions are in column I (I18465 = G - F). J18465 is not blank: it holds the non-CO2 emissions (F - H, 254.9 Mt for Egypt), so non-CO2 is counted twice and LULUCF is missed (cell plan 2026-10-20 corrected the register). Found by the item 8 plan (v5.7).</t>
+          <t>The excludes-LULUCF branch adds $J$18450 where the LULUCF emissions are in column I (I18450 = G - F). J18450 is not blank: it holds the non-CO2 emissions (F - H, 254.9 Mt for Egypt), so non-CO2 is counted twice and LULUCF is missed (cell plan 2026-10-20 corrected the register). Found by the item 8 plan (v5.7).</t>
         </is>
       </c>
       <c r="J132" s="58" t="inlineStr">
         <is>
-          <t>Add I18465 (LULUCF) instead of J18465 (non-CO2).</t>
+          <t>Add I18450 (LULUCF) instead of J18450 (non-CO2).</t>
         </is>
       </c>
       <c r="K132" s="58" t="inlineStr">
@@ -13336,7 +13336,7 @@
       <c r="R132" s="58" t="inlineStr"/>
       <c r="S132" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T132" s="58" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="H133" s="58" t="inlineStr">
         <is>
-          <t>Mitigation row 18466</t>
+          <t>Mitigation row 18451</t>
         </is>
       </c>
       <c r="I133" s="58" t="inlineStr">
@@ -13430,7 +13430,7 @@
       <c r="R133" s="58" t="inlineStr"/>
       <c r="S133" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T133" s="58" t="inlineStr">
@@ -13520,7 +13520,7 @@
       <c r="R134" s="58" t="inlineStr"/>
       <c r="S134" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T134" s="58" t="inlineStr">
@@ -13610,7 +13610,7 @@
       <c r="R135" s="58" t="inlineStr"/>
       <c r="S135" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T135" s="58" t="inlineStr">
@@ -13700,7 +13700,7 @@
       <c r="R136" s="58" t="inlineStr"/>
       <c r="S136" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T136" s="58" t="inlineStr">
@@ -13790,7 +13790,7 @@
       <c r="R137" s="58" t="inlineStr"/>
       <c r="S137" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T137" s="58" t="inlineStr">
@@ -13880,7 +13880,7 @@
       <c r="R138" s="58" t="inlineStr"/>
       <c r="S138" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T138" s="58" t="inlineStr">
@@ -13970,7 +13970,7 @@
       <c r="R139" s="58" t="inlineStr"/>
       <c r="S139" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T139" s="58" t="inlineStr">
@@ -14056,7 +14056,7 @@
       <c r="R140" s="58" t="inlineStr"/>
       <c r="S140" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T140" s="58" t="inlineStr">
@@ -14146,7 +14146,7 @@
       <c r="R141" s="58" t="inlineStr"/>
       <c r="S141" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T141" s="58" t="inlineStr">
@@ -14236,7 +14236,7 @@
       <c r="R142" s="58" t="inlineStr"/>
       <c r="S142" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T142" s="58" t="inlineStr">
@@ -14326,7 +14326,7 @@
       <c r="R143" s="58" t="inlineStr"/>
       <c r="S143" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T143" s="58" t="inlineStr">
@@ -14416,7 +14416,7 @@
       <c r="R144" s="58" t="inlineStr"/>
       <c r="S144" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T144" s="58" t="inlineStr">
@@ -14506,7 +14506,7 @@
       <c r="R145" s="58" t="inlineStr"/>
       <c r="S145" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T145" s="58" t="inlineStr">
@@ -14596,7 +14596,7 @@
       <c r="R146" s="58" t="inlineStr"/>
       <c r="S146" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T146" s="58" t="inlineStr">
@@ -14686,7 +14686,7 @@
       <c r="R147" s="58" t="inlineStr"/>
       <c r="S147" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T147" s="58" t="inlineStr">
@@ -14776,7 +14776,7 @@
       <c r="R148" s="58" t="inlineStr"/>
       <c r="S148" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T148" s="58" t="inlineStr">
@@ -14866,7 +14866,7 @@
       <c r="R149" s="58" t="inlineStr"/>
       <c r="S149" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T149" s="58" t="inlineStr">
@@ -14956,7 +14956,7 @@
       <c r="R150" s="58" t="inlineStr"/>
       <c r="S150" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T150" s="58" t="inlineStr">
@@ -15046,7 +15046,7 @@
       <c r="R151" s="58" t="inlineStr"/>
       <c r="S151" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T151" s="58" t="inlineStr">
@@ -15132,7 +15132,7 @@
       <c r="R152" s="58" t="inlineStr"/>
       <c r="S152" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T152" s="58" t="inlineStr">
@@ -15222,7 +15222,7 @@
       <c r="R153" s="58" t="inlineStr"/>
       <c r="S153" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T153" s="58" t="inlineStr">
@@ -15312,7 +15312,7 @@
       <c r="R154" s="58" t="inlineStr"/>
       <c r="S154" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T154" s="58" t="inlineStr">
@@ -15398,7 +15398,7 @@
       <c r="R155" s="58" t="inlineStr"/>
       <c r="S155" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T155" s="58" t="inlineStr">
@@ -15496,7 +15496,7 @@
       <c r="R156" s="58" t="inlineStr"/>
       <c r="S156" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T156" s="58" t="inlineStr">
@@ -15594,7 +15594,7 @@
       <c r="R157" s="58" t="inlineStr"/>
       <c r="S157" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T157" s="58" t="inlineStr">
@@ -15688,7 +15688,7 @@
       <c r="R158" s="58" t="inlineStr"/>
       <c r="S158" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T158" s="58" t="inlineStr">
@@ -15782,7 +15782,7 @@
       <c r="R159" s="58" t="inlineStr"/>
       <c r="S159" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T159" s="58" t="inlineStr">
@@ -15825,22 +15825,22 @@
       </c>
       <c r="H160" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 6252, 6257 (policy 12569, 12574)</t>
+          <t>Mitigation rows 6238, 6243 (policy 12554, 12559)</t>
         </is>
       </c>
       <c r="I160" s="58" t="inlineStr">
         <is>
-          <t>The net revenue rows (USD and % of GDP) read the next column of rows 8038 and 8043 (K6252 = L8038 ... AD6252 = AE8038), so each year shows the next year's net revenue. Report only (rows 6253, 6258 read them). Found by the read-of-later-years scan of legacy (v6.2, user 2026-10-20).</t>
+          <t>The net revenue rows (USD and % of GDP) read the next column of rows 8024 and 8029 (K6238 = L8024 ... AD6238 = AE8024), so each year shows the next year's net revenue. Report only (rows 6239, 6244 read them). Found by the read-of-later-years scan of legacy (v6.2, user 2026-10-20).</t>
         </is>
       </c>
       <c r="J160" s="58" t="inlineStr">
         <is>
-          <t>K6252 =K8038 and K6257 =K8043, filled K:AD; policy rows 12569, 12574 the same (+6,317).</t>
+          <t>K6238 =K8024 and K6243 =K8029, filled K:AD; policy rows 12554, 12559 the same (+6,316).</t>
         </is>
       </c>
       <c r="K160" s="58" t="inlineStr">
         <is>
-          <t>Each year reports the next year's net revenue (USD and % of GDP). prototype: Not in the prototype (its revenue rows read the same year; reporting rebuilt). Legacy fix: K6252 =K8038 and K6257 =K8043, filled K:AD.</t>
+          <t>Each year reports the next year's net revenue (USD and % of GDP). prototype: Not in the prototype (its revenue rows read the same year; reporting rebuilt). Legacy fix: K6238 =K8024 and K6243 =K8029, filled K:AD.</t>
         </is>
       </c>
       <c r="L160" s="58" t="inlineStr">
@@ -15876,7 +15876,7 @@
       <c r="R160" s="58" t="inlineStr"/>
       <c r="S160" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T160" s="58" t="inlineStr">
@@ -15919,22 +15919,22 @@
       </c>
       <c r="H161" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 2785-2788, 2947-2951, 7897-7900 (against 2743, 2745)</t>
+          <t>Mitigation rows 2785-2788, 2947-2951, 7883-7886 (against 2743, 2745)</t>
         </is>
       </c>
       <c r="I161" s="58" t="inlineStr">
         <is>
-          <t>The rows add L2743 + L2745, but L2745 already includes L2743, so the baseline renewable subsidy is counted twice. Only when MTInputs row 354 (RenewableSubsidyBL) is not zero; 0 for Egypt. Found by the cell plans (user 2026-10-20: a bug).</t>
+          <t>The rows add L2743 + L2745, but L2745 already includes L2743, so the baseline renewable subsidy is counted twice. Only when MTInputs row 352 (RenewableSubsidyBL) is not zero; 0 for Egypt. Found by the cell plans (user 2026-10-20: a bug).</t>
         </is>
       </c>
       <c r="J161" s="58" t="inlineStr">
         <is>
-          <t>In rows 2785-2788, 2947-2951 and 7897-7900 drop the + L2743 term (L2745 already includes it); policy rows the same (+6,331).</t>
+          <t>In rows 2785-2788, 2947-2951 and 7883-7886 drop the + L2743 term (L2745 already includes it); policy rows the same (+6,316).</t>
         </is>
       </c>
       <c r="K161" s="58" t="inlineStr">
         <is>
-          <t>With a baseline renewable subsidy (MTInputs 354) the subsidy cost is counted twice. prototype: Fixed (prototype: one renewable subsidy row rnsp = baseline + additional, counted once).</t>
+          <t>With a baseline renewable subsidy (MTInputs 352) the subsidy cost is counted twice. prototype: Fixed (prototype: one renewable subsidy row rnsp = baseline + additional, counted once).</t>
         </is>
       </c>
       <c r="L161" s="58" t="inlineStr"/>
@@ -15962,7 +15962,7 @@
       <c r="R161" s="58" t="inlineStr"/>
       <c r="S161" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T161" s="58" t="inlineStr">
@@ -16005,17 +16005,17 @@
       </c>
       <c r="H162" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 18470-18471</t>
+          <t>Mitigation rows 18455-18456</t>
         </is>
       </c>
       <c r="I162" s="58" t="inlineStr">
         <is>
-          <t>F18471 (conditional) applies the cut to the target-year BAU intensity (F18469); F18470 (unconditional) applies it to the reference-year intensity (F18468). Found by the cell plans (user 2026-10-20: a bug).</t>
+          <t>F18456 (conditional) applies the cut to the target-year BAU intensity (F18454); F18455 (unconditional) applies it to the reference-year intensity (F18453). Found by the cell plans (user 2026-10-20: a bug).</t>
         </is>
       </c>
       <c r="J162" s="58" t="inlineStr">
         <is>
-          <t>F18471: apply the cut to the reference-year intensity F18468, as F18470 does.</t>
+          <t>F18456: apply the cut to the reference-year intensity F18453, as F18455 does.</t>
         </is>
       </c>
       <c r="K162" s="58" t="inlineStr">
@@ -16048,7 +16048,7 @@
       <c r="R162" s="58" t="inlineStr"/>
       <c r="S162" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T162" s="58" t="inlineStr">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="H163" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 466, 2442, 16185 (gdp.pre.lvl); 7736, 7756, 7999 (sub.new.usd); 7652-13977 (rev.ctr.coa)</t>
+          <t>Mitigation rows 466, 2442, 16170 (gdp.pre.lvl); 7722, 7742, 7985 (sub.new.usd); 7638-13962 (rev.ctr.coa)</t>
         </is>
       </c>
       <c r="I163" s="58" t="inlineStr">
@@ -16138,7 +16138,7 @@
       <c r="R163" s="58" t="inlineStr"/>
       <c r="S163" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T163" s="58" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="H164" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 7620, 13937 (oc.tot.); em.pm2.All.&lt;sector&gt; rows</t>
+          <t>Mitigation rows 7606, 13922 (oc.tot.); em.pm2.All.&lt;sector&gt; rows</t>
         </is>
       </c>
       <c r="I164" s="58" t="inlineStr">
@@ -16228,7 +16228,7 @@
       <c r="R164" s="58" t="inlineStr"/>
       <c r="S164" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T164" s="58" t="inlineStr">
@@ -16271,7 +16271,7 @@
       </c>
       <c r="H165" s="58" t="inlineStr">
         <is>
-          <t>Mitigation rows 7620, 13937 and the GHG total rows (nox.tot)</t>
+          <t>Mitigation rows 7606, 13922 and the GHG total rows (nox.tot)</t>
         </is>
       </c>
       <c r="I165" s="58" t="inlineStr">
@@ -16318,7 +16318,7 @@
       <c r="R165" s="58" t="inlineStr"/>
       <c r="S165" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T165" s="58" t="inlineStr">
@@ -16568,7 +16568,7 @@
       <c r="R4" s="58" t="inlineStr"/>
       <c r="S4" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T4" s="58" t="inlineStr">
@@ -16650,7 +16650,7 @@
       <c r="R5" s="58" t="inlineStr"/>
       <c r="S5" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T5" s="58" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="S6" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T6" s="58" t="inlineStr">
@@ -16822,7 +16822,7 @@
       <c r="R7" s="58" t="inlineStr"/>
       <c r="S7" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T7" s="58" t="inlineStr">
@@ -16908,7 +16908,7 @@
       <c r="R8" s="58" t="inlineStr"/>
       <c r="S8" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T8" s="58" t="inlineStr">
@@ -16990,7 +16990,7 @@
       <c r="R9" s="58" t="inlineStr"/>
       <c r="S9" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T9" s="58" t="inlineStr">
@@ -17072,7 +17072,7 @@
       <c r="R10" s="58" t="inlineStr"/>
       <c r="S10" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T10" s="58" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="J11" s="58" t="inlineStr">
         <is>
-          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6590; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The prototype floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
+          <t>Traced (v5.6): legacy process emissions = 2023 inventory x the year-on-year growth of industrial energy CO2 (row 6576; 2024: +16.8%, the rebound after the 2023 demand shock, so 56.9 -&gt; 66.5). The prototype floored that growth at 0 (a departure: removed in v5.6, as legacy). The remaining gap is the industrial energy CO2 path, part of the fuel-use gap (I14).</t>
         </is>
       </c>
       <c r="K11" s="58" t="n"/>
@@ -17158,7 +17158,7 @@
       <c r="R11" s="58" t="inlineStr"/>
       <c r="S11" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T11" s="58" t="inlineStr">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="J12" s="58" t="inlineStr">
         <is>
-          <t>Checked (v5.6): energy N2O moves with energy CO2 as legacy (row 7563 = previous x CO2 ratio). Production for fuel-supply methane differs: now issue I66.</t>
+          <t>Checked (v5.6): energy N2O moves with energy CO2 as legacy (row 7549 = previous x CO2 ratio). Production for fuel-supply methane differs: now issue I66.</t>
         </is>
       </c>
       <c r="K12" s="58" t="n"/>
@@ -17244,7 +17244,7 @@
       <c r="R12" s="58" t="inlineStr"/>
       <c r="S12" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T12" s="58" t="inlineStr">
@@ -17326,7 +17326,7 @@
       <c r="R13" s="58" t="inlineStr"/>
       <c r="S13" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T13" s="58" t="inlineStr">
@@ -17416,7 +17416,7 @@
       </c>
       <c r="S14" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T14" s="58" t="inlineStr">
@@ -17464,7 +17464,7 @@
       </c>
       <c r="I15" s="58" t="inlineStr">
         <is>
-          <t>Legacy row 7534 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the prototype calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
+          <t>Legacy row 7520 ("Adjust EFs to match energy-related CO2 to UNFCCC inventories?", Yes* by default) multiplies every CO2 EF by the inventory energy CO2 of the year before the base year over the estimate from the base-year energy balance (Egypt: 2021 inventory against 2022, 0.930), so CO2 is about 7% below uncalibrated EFs in every sector. The inventory has a break between 2021 and 2022 (I17: 211 to 252 Mt), which legacy carries into the factor. v4.11 replicates legacy (user 2026-10-18: go with legacy); before, the prototype calibrated in 2024 and kept the switch off (user decisions v3.2, v3.4).</t>
         </is>
       </c>
       <c r="J15" s="58" t="inlineStr">
@@ -17502,7 +17502,7 @@
       <c r="R15" s="58" t="inlineStr"/>
       <c r="S15" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T15" s="58" t="inlineStr">
@@ -17588,7 +17588,7 @@
       <c r="R16" s="58" t="inlineStr"/>
       <c r="S16" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T16" s="58" t="inlineStr">
@@ -17670,7 +17670,7 @@
       <c r="R17" s="58" t="inlineStr"/>
       <c r="S17" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T17" s="58" t="inlineStr">
@@ -17756,7 +17756,7 @@
       <c r="R18" s="58" t="inlineStr"/>
       <c r="S18" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T18" s="58" t="inlineStr">
@@ -17846,7 +17846,7 @@
       <c r="R19" s="58" t="inlineStr"/>
       <c r="S19" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T19" s="58" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="S20" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T20" s="58" t="inlineStr">
@@ -18022,7 +18022,7 @@
       <c r="R21" s="58" t="inlineStr"/>
       <c r="S21" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T21" s="58" t="inlineStr">
@@ -18108,7 +18108,7 @@
       </c>
       <c r="S22" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T22" s="58" t="inlineStr">
@@ -18156,7 +18156,7 @@
       </c>
       <c r="I23" s="58" t="inlineStr">
         <is>
-          <t>Legacy rows 7297-7321 feed the air-pollution module CH4 by sector: oil and gas extraction methane under "other", agriculture and waste methane under "food &amp; forestry" (waste is not food or forestry), no combustion CH4 (no factors in legacy). v3.12 replicates the allocation and adds the combustion CH4 of each sector (GAINS factors, section 14), with all fossil fuel supply methane (extraction, downstream gas, coal mining, biomass) under "other".</t>
+          <t>Legacy rows 7283-7307 feed the air-pollution module CH4 by sector: oil and gas extraction methane under "other", agriculture and waste methane under "food &amp; forestry" (waste is not food or forestry), no combustion CH4 (no factors in legacy). v3.12 replicates the allocation and adds the combustion CH4 of each sector (GAINS factors, section 14), with all fossil fuel supply methane (extraction, downstream gas, coal mining, biomass) under "other".</t>
         </is>
       </c>
       <c r="J23" s="58" t="inlineStr">
@@ -18194,7 +18194,7 @@
       <c r="R23" s="58" t="inlineStr"/>
       <c r="S23" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T23" s="58" t="inlineStr">
@@ -18280,7 +18280,7 @@
       <c r="R24" s="58" t="inlineStr"/>
       <c r="S24" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T24" s="58" t="inlineStr">
@@ -18328,7 +18328,7 @@
       </c>
       <c r="I25" s="58" t="inlineStr">
         <is>
-          <t>Legacy's effective carbon rate (row 16662) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The prototype replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
+          <t>Legacy's effective carbon rate (row 16647) and total carbon price (F5d) divide revenue net of subsidies, VAT included, by CO2; the OECD effective carbon rate counts carbon taxes, fuel excises and permit prices only. The prototype replicates the legacy definition (section 17, v3.15) and says so in the note; Egypt has negative rates (subsidies exceed taxes).</t>
         </is>
       </c>
       <c r="J25" s="58" t="inlineStr">
@@ -18366,7 +18366,7 @@
       <c r="R25" s="58" t="inlineStr"/>
       <c r="S25" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T25" s="58" t="inlineStr">
@@ -18452,7 +18452,7 @@
       <c r="R26" s="58" t="inlineStr"/>
       <c r="S26" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T26" s="58" t="inlineStr">
@@ -18530,7 +18530,7 @@
       <c r="R27" s="58" t="inlineStr"/>
       <c r="S27" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T27" s="58" t="inlineStr">
@@ -18612,7 +18612,7 @@
       </c>
       <c r="S28" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T28" s="58" t="inlineStr">
@@ -18694,7 +18694,7 @@
       <c r="R29" s="58" t="inlineStr"/>
       <c r="S29" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T29" s="58" t="inlineStr">
@@ -18772,7 +18772,7 @@
       <c r="R30" s="58" t="inlineStr"/>
       <c r="S30" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T30" s="58" t="inlineStr">
@@ -18854,7 +18854,7 @@
       <c r="R31" s="58" t="inlineStr"/>
       <c r="S31" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T31" s="58" t="inlineStr">
@@ -18936,7 +18936,7 @@
       <c r="R32" s="58" t="inlineStr"/>
       <c r="S32" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T32" s="58" t="inlineStr">
@@ -19022,7 +19022,7 @@
       <c r="R33" s="58" t="inlineStr"/>
       <c r="S33" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T33" s="58" t="inlineStr">
@@ -19104,7 +19104,7 @@
       <c r="R34" s="58" t="inlineStr"/>
       <c r="S34" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T34" s="58" t="inlineStr">
@@ -19190,7 +19190,7 @@
       </c>
       <c r="S35" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T35" s="58" t="inlineStr">
@@ -19268,7 +19268,7 @@
       <c r="R36" s="58" t="inlineStr"/>
       <c r="S36" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T36" s="58" t="inlineStr">
@@ -19346,7 +19346,7 @@
       <c r="R37" s="58" t="inlineStr"/>
       <c r="S37" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T37" s="58" t="inlineStr">
@@ -19424,7 +19424,7 @@
       <c r="R38" s="58" t="inlineStr"/>
       <c r="S38" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T38" s="58" t="inlineStr">
@@ -19506,7 +19506,7 @@
       </c>
       <c r="S39" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T39" s="58" t="inlineStr">
@@ -19584,7 +19584,7 @@
       <c r="R40" s="58" t="inlineStr"/>
       <c r="S40" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T40" s="58" t="inlineStr">
@@ -19666,7 +19666,7 @@
       <c r="R41" s="58" t="inlineStr"/>
       <c r="S41" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T41" s="58" t="inlineStr">
@@ -19748,7 +19748,7 @@
       <c r="R42" s="58" t="inlineStr"/>
       <c r="S42" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T42" s="58" t="inlineStr">
@@ -19830,7 +19830,7 @@
       <c r="R43" s="58" t="inlineStr"/>
       <c r="S43" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T43" s="58" t="inlineStr">
@@ -19912,7 +19912,7 @@
       <c r="R44" s="58" t="inlineStr"/>
       <c r="S44" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T44" s="58" t="inlineStr">
@@ -19998,7 +19998,7 @@
       <c r="R45" s="58" t="inlineStr"/>
       <c r="S45" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T45" s="58" t="inlineStr">
@@ -20080,7 +20080,7 @@
       <c r="R46" s="58" t="inlineStr"/>
       <c r="S46" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T46" s="58" t="inlineStr">
@@ -20166,7 +20166,7 @@
       </c>
       <c r="S47" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T47" s="58" t="inlineStr">
@@ -20248,7 +20248,7 @@
       <c r="R48" s="58" t="inlineStr"/>
       <c r="S48" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T48" s="58" t="inlineStr">
@@ -20330,7 +20330,7 @@
       <c r="R49" s="58" t="inlineStr"/>
       <c r="S49" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T49" s="58" t="inlineStr">
@@ -20408,7 +20408,7 @@
       <c r="R50" s="58" t="inlineStr"/>
       <c r="S50" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T50" s="58" t="inlineStr">
@@ -20494,7 +20494,7 @@
       <c r="R51" s="58" t="inlineStr"/>
       <c r="S51" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T51" s="58" t="inlineStr">
@@ -20580,7 +20580,7 @@
       <c r="R52" s="58" t="inlineStr"/>
       <c r="S52" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T52" s="58" t="inlineStr">
@@ -20666,7 +20666,7 @@
       <c r="R53" s="58" t="inlineStr"/>
       <c r="S53" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T53" s="58" t="inlineStr">
@@ -20748,7 +20748,7 @@
       <c r="R54" s="58" t="inlineStr"/>
       <c r="S54" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T54" s="58" t="inlineStr">
@@ -20834,7 +20834,7 @@
       </c>
       <c r="S55" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T55" s="58" t="inlineStr">
@@ -20916,7 +20916,7 @@
       <c r="R56" s="58" t="inlineStr"/>
       <c r="S56" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T56" s="58" t="inlineStr">
@@ -21002,7 +21002,7 @@
       <c r="R57" s="58" t="inlineStr"/>
       <c r="S57" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T57" s="58" t="inlineStr">
@@ -21084,7 +21084,7 @@
       <c r="R58" s="58" t="inlineStr"/>
       <c r="S58" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T58" s="58" t="inlineStr">
@@ -21162,7 +21162,7 @@
       <c r="R59" s="58" t="inlineStr"/>
       <c r="S59" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T59" s="58" t="inlineStr">
@@ -21244,7 +21244,7 @@
       <c r="R60" s="58" t="inlineStr"/>
       <c r="S60" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T60" s="58" t="inlineStr">
@@ -21326,7 +21326,7 @@
       <c r="R61" s="58" t="inlineStr"/>
       <c r="S61" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T61" s="58" t="inlineStr">
@@ -21408,7 +21408,7 @@
       <c r="R62" s="58" t="inlineStr"/>
       <c r="S62" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T62" s="58" t="inlineStr">
@@ -21490,7 +21490,7 @@
       <c r="R63" s="58" t="inlineStr"/>
       <c r="S63" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T63" s="58" t="inlineStr">
@@ -21576,7 +21576,7 @@
       <c r="R64" s="58" t="inlineStr"/>
       <c r="S64" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T64" s="58" t="inlineStr">
@@ -21654,7 +21654,7 @@
       <c r="R65" s="58" t="inlineStr"/>
       <c r="S65" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T65" s="58" t="inlineStr">
@@ -21736,7 +21736,7 @@
       </c>
       <c r="S66" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T66" s="58" t="inlineStr">
@@ -21814,7 +21814,7 @@
       <c r="R67" s="58" t="inlineStr"/>
       <c r="S67" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T67" s="58" t="inlineStr">
@@ -21892,7 +21892,7 @@
       <c r="R68" s="58" t="inlineStr"/>
       <c r="S68" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T68" s="58" t="inlineStr">
@@ -21974,7 +21974,7 @@
       <c r="R69" s="58" t="inlineStr"/>
       <c r="S69" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T69" s="58" t="inlineStr">
@@ -22052,7 +22052,7 @@
       <c r="R70" s="58" t="inlineStr"/>
       <c r="S70" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T70" s="58" t="inlineStr">
@@ -22130,7 +22130,7 @@
       <c r="R71" s="58" t="inlineStr"/>
       <c r="S71" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T71" s="58" t="inlineStr">
@@ -22212,7 +22212,7 @@
       <c r="R72" s="58" t="inlineStr"/>
       <c r="S72" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T72" s="58" t="inlineStr">
@@ -22290,7 +22290,7 @@
       <c r="R73" s="58" t="inlineStr"/>
       <c r="S73" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T73" s="58" t="inlineStr">
@@ -22372,7 +22372,7 @@
       <c r="R74" s="58" t="inlineStr"/>
       <c r="S74" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T74" s="58" t="inlineStr">
@@ -22454,7 +22454,7 @@
       <c r="R75" s="58" t="inlineStr"/>
       <c r="S75" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T75" s="58" t="inlineStr">
@@ -22532,7 +22532,7 @@
       <c r="R76" s="58" t="inlineStr"/>
       <c r="S76" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T76" s="58" t="inlineStr">
@@ -22610,7 +22610,7 @@
       <c r="R77" s="58" t="inlineStr"/>
       <c r="S77" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T77" s="58" t="inlineStr">
@@ -22688,7 +22688,7 @@
       <c r="R78" s="58" t="inlineStr"/>
       <c r="S78" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T78" s="58" t="inlineStr">
@@ -22770,7 +22770,7 @@
       </c>
       <c r="S79" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T79" s="58" t="inlineStr">
@@ -22852,7 +22852,7 @@
       <c r="R80" s="58" t="inlineStr"/>
       <c r="S80" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T80" s="58" t="inlineStr">
@@ -22934,7 +22934,7 @@
       <c r="R81" s="58" t="inlineStr"/>
       <c r="S81" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T81" s="58" t="inlineStr">
@@ -23012,7 +23012,7 @@
       <c r="R82" s="58" t="inlineStr"/>
       <c r="S82" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T82" s="58" t="inlineStr">
@@ -23102,7 +23102,7 @@
       <c r="R83" s="58" t="inlineStr"/>
       <c r="S83" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T83" s="58" t="inlineStr">
@@ -23188,7 +23188,7 @@
       <c r="R84" s="58" t="inlineStr"/>
       <c r="S84" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T84" s="58" t="inlineStr">
@@ -23274,7 +23274,7 @@
       <c r="R85" s="58" t="inlineStr"/>
       <c r="S85" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T85" s="58" t="inlineStr">
@@ -23356,7 +23356,7 @@
       <c r="R86" s="58" t="inlineStr"/>
       <c r="S86" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T86" s="58" t="inlineStr">
@@ -23438,7 +23438,7 @@
       <c r="R87" s="58" t="inlineStr"/>
       <c r="S87" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T87" s="58" t="inlineStr">
@@ -23520,7 +23520,7 @@
       <c r="R88" s="58" t="inlineStr"/>
       <c r="S88" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T88" s="58" t="inlineStr">
@@ -23602,7 +23602,7 @@
       <c r="R89" s="58" t="inlineStr"/>
       <c r="S89" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T89" s="58" t="inlineStr">
@@ -23684,7 +23684,7 @@
       <c r="R90" s="58" t="inlineStr"/>
       <c r="S90" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T90" s="58" t="inlineStr">
@@ -23766,7 +23766,7 @@
       <c r="R91" s="58" t="inlineStr"/>
       <c r="S91" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T91" s="58" t="inlineStr">
@@ -23848,7 +23848,7 @@
       <c r="R92" s="58" t="inlineStr"/>
       <c r="S92" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T92" s="58" t="inlineStr">
@@ -23930,7 +23930,7 @@
       <c r="R93" s="58" t="inlineStr"/>
       <c r="S93" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T93" s="58" t="inlineStr">
@@ -24012,7 +24012,7 @@
       <c r="R94" s="58" t="inlineStr"/>
       <c r="S94" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T94" s="58" t="inlineStr">
@@ -24094,7 +24094,7 @@
       <c r="R95" s="58" t="inlineStr"/>
       <c r="S95" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T95" s="58" t="inlineStr">
@@ -24176,7 +24176,7 @@
       <c r="R96" s="58" t="inlineStr"/>
       <c r="S96" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T96" s="58" t="inlineStr">
@@ -24258,7 +24258,7 @@
       <c r="R97" s="58" t="inlineStr"/>
       <c r="S97" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T97" s="58" t="inlineStr">
@@ -24340,7 +24340,7 @@
       <c r="R98" s="58" t="inlineStr"/>
       <c r="S98" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T98" s="58" t="inlineStr">
@@ -24426,7 +24426,7 @@
       <c r="R99" s="58" t="inlineStr"/>
       <c r="S99" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T99" s="58" t="inlineStr">
@@ -24512,7 +24512,7 @@
       <c r="R100" s="58" t="inlineStr"/>
       <c r="S100" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T100" s="58" t="inlineStr">
@@ -24598,7 +24598,7 @@
       <c r="R101" s="58" t="inlineStr"/>
       <c r="S101" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T101" s="58" t="inlineStr">
@@ -24646,7 +24646,7 @@
       </c>
       <c r="I102" s="58" t="inlineStr">
         <is>
-          <t>Legacy row 14356 takes the yearly change of the revenue gain in USD over the current GDP, not the change of the gain as a share of GDP: with GDP growing, a constant share of GDP keeps giving impulses (Egypt: impulses sum to 4.9% of GDP against a final fiscal space of 3.5%). Replicated in v4.15 (user 2026-10-18: replicate legacy, note issues).</t>
+          <t>Legacy row 14341 takes the yearly change of the revenue gain in USD over the current GDP, not the change of the gain as a share of GDP: with GDP growing, a constant share of GDP keeps giving impulses (Egypt: impulses sum to 4.9% of GDP against a final fiscal space of 3.5%). Replicated in v4.15 (user 2026-10-18: replicate legacy, note issues).</t>
         </is>
       </c>
       <c r="J102" s="58" t="inlineStr">
@@ -24684,7 +24684,7 @@
       <c r="R102" s="58" t="inlineStr"/>
       <c r="S102" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T102" s="58" t="inlineStr">
@@ -24770,7 +24770,7 @@
       <c r="R103" s="58" t="inlineStr"/>
       <c r="S103" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T103" s="58" t="inlineStr">
@@ -24856,7 +24856,7 @@
       <c r="R104" s="58" t="inlineStr"/>
       <c r="S104" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T104" s="58" t="inlineStr">
@@ -24942,7 +24942,7 @@
       <c r="R105" s="58" t="inlineStr"/>
       <c r="S105" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T105" s="58" t="inlineStr">
@@ -25028,7 +25028,7 @@
       <c r="R106" s="58" t="inlineStr"/>
       <c r="S106" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T106" s="58" t="inlineStr">
@@ -25076,12 +25076,12 @@
       </c>
       <c r="I107" s="58" t="inlineStr">
         <is>
-          <t>Legacy total revenue (row 8026) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7913-7999) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7896-7904). The prototype 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
+          <t>Legacy total revenue (row 8012) includes the transport revenues of the engineer road model (customs and VAT on vehicles, feebates, vehicle and charging subsidies, distance tax; rows 7899-7985) and the renewable subsidy cost (from the elasticity power model even where the engineer model is used, rows 7882-7890). The prototype 12e block has both rows at 0 (road engineer revenues parked; no renewable subsidy policy). Egypt: transport +0.04 bn in 2030 against baseline.</t>
         </is>
       </c>
       <c r="J107" s="58" t="inlineStr">
         <is>
-          <t>Renewable subsidies: in the power model since v5.4 (prrns), counted in rsub, rtot and block 12e row rpol.ren, as legacy rows 7896-7904. Transport revenues: dropped with the engineer road model (I61, user 2026-10-20); row rpol.trs stays 0.</t>
+          <t>Renewable subsidies: in the power model since v5.4 (prrns), counted in rsub, rtot and block 12e row rpol.ren, as legacy rows 7882-7890. Transport revenues: dropped with the engineer road model (I61, user 2026-10-20); row rpol.trs stays 0.</t>
         </is>
       </c>
       <c r="K107" s="58" t="n"/>
@@ -25114,7 +25114,7 @@
       <c r="R107" s="58" t="inlineStr"/>
       <c r="S107" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T107" s="58" t="inlineStr">
@@ -25162,7 +25162,7 @@
       </c>
       <c r="I108" s="58" t="inlineStr">
         <is>
-          <t>Legacy counts the methane fee in total revenue (row 8024) and so in the fiscal space, on the scenario's own activity. The prototype counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
+          <t>Legacy counts the methane fee in total revenue (row 8010) and so in the fiscal space, on the scenario's own activity. The prototype counts it too, but with the stored scenario-1 activity of downstream gas and biomass use (v6.2, user decision 2026-10-20: no vulnerability to circular references through the GDP feedback). Differs from legacy only when a policy changes gas or biomass use and a methane fee applies. None for Egypt (no methane fee in the scenarios).</t>
         </is>
       </c>
       <c r="J108" s="58" t="inlineStr">
@@ -25200,7 +25200,7 @@
       <c r="R108" s="58" t="inlineStr"/>
       <c r="S108" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T108" s="58" t="inlineStr">
@@ -25286,7 +25286,7 @@
       <c r="R109" s="58" t="inlineStr"/>
       <c r="S109" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T109" s="58" t="inlineStr">
@@ -25372,7 +25372,7 @@
       <c r="R110" s="58" t="inlineStr"/>
       <c r="S110" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T110" s="58" t="inlineStr">
@@ -25446,7 +25446,7 @@
       <c r="R111" s="58" t="inlineStr"/>
       <c r="S111" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T111" s="58" t="inlineStr">
@@ -25520,7 +25520,7 @@
       <c r="R112" s="58" t="inlineStr"/>
       <c r="S112" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T112" s="58" t="inlineStr">
@@ -25594,7 +25594,7 @@
       <c r="R113" s="58" t="inlineStr"/>
       <c r="S113" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T113" s="58" t="inlineStr">
@@ -25672,7 +25672,7 @@
       </c>
       <c r="S114" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T114" s="58" t="inlineStr">
@@ -25746,7 +25746,7 @@
       <c r="R115" s="58" t="inlineStr"/>
       <c r="S115" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T115" s="58" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="S116" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T116" s="58" t="inlineStr">
@@ -25902,7 +25902,7 @@
       <c r="R117" s="58" t="inlineStr"/>
       <c r="S117" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T117" s="58" t="inlineStr">
@@ -25980,7 +25980,7 @@
       <c r="R118" s="58" t="inlineStr"/>
       <c r="S118" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T118" s="58" t="inlineStr">
@@ -26058,7 +26058,7 @@
       <c r="R119" s="58" t="inlineStr"/>
       <c r="S119" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T119" s="58" t="inlineStr">
@@ -26136,7 +26136,7 @@
       <c r="R120" s="58" t="inlineStr"/>
       <c r="S120" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T120" s="58" t="inlineStr">
@@ -26218,7 +26218,7 @@
       <c r="R121" s="58" t="inlineStr"/>
       <c r="S121" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T121" s="58" t="inlineStr">
@@ -26300,7 +26300,7 @@
       <c r="R122" s="58" t="inlineStr"/>
       <c r="S122" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T122" s="58" t="inlineStr">
@@ -26382,7 +26382,7 @@
       <c r="R123" s="58" t="inlineStr"/>
       <c r="S123" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T123" s="58" t="inlineStr">
@@ -26468,7 +26468,7 @@
       <c r="R124" s="58" t="inlineStr"/>
       <c r="S124" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T124" s="58" t="inlineStr">
@@ -26554,7 +26554,7 @@
       <c r="R125" s="58" t="inlineStr"/>
       <c r="S125" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T125" s="58" t="inlineStr">
@@ -26636,7 +26636,7 @@
       <c r="R126" s="58" t="inlineStr"/>
       <c r="S126" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T126" s="58" t="inlineStr">
@@ -26718,7 +26718,7 @@
       <c r="R127" s="58" t="inlineStr"/>
       <c r="S127" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T127" s="58" t="inlineStr">
@@ -26800,7 +26800,7 @@
       <c r="R128" s="58" t="inlineStr"/>
       <c r="S128" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T128" s="58" t="inlineStr">
@@ -26848,7 +26848,7 @@
       </c>
       <c r="I129" s="58" t="inlineStr">
         <is>
-          <t>MTInputs 354-355 are labelled $/kWh nominal and enter the real cost and revenue without deflation (Mitigation row 2743). Replicated (rows rnsp, rns).</t>
+          <t>MTInputs 352-353 are labelled $/kWh nominal and enter the real cost and revenue without deflation (Mitigation row 2743). Replicated (rows rnsp, rns).</t>
         </is>
       </c>
       <c r="J129" s="58" t="inlineStr">
@@ -26882,7 +26882,7 @@
       <c r="R129" s="58" t="inlineStr"/>
       <c r="S129" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T129" s="58" t="inlineStr">
@@ -26964,7 +26964,7 @@
       <c r="R130" s="58" t="inlineStr"/>
       <c r="S130" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T130" s="58" t="inlineStr">
@@ -27046,7 +27046,7 @@
       <c r="R131" s="58" t="inlineStr"/>
       <c r="S131" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T131" s="58" t="inlineStr">
@@ -27128,7 +27128,7 @@
       <c r="R132" s="58" t="inlineStr"/>
       <c r="S132" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T132" s="58" t="inlineStr">
@@ -27214,7 +27214,7 @@
       <c r="R133" s="58" t="inlineStr"/>
       <c r="S133" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T133" s="58" t="inlineStr">
@@ -27300,7 +27300,7 @@
       <c r="R134" s="58" t="inlineStr"/>
       <c r="S134" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T134" s="58" t="inlineStr">
@@ -27378,7 +27378,7 @@
       <c r="R135" s="58" t="inlineStr"/>
       <c r="S135" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T135" s="58" t="inlineStr">
@@ -27464,7 +27464,7 @@
       <c r="R136" s="58" t="inlineStr"/>
       <c r="S136" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T136" s="58" t="inlineStr">
@@ -27546,7 +27546,7 @@
       <c r="R137" s="58" t="inlineStr"/>
       <c r="S137" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T137" s="58" t="inlineStr">
@@ -27628,7 +27628,7 @@
       <c r="R138" s="58" t="inlineStr"/>
       <c r="S138" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T138" s="58" t="inlineStr">
@@ -27710,7 +27710,7 @@
       <c r="R139" s="58" t="inlineStr"/>
       <c r="S139" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T139" s="58" t="inlineStr">
@@ -27796,7 +27796,7 @@
       <c r="R140" s="58" t="inlineStr"/>
       <c r="S140" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T140" s="58" t="inlineStr">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="I141" s="58" t="inlineStr">
         <is>
-          <t>Legacy grows crude oil, natural gas and coal production (rows 6146-6149) from 2024 with the producer-price response to the methane fee (rows 6137-6144: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The prototype holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
+          <t>Legacy grows crude oil, natural gas and coal production (rows 6132-6135) from 2024 with the producer-price response to the methane fee (rows 6123-6130: price increase x pass-through, Manual inputs J190:J194 elasticities) and the growth of world demand of the global demand scenario (Prices_int rows 323-333, lagged one year). The prototype holds production at the base year (rows ch4.act og, cm). Found 2026-10-19 checking I26.</t>
         </is>
       </c>
       <c r="J141" s="58" t="inlineStr">
@@ -27882,7 +27882,7 @@
       <c r="R141" s="58" t="inlineStr"/>
       <c r="S141" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T141" s="58" t="inlineStr">
@@ -27930,7 +27930,7 @@
       </c>
       <c r="I142" s="58" t="inlineStr">
         <is>
-          <t>Legacy row 18464 H uses 5665 (Mt CO2) for China instead of the data (row 889). The prototype reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
+          <t>Legacy row 18449 H uses 5665 (Mt CO2) for China instead of the data (row 889). The prototype reads sheet GHGHist (or the model where the reference year is modelled); China's latest NDC is a Historical target (ref 2024, modelled), so the value is not used.</t>
         </is>
       </c>
       <c r="J142" s="58" t="inlineStr">
@@ -27968,7 +27968,7 @@
       <c r="R142" s="58" t="inlineStr"/>
       <c r="S142" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T142" s="58" t="inlineStr">
@@ -28054,7 +28054,7 @@
       <c r="R143" s="58" t="inlineStr"/>
       <c r="S143" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T143" s="58" t="inlineStr">
@@ -28140,7 +28140,7 @@
       <c r="R144" s="58" t="inlineStr"/>
       <c r="S144" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T144" s="58" t="inlineStr">
@@ -28226,7 +28226,7 @@
       <c r="R145" s="58" t="inlineStr"/>
       <c r="S145" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T145" s="58" t="inlineStr">
@@ -28308,7 +28308,7 @@
       <c r="R146" s="58" t="inlineStr"/>
       <c r="S146" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T146" s="58" t="inlineStr">
@@ -28356,7 +28356,7 @@
       </c>
       <c r="I147" s="58" t="inlineStr">
         <is>
-          <t>Legacy and the prototype let revenue of year t move GDP only from year t+1 (legacy row 8776 reads the previous column; prototype gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
+          <t>Legacy and the prototype let revenue of year t move GDP only from year t+1 (legacy row 8761 reads the previous column; prototype gdp.lvl = 1 + last year's gdp.eff), and the fiscal space reads revenue of year t only. This lag is what keeps the model free of circular references whatever the revenue lines read; it is not stated anywhere. Recommendation to the CPAT team: make it an explicit rule of the method and keep it when the GDP block changes. Replicated.</t>
         </is>
       </c>
       <c r="J147" s="58" t="inlineStr">
@@ -28390,7 +28390,7 @@
       <c r="R147" s="58" t="inlineStr"/>
       <c r="S147" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T147" s="58" t="inlineStr">
@@ -28476,7 +28476,7 @@
       <c r="R148" s="58" t="inlineStr"/>
       <c r="S148" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T148" s="58" t="inlineStr">
@@ -28529,7 +28529,7 @@
       </c>
       <c r="J149" s="58" t="inlineStr">
         <is>
-          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7562) uses the first two years and applies the factor from the third (it reads only earlier years). The prototype calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
+          <t>Legacy checked: no bug. The source allocation uses energy-balance data (row 894) and the energy CH4 calibration (row 7548) uses the first two years and applies the factor from the third (it reads only earlier years). The prototype calibrated on GHGYear (2024) in every year (its own design) and now reads stored scenario-1 values; the fiscal space uses the stored scenario-1 activity (I47).</t>
         </is>
       </c>
       <c r="K149" s="58" t="n"/>
@@ -28562,7 +28562,7 @@
       <c r="R149" s="58" t="inlineStr"/>
       <c r="S149" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T149" s="58" t="inlineStr">
@@ -28648,7 +28648,7 @@
       <c r="R150" s="58" t="inlineStr"/>
       <c r="S150" s="58" t="inlineStr">
         <is>
-          <t>v7.0</t>
+          <t>v8.2</t>
         </is>
       </c>
       <c r="T150" s="58" t="inlineStr">

--- a/excel_ai/legacy/workbooks/Tracking issues.xlsx
+++ b/excel_ai/legacy/workbooks/Tracking issues.xlsx
@@ -18,7 +18,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CPAT_dev" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGS'!$A$3:$T$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BUGS'!$A$3:$T$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ISSUES-OTHER'!$A$3:$T$150</definedName>
   </definedNames>
   <calcPr calcId="191028" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T165"/>
+  <dimension ref="A1:T166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1320,7 +1320,7 @@
       <c r="R4" s="58" t="inlineStr"/>
       <c r="S4" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T4" s="58" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="S5" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T5" s="58" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="S6" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T6" s="58" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="R7" s="58" t="inlineStr"/>
       <c r="S7" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T7" s="58" t="inlineStr">
@@ -1688,7 +1688,7 @@
       <c r="R8" s="58" t="inlineStr"/>
       <c r="S8" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T8" s="58" t="inlineStr">
@@ -1778,7 +1778,7 @@
       <c r="R9" s="58" t="inlineStr"/>
       <c r="S9" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T9" s="58" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="S10" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T10" s="58" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="S11" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T11" s="58" t="inlineStr">
@@ -2056,7 +2056,7 @@
       <c r="R12" s="58" t="inlineStr"/>
       <c r="S12" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T12" s="58" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="R13" s="58" t="inlineStr"/>
       <c r="S13" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T13" s="58" t="inlineStr">
@@ -2240,7 +2240,7 @@
       <c r="R14" s="58" t="inlineStr"/>
       <c r="S14" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T14" s="58" t="inlineStr">
@@ -2330,7 +2330,7 @@
       <c r="R15" s="58" t="inlineStr"/>
       <c r="S15" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T15" s="58" t="inlineStr">
@@ -2428,7 +2428,7 @@
       </c>
       <c r="S16" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T16" s="58" t="inlineStr">
@@ -2522,7 +2522,7 @@
       <c r="R17" s="58" t="inlineStr"/>
       <c r="S17" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T17" s="58" t="inlineStr">
@@ -2616,7 +2616,7 @@
       <c r="R18" s="58" t="inlineStr"/>
       <c r="S18" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T18" s="58" t="inlineStr">
@@ -2714,7 +2714,7 @@
       <c r="R19" s="58" t="inlineStr"/>
       <c r="S19" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T19" s="58" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="S20" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T20" s="58" t="inlineStr">
@@ -2906,7 +2906,7 @@
       <c r="R21" s="58" t="inlineStr"/>
       <c r="S21" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T21" s="58" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="S22" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T22" s="58" t="inlineStr">
@@ -3098,7 +3098,7 @@
       <c r="R23" s="58" t="inlineStr"/>
       <c r="S23" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T23" s="58" t="inlineStr">
@@ -3192,7 +3192,7 @@
       <c r="R24" s="58" t="inlineStr"/>
       <c r="S24" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T24" s="58" t="inlineStr">
@@ -3286,7 +3286,7 @@
       <c r="R25" s="58" t="inlineStr"/>
       <c r="S25" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T25" s="58" t="inlineStr">
@@ -3380,7 +3380,7 @@
       <c r="R26" s="58" t="inlineStr"/>
       <c r="S26" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T26" s="58" t="inlineStr">
@@ -3474,7 +3474,7 @@
       <c r="R27" s="58" t="inlineStr"/>
       <c r="S27" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T27" s="58" t="inlineStr">
@@ -3568,7 +3568,7 @@
       <c r="R28" s="58" t="inlineStr"/>
       <c r="S28" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T28" s="58" t="inlineStr">
@@ -3662,7 +3662,7 @@
       <c r="R29" s="58" t="inlineStr"/>
       <c r="S29" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T29" s="58" t="inlineStr">
@@ -3756,7 +3756,7 @@
       <c r="R30" s="58" t="inlineStr"/>
       <c r="S30" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T30" s="58" t="inlineStr">
@@ -3850,7 +3850,7 @@
       <c r="R31" s="58" t="inlineStr"/>
       <c r="S31" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T31" s="58" t="inlineStr">
@@ -3944,7 +3944,7 @@
       <c r="R32" s="58" t="inlineStr"/>
       <c r="S32" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T32" s="58" t="inlineStr">
@@ -4038,7 +4038,7 @@
       <c r="R33" s="58" t="inlineStr"/>
       <c r="S33" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T33" s="58" t="inlineStr">
@@ -4132,7 +4132,7 @@
       <c r="R34" s="58" t="inlineStr"/>
       <c r="S34" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T34" s="58" t="inlineStr">
@@ -4226,7 +4226,7 @@
       <c r="R35" s="58" t="inlineStr"/>
       <c r="S35" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T35" s="58" t="inlineStr">
@@ -4320,7 +4320,7 @@
       <c r="R36" s="58" t="inlineStr"/>
       <c r="S36" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T36" s="58" t="inlineStr">
@@ -4414,7 +4414,7 @@
       <c r="R37" s="58" t="inlineStr"/>
       <c r="S37" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T37" s="58" t="inlineStr">
@@ -4508,7 +4508,7 @@
       <c r="R38" s="58" t="inlineStr"/>
       <c r="S38" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T38" s="58" t="inlineStr">
@@ -4602,7 +4602,7 @@
       <c r="R39" s="58" t="inlineStr"/>
       <c r="S39" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T39" s="58" t="inlineStr">
@@ -4696,7 +4696,7 @@
       <c r="R40" s="58" t="inlineStr"/>
       <c r="S40" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T40" s="58" t="inlineStr">
@@ -4790,7 +4790,7 @@
       <c r="R41" s="58" t="inlineStr"/>
       <c r="S41" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T41" s="58" t="inlineStr">
@@ -4884,7 +4884,7 @@
       <c r="R42" s="58" t="inlineStr"/>
       <c r="S42" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T42" s="58" t="inlineStr">
@@ -4978,7 +4978,7 @@
       <c r="R43" s="58" t="inlineStr"/>
       <c r="S43" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T43" s="58" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="S44" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T44" s="58" t="inlineStr">
@@ -5170,7 +5170,7 @@
       </c>
       <c r="S45" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T45" s="58" t="inlineStr">
@@ -5260,7 +5260,7 @@
       <c r="R46" s="58" t="inlineStr"/>
       <c r="S46" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T46" s="58" t="inlineStr">
@@ -5358,7 +5358,7 @@
       <c r="R47" s="58" t="inlineStr"/>
       <c r="S47" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T47" s="58" t="inlineStr">
@@ -5448,7 +5448,7 @@
       <c r="R48" s="58" t="inlineStr"/>
       <c r="S48" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T48" s="58" t="inlineStr">
@@ -5538,7 +5538,7 @@
       <c r="R49" s="58" t="inlineStr"/>
       <c r="S49" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T49" s="58" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="S50" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T50" s="58" t="inlineStr">
@@ -5730,7 +5730,7 @@
       <c r="R51" s="58" t="inlineStr"/>
       <c r="S51" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T51" s="58" t="inlineStr">
@@ -5824,7 +5824,7 @@
       <c r="R52" s="58" t="inlineStr"/>
       <c r="S52" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T52" s="58" t="inlineStr">
@@ -5918,7 +5918,7 @@
       <c r="R53" s="58" t="inlineStr"/>
       <c r="S53" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T53" s="58" t="inlineStr">
@@ -6012,7 +6012,7 @@
       <c r="R54" s="58" t="inlineStr"/>
       <c r="S54" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T54" s="58" t="inlineStr">
@@ -6106,7 +6106,7 @@
       <c r="R55" s="58" t="inlineStr"/>
       <c r="S55" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T55" s="58" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="S56" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T56" s="58" t="inlineStr">
@@ -6298,7 +6298,7 @@
       <c r="R57" s="58" t="inlineStr"/>
       <c r="S57" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T57" s="58" t="inlineStr">
@@ -6396,7 +6396,7 @@
       <c r="R58" s="58" t="inlineStr"/>
       <c r="S58" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T58" s="58" t="inlineStr">
@@ -6494,7 +6494,7 @@
       <c r="R59" s="58" t="inlineStr"/>
       <c r="S59" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T59" s="58" t="inlineStr">
@@ -6588,7 +6588,7 @@
       <c r="R60" s="58" t="inlineStr"/>
       <c r="S60" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T60" s="58" t="inlineStr">
@@ -6682,7 +6682,7 @@
       <c r="R61" s="58" t="inlineStr"/>
       <c r="S61" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T61" s="58" t="inlineStr">
@@ -6776,7 +6776,7 @@
       <c r="R62" s="58" t="inlineStr"/>
       <c r="S62" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T62" s="58" t="inlineStr">
@@ -6870,7 +6870,7 @@
       <c r="R63" s="58" t="inlineStr"/>
       <c r="S63" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T63" s="58" t="inlineStr">
@@ -6968,7 +6968,7 @@
       <c r="R64" s="58" t="inlineStr"/>
       <c r="S64" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T64" s="58" t="inlineStr">
@@ -7066,7 +7066,7 @@
       <c r="R65" s="58" t="inlineStr"/>
       <c r="S65" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T65" s="58" t="inlineStr">
@@ -7160,7 +7160,7 @@
       <c r="R66" s="58" t="inlineStr"/>
       <c r="S66" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T66" s="58" t="inlineStr">
@@ -7254,7 +7254,7 @@
       <c r="R67" s="58" t="inlineStr"/>
       <c r="S67" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T67" s="58" t="inlineStr">
@@ -7348,7 +7348,7 @@
       <c r="R68" s="58" t="inlineStr"/>
       <c r="S68" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T68" s="58" t="inlineStr">
@@ -7442,7 +7442,7 @@
       <c r="R69" s="58" t="inlineStr"/>
       <c r="S69" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T69" s="58" t="inlineStr">
@@ -7536,7 +7536,7 @@
       <c r="R70" s="58" t="inlineStr"/>
       <c r="S70" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T70" s="58" t="inlineStr">
@@ -7626,7 +7626,7 @@
       <c r="R71" s="58" t="inlineStr"/>
       <c r="S71" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T71" s="58" t="inlineStr">
@@ -7720,7 +7720,7 @@
       <c r="R72" s="58" t="inlineStr"/>
       <c r="S72" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T72" s="58" t="inlineStr">
@@ -7814,7 +7814,7 @@
       </c>
       <c r="S73" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T73" s="58" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="S74" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T74" s="58" t="inlineStr">
@@ -7998,7 +7998,7 @@
       <c r="R75" s="58" t="inlineStr"/>
       <c r="S75" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T75" s="58" t="inlineStr">
@@ -8092,7 +8092,7 @@
       <c r="R76" s="58" t="inlineStr"/>
       <c r="S76" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T76" s="58" t="inlineStr">
@@ -8186,7 +8186,7 @@
       <c r="R77" s="58" t="inlineStr"/>
       <c r="S77" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T77" s="58" t="inlineStr">
@@ -8284,7 +8284,7 @@
       </c>
       <c r="S78" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T78" s="58" t="inlineStr">
@@ -8378,7 +8378,7 @@
       <c r="R79" s="58" t="inlineStr"/>
       <c r="S79" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T79" s="58" t="inlineStr">
@@ -8472,7 +8472,7 @@
       <c r="R80" s="58" t="inlineStr"/>
       <c r="S80" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T80" s="58" t="inlineStr">
@@ -8562,7 +8562,7 @@
       <c r="R81" s="58" t="inlineStr"/>
       <c r="S81" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T81" s="58" t="inlineStr">
@@ -8656,7 +8656,7 @@
       <c r="R82" s="58" t="inlineStr"/>
       <c r="S82" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T82" s="58" t="inlineStr">
@@ -8750,7 +8750,7 @@
       <c r="R83" s="58" t="inlineStr"/>
       <c r="S83" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T83" s="58" t="inlineStr">
@@ -8848,7 +8848,7 @@
       <c r="R84" s="58" t="inlineStr"/>
       <c r="S84" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T84" s="58" t="inlineStr">
@@ -8942,7 +8942,7 @@
       <c r="R85" s="58" t="inlineStr"/>
       <c r="S85" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T85" s="58" t="inlineStr">
@@ -9032,7 +9032,7 @@
       <c r="R86" s="58" t="inlineStr"/>
       <c r="S86" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T86" s="58" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="S87" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T87" s="58" t="inlineStr">
@@ -9224,7 +9224,7 @@
       <c r="R88" s="58" t="inlineStr"/>
       <c r="S88" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T88" s="58" t="inlineStr">
@@ -9318,7 +9318,7 @@
       <c r="R89" s="58" t="inlineStr"/>
       <c r="S89" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T89" s="58" t="inlineStr">
@@ -9408,7 +9408,7 @@
       <c r="R90" s="58" t="inlineStr"/>
       <c r="S90" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T90" s="58" t="inlineStr">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="S91" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T91" s="58" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="S92" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T92" s="58" t="inlineStr">
@@ -9702,7 +9702,7 @@
       </c>
       <c r="S93" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T93" s="58" t="inlineStr">
@@ -9796,7 +9796,7 @@
       </c>
       <c r="S94" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T94" s="58" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="S95" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T95" s="58" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="S96" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T96" s="58" t="inlineStr">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="S97" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T97" s="58" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="S98" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T98" s="58" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="S99" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T99" s="58" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="S100" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T100" s="58" t="inlineStr">
@@ -10454,7 +10454,7 @@
       </c>
       <c r="S101" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T101" s="58" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="S102" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T102" s="58" t="inlineStr">
@@ -10646,7 +10646,7 @@
       <c r="R103" s="58" t="inlineStr"/>
       <c r="S103" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T103" s="58" t="inlineStr">
@@ -10740,7 +10740,7 @@
       <c r="R104" s="58" t="inlineStr"/>
       <c r="S104" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T104" s="58" t="inlineStr">
@@ -10834,7 +10834,7 @@
       <c r="R105" s="58" t="inlineStr"/>
       <c r="S105" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T105" s="58" t="inlineStr">
@@ -10924,7 +10924,7 @@
       <c r="R106" s="58" t="inlineStr"/>
       <c r="S106" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T106" s="58" t="inlineStr">
@@ -11014,7 +11014,7 @@
       <c r="R107" s="58" t="inlineStr"/>
       <c r="S107" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T107" s="58" t="inlineStr">
@@ -11104,7 +11104,7 @@
       <c r="R108" s="58" t="inlineStr"/>
       <c r="S108" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T108" s="58" t="inlineStr">
@@ -11194,7 +11194,7 @@
       <c r="R109" s="58" t="inlineStr"/>
       <c r="S109" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T109" s="58" t="inlineStr">
@@ -11284,7 +11284,7 @@
       <c r="R110" s="58" t="inlineStr"/>
       <c r="S110" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T110" s="58" t="inlineStr">
@@ -11374,7 +11374,7 @@
       <c r="R111" s="58" t="inlineStr"/>
       <c r="S111" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T111" s="58" t="inlineStr">
@@ -11468,7 +11468,7 @@
       <c r="R112" s="58" t="inlineStr"/>
       <c r="S112" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T112" s="58" t="inlineStr">
@@ -11562,7 +11562,7 @@
       <c r="R113" s="58" t="inlineStr"/>
       <c r="S113" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T113" s="58" t="inlineStr">
@@ -11652,7 +11652,7 @@
       <c r="R114" s="58" t="inlineStr"/>
       <c r="S114" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T114" s="58" t="inlineStr">
@@ -11742,7 +11742,7 @@
       <c r="R115" s="58" t="inlineStr"/>
       <c r="S115" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T115" s="58" t="inlineStr">
@@ -11832,7 +11832,7 @@
       <c r="R116" s="58" t="inlineStr"/>
       <c r="S116" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T116" s="58" t="inlineStr">
@@ -11926,7 +11926,7 @@
       <c r="R117" s="58" t="inlineStr"/>
       <c r="S117" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T117" s="58" t="inlineStr">
@@ -12020,7 +12020,7 @@
       <c r="R118" s="58" t="inlineStr"/>
       <c r="S118" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T118" s="58" t="inlineStr">
@@ -12118,7 +12118,7 @@
       <c r="R119" s="58" t="inlineStr"/>
       <c r="S119" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T119" s="58" t="inlineStr">
@@ -12212,7 +12212,7 @@
       <c r="R120" s="58" t="inlineStr"/>
       <c r="S120" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T120" s="58" t="inlineStr">
@@ -12306,7 +12306,7 @@
       <c r="R121" s="58" t="inlineStr"/>
       <c r="S121" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T121" s="58" t="inlineStr">
@@ -12404,7 +12404,7 @@
       <c r="R122" s="58" t="inlineStr"/>
       <c r="S122" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T122" s="58" t="inlineStr">
@@ -12498,7 +12498,7 @@
       <c r="R123" s="58" t="inlineStr"/>
       <c r="S123" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T123" s="58" t="inlineStr">
@@ -12592,7 +12592,7 @@
       <c r="R124" s="58" t="inlineStr"/>
       <c r="S124" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T124" s="58" t="inlineStr">
@@ -12686,7 +12686,7 @@
       <c r="R125" s="58" t="inlineStr"/>
       <c r="S125" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T125" s="58" t="inlineStr">
@@ -12776,7 +12776,7 @@
       <c r="R126" s="58" t="inlineStr"/>
       <c r="S126" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T126" s="58" t="inlineStr">
@@ -12866,7 +12866,7 @@
       <c r="R127" s="58" t="inlineStr"/>
       <c r="S127" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T127" s="58" t="inlineStr">
@@ -12960,7 +12960,7 @@
       <c r="R128" s="58" t="inlineStr"/>
       <c r="S128" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T128" s="58" t="inlineStr">
@@ -13054,7 +13054,7 @@
       <c r="R129" s="58" t="inlineStr"/>
       <c r="S129" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T129" s="58" t="inlineStr">
@@ -13148,7 +13148,7 @@
       <c r="R130" s="58" t="inlineStr"/>
       <c r="S130" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T130" s="58" t="inlineStr">
@@ -13242,7 +13242,7 @@
       <c r="R131" s="58" t="inlineStr"/>
       <c r="S131" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T131" s="58" t="inlineStr">
@@ -13336,7 +13336,7 @@
       <c r="R132" s="58" t="inlineStr"/>
       <c r="S132" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T132" s="58" t="inlineStr">
@@ -13430,7 +13430,7 @@
       <c r="R133" s="58" t="inlineStr"/>
       <c r="S133" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T133" s="58" t="inlineStr">
@@ -13520,7 +13520,7 @@
       <c r="R134" s="58" t="inlineStr"/>
       <c r="S134" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T134" s="58" t="inlineStr">
@@ -13610,7 +13610,7 @@
       <c r="R135" s="58" t="inlineStr"/>
       <c r="S135" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T135" s="58" t="inlineStr">
@@ -13700,7 +13700,7 @@
       <c r="R136" s="58" t="inlineStr"/>
       <c r="S136" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T136" s="58" t="inlineStr">
@@ -13790,7 +13790,7 @@
       <c r="R137" s="58" t="inlineStr"/>
       <c r="S137" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T137" s="58" t="inlineStr">
@@ -13880,7 +13880,7 @@
       <c r="R138" s="58" t="inlineStr"/>
       <c r="S138" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T138" s="58" t="inlineStr">
@@ -13970,7 +13970,7 @@
       <c r="R139" s="58" t="inlineStr"/>
       <c r="S139" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T139" s="58" t="inlineStr">
@@ -14056,7 +14056,7 @@
       <c r="R140" s="58" t="inlineStr"/>
       <c r="S140" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T140" s="58" t="inlineStr">
@@ -14146,7 +14146,7 @@
       <c r="R141" s="58" t="inlineStr"/>
       <c r="S141" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T141" s="58" t="inlineStr">
@@ -14236,7 +14236,7 @@
       <c r="R142" s="58" t="inlineStr"/>
       <c r="S142" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T142" s="58" t="inlineStr">
@@ -14326,7 +14326,7 @@
       <c r="R143" s="58" t="inlineStr"/>
       <c r="S143" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T143" s="58" t="inlineStr">
@@ -14416,7 +14416,7 @@
       <c r="R144" s="58" t="inlineStr"/>
       <c r="S144" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T144" s="58" t="inlineStr">
@@ -14506,7 +14506,7 @@
       <c r="R145" s="58" t="inlineStr"/>
       <c r="S145" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T145" s="58" t="inlineStr">
@@ -14596,7 +14596,7 @@
       <c r="R146" s="58" t="inlineStr"/>
       <c r="S146" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T146" s="58" t="inlineStr">
@@ -14686,7 +14686,7 @@
       <c r="R147" s="58" t="inlineStr"/>
       <c r="S147" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T147" s="58" t="inlineStr">
@@ -14776,7 +14776,7 @@
       <c r="R148" s="58" t="inlineStr"/>
       <c r="S148" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T148" s="58" t="inlineStr">
@@ -14866,7 +14866,7 @@
       <c r="R149" s="58" t="inlineStr"/>
       <c r="S149" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T149" s="58" t="inlineStr">
@@ -14956,7 +14956,7 @@
       <c r="R150" s="58" t="inlineStr"/>
       <c r="S150" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T150" s="58" t="inlineStr">
@@ -15046,7 +15046,7 @@
       <c r="R151" s="58" t="inlineStr"/>
       <c r="S151" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T151" s="58" t="inlineStr">
@@ -15132,7 +15132,7 @@
       <c r="R152" s="58" t="inlineStr"/>
       <c r="S152" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T152" s="58" t="inlineStr">
@@ -15222,7 +15222,7 @@
       <c r="R153" s="58" t="inlineStr"/>
       <c r="S153" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T153" s="58" t="inlineStr">
@@ -15312,7 +15312,7 @@
       <c r="R154" s="58" t="inlineStr"/>
       <c r="S154" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T154" s="58" t="inlineStr">
@@ -15398,7 +15398,7 @@
       <c r="R155" s="58" t="inlineStr"/>
       <c r="S155" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T155" s="58" t="inlineStr">
@@ -15496,7 +15496,7 @@
       <c r="R156" s="58" t="inlineStr"/>
       <c r="S156" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T156" s="58" t="inlineStr">
@@ -15594,7 +15594,7 @@
       <c r="R157" s="58" t="inlineStr"/>
       <c r="S157" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T157" s="58" t="inlineStr">
@@ -15688,7 +15688,7 @@
       <c r="R158" s="58" t="inlineStr"/>
       <c r="S158" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T158" s="58" t="inlineStr">
@@ -15782,7 +15782,7 @@
       <c r="R159" s="58" t="inlineStr"/>
       <c r="S159" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T159" s="58" t="inlineStr">
@@ -15876,7 +15876,7 @@
       <c r="R160" s="58" t="inlineStr"/>
       <c r="S160" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T160" s="58" t="inlineStr">
@@ -15962,7 +15962,7 @@
       <c r="R161" s="58" t="inlineStr"/>
       <c r="S161" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T161" s="58" t="inlineStr">
@@ -16048,7 +16048,7 @@
       <c r="R162" s="58" t="inlineStr"/>
       <c r="S162" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T162" s="58" t="inlineStr">
@@ -16138,7 +16138,7 @@
       <c r="R163" s="58" t="inlineStr"/>
       <c r="S163" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T163" s="58" t="inlineStr">
@@ -16228,7 +16228,7 @@
       <c r="R164" s="58" t="inlineStr"/>
       <c r="S164" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T164" s="58" t="inlineStr">
@@ -16318,7 +16318,7 @@
       <c r="R165" s="58" t="inlineStr"/>
       <c r="S165" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T165" s="58" t="inlineStr">
@@ -16327,15 +16327,105 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" s="58" t="inlineStr">
+        <is>
+          <t>L134</t>
+        </is>
+      </c>
+      <c r="B166" s="58" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="C166" s="58" t="inlineStr"/>
+      <c r="D166" s="58" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E166" s="58" t="inlineStr">
+        <is>
+          <t>Price-increase units: other oil products "$/bbn", default "$/liter" for other oil products and biomass</t>
+        </is>
+      </c>
+      <c r="F166" s="58" t="inlineStr">
+        <is>
+          <t>Legacy bug (mitigation)</t>
+        </is>
+      </c>
+      <c r="G166" s="58" t="inlineStr">
+        <is>
+          <t>Other mitigation</t>
+        </is>
+      </c>
+      <c r="H166" s="58" t="inlineStr">
+        <is>
+          <t>MTInputs rows 182-183 (columns E and G); Mitigation I177, I180</t>
+        </is>
+      </c>
+      <c r="I166" s="58" t="inlineStr">
+        <is>
+          <t>The unit labels of the price-increase inputs read "$/bbn" (for $/bbl) for other oil products, and the default column says "$/liter" for other oil products and biomass, whose prices are per barrel and per GJ. No formula reads the labels (Mitigation rows 168-180 use the amounts in G and H only), so no value changes; a user typing an increase per liter for these fuels gets a wrong price path. Found by the tracker leads (2026-10-23).</t>
+        </is>
+      </c>
+      <c r="J166" s="58" t="inlineStr">
+        <is>
+          <t>Label the price-increase units USD/bbl (other oil products) and USD/GJ (biomass) in columns E and G of MTInputs rows 182-183.</t>
+        </is>
+      </c>
+      <c r="K166" s="58" t="inlineStr">
+        <is>
+          <t>Labels only: no value changes; a user may type an increase in the wrong unit. prototype: Fixed (v8.3): the prototype's ScenarioDefinition rows 182-183 read $/bbl and $/GJ, defaults included.</t>
+        </is>
+      </c>
+      <c r="L166" s="58" t="inlineStr"/>
+      <c r="M166" s="58" t="inlineStr">
+        <is>
+          <t>Not reconciled yet</t>
+        </is>
+      </c>
+      <c r="N166" s="58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O166" s="58" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="P166" s="58" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="Q166" s="58" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="R166" s="58" t="inlineStr"/>
+      <c r="S166" s="58" t="inlineStr">
+        <is>
+          <t>v8.3</t>
+        </is>
+      </c>
+      <c r="T166" s="58" t="inlineStr">
+        <is>
+          <t>Legacy bug</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:T165">
+  <autoFilter ref="A3:T166">
     <filterColumn colId="1" hiddenButton="0" showButton="1">
       <customFilters>
         <customFilter val="Closed*" operator="notEqual"/>
       </customFilters>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A4:T165">
+  <conditionalFormatting sqref="A4:T166">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT($B4,6)="Closed"</formula>
     </cfRule>
@@ -16568,7 +16658,7 @@
       <c r="R4" s="58" t="inlineStr"/>
       <c r="S4" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T4" s="58" t="inlineStr">
@@ -16650,7 +16740,7 @@
       <c r="R5" s="58" t="inlineStr"/>
       <c r="S5" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T5" s="58" t="inlineStr">
@@ -16740,7 +16830,7 @@
       </c>
       <c r="S6" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T6" s="58" t="inlineStr">
@@ -16822,7 +16912,7 @@
       <c r="R7" s="58" t="inlineStr"/>
       <c r="S7" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T7" s="58" t="inlineStr">
@@ -16908,7 +16998,7 @@
       <c r="R8" s="58" t="inlineStr"/>
       <c r="S8" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T8" s="58" t="inlineStr">
@@ -16990,7 +17080,7 @@
       <c r="R9" s="58" t="inlineStr"/>
       <c r="S9" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T9" s="58" t="inlineStr">
@@ -17072,7 +17162,7 @@
       <c r="R10" s="58" t="inlineStr"/>
       <c r="S10" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T10" s="58" t="inlineStr">
@@ -17158,7 +17248,7 @@
       <c r="R11" s="58" t="inlineStr"/>
       <c r="S11" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T11" s="58" t="inlineStr">
@@ -17244,7 +17334,7 @@
       <c r="R12" s="58" t="inlineStr"/>
       <c r="S12" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T12" s="58" t="inlineStr">
@@ -17326,7 +17416,7 @@
       <c r="R13" s="58" t="inlineStr"/>
       <c r="S13" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T13" s="58" t="inlineStr">
@@ -17416,7 +17506,7 @@
       </c>
       <c r="S14" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T14" s="58" t="inlineStr">
@@ -17502,7 +17592,7 @@
       <c r="R15" s="58" t="inlineStr"/>
       <c r="S15" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T15" s="58" t="inlineStr">
@@ -17588,7 +17678,7 @@
       <c r="R16" s="58" t="inlineStr"/>
       <c r="S16" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T16" s="58" t="inlineStr">
@@ -17670,7 +17760,7 @@
       <c r="R17" s="58" t="inlineStr"/>
       <c r="S17" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T17" s="58" t="inlineStr">
@@ -17756,7 +17846,7 @@
       <c r="R18" s="58" t="inlineStr"/>
       <c r="S18" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T18" s="58" t="inlineStr">
@@ -17846,7 +17936,7 @@
       <c r="R19" s="58" t="inlineStr"/>
       <c r="S19" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T19" s="58" t="inlineStr">
@@ -17936,7 +18026,7 @@
       </c>
       <c r="S20" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T20" s="58" t="inlineStr">
@@ -18022,7 +18112,7 @@
       <c r="R21" s="58" t="inlineStr"/>
       <c r="S21" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T21" s="58" t="inlineStr">
@@ -18108,7 +18198,7 @@
       </c>
       <c r="S22" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T22" s="58" t="inlineStr">
@@ -18194,7 +18284,7 @@
       <c r="R23" s="58" t="inlineStr"/>
       <c r="S23" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T23" s="58" t="inlineStr">
@@ -18280,7 +18370,7 @@
       <c r="R24" s="58" t="inlineStr"/>
       <c r="S24" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T24" s="58" t="inlineStr">
@@ -18366,7 +18456,7 @@
       <c r="R25" s="58" t="inlineStr"/>
       <c r="S25" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T25" s="58" t="inlineStr">
@@ -18452,7 +18542,7 @@
       <c r="R26" s="58" t="inlineStr"/>
       <c r="S26" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T26" s="58" t="inlineStr">
@@ -18530,7 +18620,7 @@
       <c r="R27" s="58" t="inlineStr"/>
       <c r="S27" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T27" s="58" t="inlineStr">
@@ -18612,7 +18702,7 @@
       </c>
       <c r="S28" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T28" s="58" t="inlineStr">
@@ -18694,7 +18784,7 @@
       <c r="R29" s="58" t="inlineStr"/>
       <c r="S29" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T29" s="58" t="inlineStr">
@@ -18772,7 +18862,7 @@
       <c r="R30" s="58" t="inlineStr"/>
       <c r="S30" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T30" s="58" t="inlineStr">
@@ -18854,7 +18944,7 @@
       <c r="R31" s="58" t="inlineStr"/>
       <c r="S31" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T31" s="58" t="inlineStr">
@@ -18936,7 +19026,7 @@
       <c r="R32" s="58" t="inlineStr"/>
       <c r="S32" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T32" s="58" t="inlineStr">
@@ -19022,7 +19112,7 @@
       <c r="R33" s="58" t="inlineStr"/>
       <c r="S33" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T33" s="58" t="inlineStr">
@@ -19104,7 +19194,7 @@
       <c r="R34" s="58" t="inlineStr"/>
       <c r="S34" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T34" s="58" t="inlineStr">
@@ -19190,7 +19280,7 @@
       </c>
       <c r="S35" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T35" s="58" t="inlineStr">
@@ -19268,7 +19358,7 @@
       <c r="R36" s="58" t="inlineStr"/>
       <c r="S36" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T36" s="58" t="inlineStr">
@@ -19346,7 +19436,7 @@
       <c r="R37" s="58" t="inlineStr"/>
       <c r="S37" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T37" s="58" t="inlineStr">
@@ -19424,7 +19514,7 @@
       <c r="R38" s="58" t="inlineStr"/>
       <c r="S38" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T38" s="58" t="inlineStr">
@@ -19506,7 +19596,7 @@
       </c>
       <c r="S39" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T39" s="58" t="inlineStr">
@@ -19584,7 +19674,7 @@
       <c r="R40" s="58" t="inlineStr"/>
       <c r="S40" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T40" s="58" t="inlineStr">
@@ -19666,7 +19756,7 @@
       <c r="R41" s="58" t="inlineStr"/>
       <c r="S41" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T41" s="58" t="inlineStr">
@@ -19748,7 +19838,7 @@
       <c r="R42" s="58" t="inlineStr"/>
       <c r="S42" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T42" s="58" t="inlineStr">
@@ -19830,7 +19920,7 @@
       <c r="R43" s="58" t="inlineStr"/>
       <c r="S43" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T43" s="58" t="inlineStr">
@@ -19912,7 +20002,7 @@
       <c r="R44" s="58" t="inlineStr"/>
       <c r="S44" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T44" s="58" t="inlineStr">
@@ -19998,7 +20088,7 @@
       <c r="R45" s="58" t="inlineStr"/>
       <c r="S45" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T45" s="58" t="inlineStr">
@@ -20080,7 +20170,7 @@
       <c r="R46" s="58" t="inlineStr"/>
       <c r="S46" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T46" s="58" t="inlineStr">
@@ -20166,7 +20256,7 @@
       </c>
       <c r="S47" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T47" s="58" t="inlineStr">
@@ -20248,7 +20338,7 @@
       <c r="R48" s="58" t="inlineStr"/>
       <c r="S48" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T48" s="58" t="inlineStr">
@@ -20330,7 +20420,7 @@
       <c r="R49" s="58" t="inlineStr"/>
       <c r="S49" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T49" s="58" t="inlineStr">
@@ -20408,7 +20498,7 @@
       <c r="R50" s="58" t="inlineStr"/>
       <c r="S50" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T50" s="58" t="inlineStr">
@@ -20494,7 +20584,7 @@
       <c r="R51" s="58" t="inlineStr"/>
       <c r="S51" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T51" s="58" t="inlineStr">
@@ -20580,7 +20670,7 @@
       <c r="R52" s="58" t="inlineStr"/>
       <c r="S52" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T52" s="58" t="inlineStr">
@@ -20666,7 +20756,7 @@
       <c r="R53" s="58" t="inlineStr"/>
       <c r="S53" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T53" s="58" t="inlineStr">
@@ -20748,7 +20838,7 @@
       <c r="R54" s="58" t="inlineStr"/>
       <c r="S54" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T54" s="58" t="inlineStr">
@@ -20834,7 +20924,7 @@
       </c>
       <c r="S55" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T55" s="58" t="inlineStr">
@@ -20916,7 +21006,7 @@
       <c r="R56" s="58" t="inlineStr"/>
       <c r="S56" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T56" s="58" t="inlineStr">
@@ -21002,7 +21092,7 @@
       <c r="R57" s="58" t="inlineStr"/>
       <c r="S57" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T57" s="58" t="inlineStr">
@@ -21084,7 +21174,7 @@
       <c r="R58" s="58" t="inlineStr"/>
       <c r="S58" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T58" s="58" t="inlineStr">
@@ -21162,7 +21252,7 @@
       <c r="R59" s="58" t="inlineStr"/>
       <c r="S59" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T59" s="58" t="inlineStr">
@@ -21244,7 +21334,7 @@
       <c r="R60" s="58" t="inlineStr"/>
       <c r="S60" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T60" s="58" t="inlineStr">
@@ -21326,7 +21416,7 @@
       <c r="R61" s="58" t="inlineStr"/>
       <c r="S61" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T61" s="58" t="inlineStr">
@@ -21408,7 +21498,7 @@
       <c r="R62" s="58" t="inlineStr"/>
       <c r="S62" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T62" s="58" t="inlineStr">
@@ -21490,7 +21580,7 @@
       <c r="R63" s="58" t="inlineStr"/>
       <c r="S63" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T63" s="58" t="inlineStr">
@@ -21576,7 +21666,7 @@
       <c r="R64" s="58" t="inlineStr"/>
       <c r="S64" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T64" s="58" t="inlineStr">
@@ -21654,7 +21744,7 @@
       <c r="R65" s="58" t="inlineStr"/>
       <c r="S65" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T65" s="58" t="inlineStr">
@@ -21736,7 +21826,7 @@
       </c>
       <c r="S66" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T66" s="58" t="inlineStr">
@@ -21814,7 +21904,7 @@
       <c r="R67" s="58" t="inlineStr"/>
       <c r="S67" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T67" s="58" t="inlineStr">
@@ -21892,7 +21982,7 @@
       <c r="R68" s="58" t="inlineStr"/>
       <c r="S68" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T68" s="58" t="inlineStr">
@@ -21974,7 +22064,7 @@
       <c r="R69" s="58" t="inlineStr"/>
       <c r="S69" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T69" s="58" t="inlineStr">
@@ -22052,7 +22142,7 @@
       <c r="R70" s="58" t="inlineStr"/>
       <c r="S70" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T70" s="58" t="inlineStr">
@@ -22130,7 +22220,7 @@
       <c r="R71" s="58" t="inlineStr"/>
       <c r="S71" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T71" s="58" t="inlineStr">
@@ -22212,7 +22302,7 @@
       <c r="R72" s="58" t="inlineStr"/>
       <c r="S72" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T72" s="58" t="inlineStr">
@@ -22290,7 +22380,7 @@
       <c r="R73" s="58" t="inlineStr"/>
       <c r="S73" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T73" s="58" t="inlineStr">
@@ -22372,7 +22462,7 @@
       <c r="R74" s="58" t="inlineStr"/>
       <c r="S74" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T74" s="58" t="inlineStr">
@@ -22454,7 +22544,7 @@
       <c r="R75" s="58" t="inlineStr"/>
       <c r="S75" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T75" s="58" t="inlineStr">
@@ -22532,7 +22622,7 @@
       <c r="R76" s="58" t="inlineStr"/>
       <c r="S76" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T76" s="58" t="inlineStr">
@@ -22610,7 +22700,7 @@
       <c r="R77" s="58" t="inlineStr"/>
       <c r="S77" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T77" s="58" t="inlineStr">
@@ -22688,7 +22778,7 @@
       <c r="R78" s="58" t="inlineStr"/>
       <c r="S78" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T78" s="58" t="inlineStr">
@@ -22770,7 +22860,7 @@
       </c>
       <c r="S79" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T79" s="58" t="inlineStr">
@@ -22852,7 +22942,7 @@
       <c r="R80" s="58" t="inlineStr"/>
       <c r="S80" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T80" s="58" t="inlineStr">
@@ -22934,7 +23024,7 @@
       <c r="R81" s="58" t="inlineStr"/>
       <c r="S81" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T81" s="58" t="inlineStr">
@@ -23012,7 +23102,7 @@
       <c r="R82" s="58" t="inlineStr"/>
       <c r="S82" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T82" s="58" t="inlineStr">
@@ -23102,7 +23192,7 @@
       <c r="R83" s="58" t="inlineStr"/>
       <c r="S83" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T83" s="58" t="inlineStr">
@@ -23188,7 +23278,7 @@
       <c r="R84" s="58" t="inlineStr"/>
       <c r="S84" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T84" s="58" t="inlineStr">
@@ -23274,7 +23364,7 @@
       <c r="R85" s="58" t="inlineStr"/>
       <c r="S85" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T85" s="58" t="inlineStr">
@@ -23356,7 +23446,7 @@
       <c r="R86" s="58" t="inlineStr"/>
       <c r="S86" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T86" s="58" t="inlineStr">
@@ -23438,7 +23528,7 @@
       <c r="R87" s="58" t="inlineStr"/>
       <c r="S87" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T87" s="58" t="inlineStr">
@@ -23520,7 +23610,7 @@
       <c r="R88" s="58" t="inlineStr"/>
       <c r="S88" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T88" s="58" t="inlineStr">
@@ -23602,7 +23692,7 @@
       <c r="R89" s="58" t="inlineStr"/>
       <c r="S89" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T89" s="58" t="inlineStr">
@@ -23684,7 +23774,7 @@
       <c r="R90" s="58" t="inlineStr"/>
       <c r="S90" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T90" s="58" t="inlineStr">
@@ -23766,7 +23856,7 @@
       <c r="R91" s="58" t="inlineStr"/>
       <c r="S91" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T91" s="58" t="inlineStr">
@@ -23848,7 +23938,7 @@
       <c r="R92" s="58" t="inlineStr"/>
       <c r="S92" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T92" s="58" t="inlineStr">
@@ -23930,7 +24020,7 @@
       <c r="R93" s="58" t="inlineStr"/>
       <c r="S93" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T93" s="58" t="inlineStr">
@@ -24012,7 +24102,7 @@
       <c r="R94" s="58" t="inlineStr"/>
       <c r="S94" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T94" s="58" t="inlineStr">
@@ -24094,7 +24184,7 @@
       <c r="R95" s="58" t="inlineStr"/>
       <c r="S95" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T95" s="58" t="inlineStr">
@@ -24176,7 +24266,7 @@
       <c r="R96" s="58" t="inlineStr"/>
       <c r="S96" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T96" s="58" t="inlineStr">
@@ -24258,7 +24348,7 @@
       <c r="R97" s="58" t="inlineStr"/>
       <c r="S97" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T97" s="58" t="inlineStr">
@@ -24340,7 +24430,7 @@
       <c r="R98" s="58" t="inlineStr"/>
       <c r="S98" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T98" s="58" t="inlineStr">
@@ -24426,7 +24516,7 @@
       <c r="R99" s="58" t="inlineStr"/>
       <c r="S99" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T99" s="58" t="inlineStr">
@@ -24512,7 +24602,7 @@
       <c r="R100" s="58" t="inlineStr"/>
       <c r="S100" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T100" s="58" t="inlineStr">
@@ -24598,7 +24688,7 @@
       <c r="R101" s="58" t="inlineStr"/>
       <c r="S101" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T101" s="58" t="inlineStr">
@@ -24684,7 +24774,7 @@
       <c r="R102" s="58" t="inlineStr"/>
       <c r="S102" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T102" s="58" t="inlineStr">
@@ -24770,7 +24860,7 @@
       <c r="R103" s="58" t="inlineStr"/>
       <c r="S103" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T103" s="58" t="inlineStr">
@@ -24856,7 +24946,7 @@
       <c r="R104" s="58" t="inlineStr"/>
       <c r="S104" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T104" s="58" t="inlineStr">
@@ -24942,7 +25032,7 @@
       <c r="R105" s="58" t="inlineStr"/>
       <c r="S105" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T105" s="58" t="inlineStr">
@@ -25028,7 +25118,7 @@
       <c r="R106" s="58" t="inlineStr"/>
       <c r="S106" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T106" s="58" t="inlineStr">
@@ -25114,7 +25204,7 @@
       <c r="R107" s="58" t="inlineStr"/>
       <c r="S107" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T107" s="58" t="inlineStr">
@@ -25200,7 +25290,7 @@
       <c r="R108" s="58" t="inlineStr"/>
       <c r="S108" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T108" s="58" t="inlineStr">
@@ -25286,7 +25376,7 @@
       <c r="R109" s="58" t="inlineStr"/>
       <c r="S109" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T109" s="58" t="inlineStr">
@@ -25372,7 +25462,7 @@
       <c r="R110" s="58" t="inlineStr"/>
       <c r="S110" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T110" s="58" t="inlineStr">
@@ -25446,7 +25536,7 @@
       <c r="R111" s="58" t="inlineStr"/>
       <c r="S111" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T111" s="58" t="inlineStr">
@@ -25520,7 +25610,7 @@
       <c r="R112" s="58" t="inlineStr"/>
       <c r="S112" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T112" s="58" t="inlineStr">
@@ -25594,7 +25684,7 @@
       <c r="R113" s="58" t="inlineStr"/>
       <c r="S113" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T113" s="58" t="inlineStr">
@@ -25672,7 +25762,7 @@
       </c>
       <c r="S114" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T114" s="58" t="inlineStr">
@@ -25746,7 +25836,7 @@
       <c r="R115" s="58" t="inlineStr"/>
       <c r="S115" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T115" s="58" t="inlineStr">
@@ -25824,7 +25914,7 @@
       </c>
       <c r="S116" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T116" s="58" t="inlineStr">
@@ -25902,7 +25992,7 @@
       <c r="R117" s="58" t="inlineStr"/>
       <c r="S117" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T117" s="58" t="inlineStr">
@@ -25980,7 +26070,7 @@
       <c r="R118" s="58" t="inlineStr"/>
       <c r="S118" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T118" s="58" t="inlineStr">
@@ -26058,7 +26148,7 @@
       <c r="R119" s="58" t="inlineStr"/>
       <c r="S119" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T119" s="58" t="inlineStr">
@@ -26136,7 +26226,7 @@
       <c r="R120" s="58" t="inlineStr"/>
       <c r="S120" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T120" s="58" t="inlineStr">
@@ -26218,7 +26308,7 @@
       <c r="R121" s="58" t="inlineStr"/>
       <c r="S121" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T121" s="58" t="inlineStr">
@@ -26300,7 +26390,7 @@
       <c r="R122" s="58" t="inlineStr"/>
       <c r="S122" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T122" s="58" t="inlineStr">
@@ -26382,7 +26472,7 @@
       <c r="R123" s="58" t="inlineStr"/>
       <c r="S123" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T123" s="58" t="inlineStr">
@@ -26468,7 +26558,7 @@
       <c r="R124" s="58" t="inlineStr"/>
       <c r="S124" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T124" s="58" t="inlineStr">
@@ -26554,7 +26644,7 @@
       <c r="R125" s="58" t="inlineStr"/>
       <c r="S125" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T125" s="58" t="inlineStr">
@@ -26636,7 +26726,7 @@
       <c r="R126" s="58" t="inlineStr"/>
       <c r="S126" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T126" s="58" t="inlineStr">
@@ -26718,7 +26808,7 @@
       <c r="R127" s="58" t="inlineStr"/>
       <c r="S127" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T127" s="58" t="inlineStr">
@@ -26800,7 +26890,7 @@
       <c r="R128" s="58" t="inlineStr"/>
       <c r="S128" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T128" s="58" t="inlineStr">
@@ -26882,7 +26972,7 @@
       <c r="R129" s="58" t="inlineStr"/>
       <c r="S129" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T129" s="58" t="inlineStr">
@@ -26964,7 +27054,7 @@
       <c r="R130" s="58" t="inlineStr"/>
       <c r="S130" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T130" s="58" t="inlineStr">
@@ -27046,7 +27136,7 @@
       <c r="R131" s="58" t="inlineStr"/>
       <c r="S131" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T131" s="58" t="inlineStr">
@@ -27128,7 +27218,7 @@
       <c r="R132" s="58" t="inlineStr"/>
       <c r="S132" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T132" s="58" t="inlineStr">
@@ -27214,7 +27304,7 @@
       <c r="R133" s="58" t="inlineStr"/>
       <c r="S133" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T133" s="58" t="inlineStr">
@@ -27300,7 +27390,7 @@
       <c r="R134" s="58" t="inlineStr"/>
       <c r="S134" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T134" s="58" t="inlineStr">
@@ -27378,7 +27468,7 @@
       <c r="R135" s="58" t="inlineStr"/>
       <c r="S135" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T135" s="58" t="inlineStr">
@@ -27464,7 +27554,7 @@
       <c r="R136" s="58" t="inlineStr"/>
       <c r="S136" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T136" s="58" t="inlineStr">
@@ -27546,7 +27636,7 @@
       <c r="R137" s="58" t="inlineStr"/>
       <c r="S137" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T137" s="58" t="inlineStr">
@@ -27628,7 +27718,7 @@
       <c r="R138" s="58" t="inlineStr"/>
       <c r="S138" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T138" s="58" t="inlineStr">
@@ -27710,7 +27800,7 @@
       <c r="R139" s="58" t="inlineStr"/>
       <c r="S139" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T139" s="58" t="inlineStr">
@@ -27796,7 +27886,7 @@
       <c r="R140" s="58" t="inlineStr"/>
       <c r="S140" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T140" s="58" t="inlineStr">
@@ -27882,7 +27972,7 @@
       <c r="R141" s="58" t="inlineStr"/>
       <c r="S141" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T141" s="58" t="inlineStr">
@@ -27968,7 +28058,7 @@
       <c r="R142" s="58" t="inlineStr"/>
       <c r="S142" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T142" s="58" t="inlineStr">
@@ -28054,7 +28144,7 @@
       <c r="R143" s="58" t="inlineStr"/>
       <c r="S143" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T143" s="58" t="inlineStr">
@@ -28140,7 +28230,7 @@
       <c r="R144" s="58" t="inlineStr"/>
       <c r="S144" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T144" s="58" t="inlineStr">
@@ -28226,7 +28316,7 @@
       <c r="R145" s="58" t="inlineStr"/>
       <c r="S145" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T145" s="58" t="inlineStr">
@@ -28308,7 +28398,7 @@
       <c r="R146" s="58" t="inlineStr"/>
       <c r="S146" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T146" s="58" t="inlineStr">
@@ -28390,7 +28480,7 @@
       <c r="R147" s="58" t="inlineStr"/>
       <c r="S147" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T147" s="58" t="inlineStr">
@@ -28476,7 +28566,7 @@
       <c r="R148" s="58" t="inlineStr"/>
       <c r="S148" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T148" s="58" t="inlineStr">
@@ -28562,7 +28652,7 @@
       <c r="R149" s="58" t="inlineStr"/>
       <c r="S149" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T149" s="58" t="inlineStr">
@@ -28648,7 +28738,7 @@
       <c r="R150" s="58" t="inlineStr"/>
       <c r="S150" s="58" t="inlineStr">
         <is>
-          <t>v8.2</t>
+          <t>v8.3</t>
         </is>
       </c>
       <c r="T150" s="58" t="inlineStr">
